--- a/input/StatGuide.xlsx
+++ b/input/StatGuide.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yannic/Dropbox/Code/Static V2/input/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yannic/Dropbox/Code/StatAssist_V2/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2076AEB-5B44-604F-AEE6-97895A0B2C35}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5E60F48-AB6A-494C-A0BD-3E3E9A026513}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12560" yWindow="8220" windowWidth="23540" windowHeight="13260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -966,9 +966,6 @@
 In the end, it is up to the analyst to determine what the meaning of an outlier is; high variability or just experimental error.</t>
   </si>
   <si>
-    <t>P-value</t>
-  </si>
-  <si>
     <t>P-Value</t>
   </si>
   <si>
@@ -1578,6 +1575,9 @@
   </si>
   <si>
     <t>What does it mean?</t>
+  </si>
+  <si>
+    <t>p</t>
   </si>
 </sst>
 </file>
@@ -2053,19 +2053,19 @@
         <v>1</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
@@ -2219,7 +2219,7 @@
       <c r="X6" s="4"/>
       <c r="Y6" s="4"/>
     </row>
-    <row r="7" spans="1:25" ht="306">
+    <row r="7" spans="1:25" ht="409.6">
       <c r="A7" s="7" t="s">
         <v>24</v>
       </c>
@@ -3376,7 +3376,7 @@
         <v>173</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F42" s="7"/>
       <c r="G42" s="7" t="s">
@@ -3452,7 +3452,7 @@
         <v>190</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F46" s="7"/>
       <c r="G46" s="7" t="s">
@@ -3558,7 +3558,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="398">
+    <row r="52" spans="1:7" ht="409.6">
       <c r="A52" s="7" t="s">
         <v>219</v>
       </c>
@@ -3900,30 +3900,30 @@
     </row>
     <row r="70" spans="1:7" ht="210">
       <c r="A70" s="7" t="s">
+        <v>498</v>
+      </c>
+      <c r="B70" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="B70" s="7" t="s">
+      <c r="C70" s="7" t="s">
         <v>303</v>
-      </c>
-      <c r="C70" s="7" t="s">
-        <v>304</v>
       </c>
       <c r="D70" s="7"/>
       <c r="E70" s="8"/>
       <c r="F70" s="7"/>
       <c r="G70" s="7" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="60">
       <c r="A71" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="C71" s="7" t="s">
         <v>306</v>
-      </c>
-      <c r="B71" s="7" t="s">
-        <v>306</v>
-      </c>
-      <c r="C71" s="7" t="s">
-        <v>307</v>
       </c>
       <c r="D71" s="7"/>
       <c r="E71" s="8"/>
@@ -3932,97 +3932,97 @@
     </row>
     <row r="72" spans="1:7" ht="285">
       <c r="A72" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="B72" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="B72" s="7" t="s">
+      <c r="C72" s="10" t="s">
         <v>309</v>
       </c>
-      <c r="C72" s="10" t="s">
+      <c r="D72" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="D72" s="7" t="s">
-        <v>311</v>
-      </c>
       <c r="E72" s="8" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="F72" s="7"/>
       <c r="G72" s="7" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="120">
       <c r="A73" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="C73" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="B73" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C73" s="7" t="s">
+      <c r="D73" s="7" t="s">
         <v>314</v>
-      </c>
-      <c r="D73" s="7" t="s">
-        <v>315</v>
       </c>
       <c r="E73" s="8"/>
       <c r="F73" s="7"/>
       <c r="G73" s="7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="105">
       <c r="A74" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="B74" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="B74" s="7" t="s">
+      <c r="C74" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="C74" s="10" t="s">
+      <c r="D74" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="D74" s="7" t="s">
-        <v>320</v>
-      </c>
       <c r="E74" s="8" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F74" s="7"/>
       <c r="G74" s="7" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="409.6">
+      <c r="A75" s="7" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" ht="398">
-      <c r="A75" s="7" t="s">
+      <c r="B75" s="7" t="s">
         <v>322</v>
       </c>
-      <c r="B75" s="7" t="s">
+      <c r="C75" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="C75" s="7" t="s">
+      <c r="D75" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="D75" s="7" t="s">
+      <c r="E75" s="8" t="s">
+        <v>483</v>
+      </c>
+      <c r="F75" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="G75" s="7" t="s">
         <v>325</v>
-      </c>
-      <c r="E75" s="8" t="s">
-        <v>484</v>
-      </c>
-      <c r="F75" s="7" t="s">
-        <v>327</v>
-      </c>
-      <c r="G75" s="7" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="75">
       <c r="A76" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="C76" s="7" t="s">
         <v>328</v>
-      </c>
-      <c r="B76" s="7" t="s">
-        <v>328</v>
-      </c>
-      <c r="C76" s="7" t="s">
-        <v>329</v>
       </c>
       <c r="D76" s="7"/>
       <c r="E76" s="8"/>
@@ -4031,92 +4031,92 @@
     </row>
     <row r="77" spans="1:7" ht="90">
       <c r="A77" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="B77" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="B77" s="7" t="s">
+      <c r="C77" s="7" t="s">
         <v>331</v>
       </c>
-      <c r="C77" s="7" t="s">
+      <c r="D77" s="7" t="s">
         <v>332</v>
-      </c>
-      <c r="D77" s="7" t="s">
-        <v>333</v>
       </c>
       <c r="E77" s="8"/>
       <c r="F77" s="7"/>
       <c r="G77" s="7" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="120">
       <c r="A78" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="C78" s="7" t="s">
         <v>335</v>
       </c>
-      <c r="B78" s="7" t="s">
-        <v>335</v>
-      </c>
-      <c r="C78" s="7" t="s">
+      <c r="D78" s="7" t="s">
         <v>336</v>
-      </c>
-      <c r="D78" s="7" t="s">
-        <v>337</v>
       </c>
       <c r="E78" s="8"/>
       <c r="F78" s="7"/>
       <c r="G78" s="7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="75">
       <c r="A79" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="C79" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="B79" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="C79" s="7" t="s">
+      <c r="D79" s="7" t="s">
         <v>340</v>
-      </c>
-      <c r="D79" s="7" t="s">
-        <v>341</v>
       </c>
       <c r="E79" s="8"/>
       <c r="F79" s="7"/>
       <c r="G79" s="7" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="384">
       <c r="A80" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="B80" s="7" t="s">
         <v>343</v>
       </c>
-      <c r="B80" s="7" t="s">
+      <c r="C80" s="7" t="s">
         <v>344</v>
       </c>
-      <c r="C80" s="7" t="s">
+      <c r="D80" s="7" t="s">
         <v>345</v>
-      </c>
-      <c r="D80" s="7" t="s">
-        <v>346</v>
       </c>
       <c r="E80" s="8"/>
       <c r="F80" s="7"/>
       <c r="G80" s="7" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="342">
       <c r="A81" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="B81" s="7" t="s">
         <v>348</v>
       </c>
-      <c r="B81" s="7" t="s">
+      <c r="C81" s="7" t="s">
         <v>349</v>
       </c>
-      <c r="C81" s="7" t="s">
+      <c r="D81" s="7" t="s">
         <v>350</v>
-      </c>
-      <c r="D81" s="7" t="s">
-        <v>351</v>
       </c>
       <c r="E81" s="8"/>
       <c r="F81" s="7"/>
@@ -4124,121 +4124,121 @@
     </row>
     <row r="82" spans="1:7" ht="84">
       <c r="A82" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="C82" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="B82" s="7" t="s">
-        <v>352</v>
-      </c>
-      <c r="C82" s="7" t="s">
+      <c r="D82" s="11" t="s">
         <v>353</v>
-      </c>
-      <c r="D82" s="11" t="s">
-        <v>354</v>
       </c>
       <c r="E82" s="8"/>
       <c r="F82" s="7"/>
       <c r="G82" s="11" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="409.6">
       <c r="A83" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="B83" s="7" t="s">
         <v>356</v>
       </c>
-      <c r="B83" s="7" t="s">
+      <c r="C83" s="7" t="s">
         <v>357</v>
       </c>
-      <c r="C83" s="7" t="s">
+      <c r="D83" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="D83" s="7" t="s">
+      <c r="E83" s="8" t="s">
+        <v>484</v>
+      </c>
+      <c r="F83" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="G83" s="7" t="s">
         <v>359</v>
       </c>
-      <c r="E83" s="8" t="s">
+    </row>
+    <row r="84" spans="1:7" ht="409.6">
+      <c r="A84" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="D84" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="E84" s="8" t="s">
         <v>485</v>
       </c>
-      <c r="F83" s="7" t="s">
-        <v>361</v>
-      </c>
-      <c r="G83" s="7" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" ht="314">
-      <c r="A84" s="7" t="s">
-        <v>362</v>
-      </c>
-      <c r="B84" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="C84" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="D84" s="7" t="s">
+      <c r="F84" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="G84" s="7" t="s">
         <v>365</v>
-      </c>
-      <c r="E84" s="8" t="s">
-        <v>486</v>
-      </c>
-      <c r="F84" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="G84" s="7" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="370">
       <c r="A85" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="B85" s="7" t="s">
         <v>368</v>
       </c>
-      <c r="B85" s="7" t="s">
+      <c r="C85" s="7" t="s">
         <v>369</v>
       </c>
-      <c r="C85" s="7" t="s">
+      <c r="D85" s="7" t="s">
         <v>370</v>
-      </c>
-      <c r="D85" s="7" t="s">
-        <v>371</v>
       </c>
       <c r="E85" s="8"/>
       <c r="F85" s="7"/>
       <c r="G85" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="195">
       <c r="A86" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="B86" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="B86" s="7" t="s">
+      <c r="C86" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="C86" s="7" t="s">
+      <c r="D86" s="7" t="s">
         <v>375</v>
       </c>
-      <c r="D86" s="7" t="s">
-        <v>376</v>
-      </c>
       <c r="E86" s="8" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="F86" s="7"/>
       <c r="G86" s="7" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="105">
       <c r="A87" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="B87" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="C87" s="7" t="s">
         <v>378</v>
       </c>
-      <c r="B87" s="7" t="s">
-        <v>378</v>
-      </c>
-      <c r="C87" s="7" t="s">
+      <c r="D87" s="7" t="s">
         <v>379</v>
-      </c>
-      <c r="D87" s="7" t="s">
-        <v>380</v>
       </c>
       <c r="E87" s="8"/>
       <c r="F87" s="7"/>
@@ -4246,34 +4246,34 @@
     </row>
     <row r="88" spans="1:7" ht="105">
       <c r="A88" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="B88" s="7" t="s">
         <v>381</v>
       </c>
-      <c r="B88" s="7" t="s">
+      <c r="C88" s="7" t="s">
         <v>382</v>
       </c>
-      <c r="C88" s="7" t="s">
+      <c r="D88" s="7" t="s">
         <v>383</v>
       </c>
-      <c r="D88" s="7" t="s">
-        <v>384</v>
-      </c>
       <c r="E88" s="8" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F88" s="7"/>
       <c r="G88" s="7" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="409.6">
       <c r="A89" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="B89" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="B89" s="7" t="s">
+      <c r="C89" s="7" t="s">
         <v>387</v>
-      </c>
-      <c r="C89" s="7" t="s">
-        <v>388</v>
       </c>
       <c r="D89" s="7"/>
       <c r="E89" s="8"/>
@@ -4282,37 +4282,37 @@
     </row>
     <row r="90" spans="1:7" ht="409.6">
       <c r="A90" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="B90" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="C90" s="7" t="s">
         <v>389</v>
       </c>
-      <c r="B90" s="7" t="s">
-        <v>389</v>
-      </c>
-      <c r="C90" s="7" t="s">
+      <c r="D90" s="7" t="s">
         <v>390</v>
       </c>
-      <c r="D90" s="7" t="s">
-        <v>391</v>
-      </c>
       <c r="E90" s="8" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F90" s="7"/>
       <c r="G90" s="7" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="126">
       <c r="A91" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="C91" s="7" t="s">
         <v>393</v>
       </c>
-      <c r="B91" s="7" t="s">
-        <v>393</v>
-      </c>
-      <c r="C91" s="7" t="s">
+      <c r="D91" s="11" t="s">
         <v>394</v>
-      </c>
-      <c r="D91" s="11" t="s">
-        <v>395</v>
       </c>
       <c r="E91" s="8"/>
       <c r="F91" s="7"/>
@@ -4320,228 +4320,228 @@
     </row>
     <row r="92" spans="1:7" ht="150">
       <c r="A92" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="B92" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="C92" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="B92" s="7" t="s">
-        <v>396</v>
-      </c>
-      <c r="C92" s="7" t="s">
+      <c r="D92" s="7" t="s">
         <v>397</v>
-      </c>
-      <c r="D92" s="7" t="s">
-        <v>398</v>
       </c>
       <c r="E92" s="8"/>
       <c r="F92" s="7"/>
       <c r="G92" s="7" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="342">
       <c r="A93" s="7" t="s">
+        <v>399</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>399</v>
+      </c>
+      <c r="C93" s="7" t="s">
         <v>400</v>
-      </c>
-      <c r="B93" s="7" t="s">
-        <v>400</v>
-      </c>
-      <c r="C93" s="7" t="s">
-        <v>401</v>
       </c>
       <c r="D93" s="7"/>
       <c r="E93" s="8" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F93" s="7"/>
       <c r="G93" s="7" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="285">
       <c r="A94" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="B94" s="7" t="s">
         <v>403</v>
       </c>
-      <c r="B94" s="7" t="s">
+      <c r="C94" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="C94" s="7" t="s">
+      <c r="D94" s="7" t="s">
         <v>405</v>
       </c>
-      <c r="D94" s="7" t="s">
-        <v>406</v>
-      </c>
       <c r="E94" s="8" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="F94" s="7"/>
       <c r="G94" s="7" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="150">
       <c r="A95" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="B95" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="C95" s="7" t="s">
         <v>408</v>
       </c>
-      <c r="B95" s="7" t="s">
-        <v>408</v>
-      </c>
-      <c r="C95" s="7" t="s">
+      <c r="D95" s="7" t="s">
         <v>409</v>
-      </c>
-      <c r="D95" s="7" t="s">
-        <v>410</v>
       </c>
       <c r="E95" s="8"/>
       <c r="F95" s="7"/>
       <c r="G95" s="7" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="135">
       <c r="A96" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="B96" s="7" t="s">
         <v>412</v>
       </c>
-      <c r="B96" s="7" t="s">
+      <c r="C96" s="7" t="s">
         <v>413</v>
       </c>
-      <c r="C96" s="7" t="s">
+      <c r="D96" s="7" t="s">
         <v>414</v>
       </c>
-      <c r="D96" s="7" t="s">
-        <v>415</v>
-      </c>
       <c r="E96" s="8" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="F96" s="7"/>
       <c r="G96" s="7" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="97" spans="1:7" ht="180">
       <c r="A97" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="B97" s="7" t="s">
         <v>417</v>
       </c>
-      <c r="B97" s="7" t="s">
+      <c r="C97" s="7" t="s">
         <v>418</v>
       </c>
-      <c r="C97" s="7" t="s">
+      <c r="D97" s="7" t="s">
         <v>419</v>
-      </c>
-      <c r="D97" s="7" t="s">
-        <v>420</v>
       </c>
       <c r="E97" s="8"/>
       <c r="F97" s="7"/>
       <c r="G97" s="7" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="90">
       <c r="A98" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="B98" s="7" t="s">
         <v>422</v>
       </c>
-      <c r="B98" s="7" t="s">
+      <c r="C98" s="7" t="s">
         <v>423</v>
       </c>
-      <c r="C98" s="7" t="s">
+      <c r="D98" s="7" t="s">
         <v>424</v>
-      </c>
-      <c r="D98" s="7" t="s">
-        <v>425</v>
       </c>
       <c r="E98" s="8"/>
       <c r="F98" s="7"/>
       <c r="G98" s="7" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="409.6">
       <c r="A99" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="B99" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="C99" s="7" t="s">
         <v>427</v>
       </c>
-      <c r="B99" s="7" t="s">
-        <v>427</v>
-      </c>
-      <c r="C99" s="7" t="s">
+      <c r="D99" s="7" t="s">
         <v>428</v>
       </c>
-      <c r="D99" s="7" t="s">
+      <c r="E99" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="F99" s="7" t="s">
         <v>429</v>
-      </c>
-      <c r="E99" s="8" t="s">
-        <v>493</v>
-      </c>
-      <c r="F99" s="7" t="s">
-        <v>430</v>
       </c>
       <c r="G99" s="7"/>
     </row>
     <row r="100" spans="1:7" ht="409.6">
       <c r="A100" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="B100" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="C100" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="B100" s="7" t="s">
-        <v>431</v>
-      </c>
-      <c r="C100" s="7" t="s">
+      <c r="D100" s="7" t="s">
         <v>432</v>
       </c>
-      <c r="D100" s="7" t="s">
+      <c r="E100" s="8" t="s">
+        <v>493</v>
+      </c>
+      <c r="F100" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="G100" s="7" t="s">
         <v>433</v>
-      </c>
-      <c r="E100" s="8" t="s">
-        <v>494</v>
-      </c>
-      <c r="F100" s="7" t="s">
-        <v>435</v>
-      </c>
-      <c r="G100" s="7" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="101" spans="1:7" ht="356">
       <c r="A101" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="B101" s="7" t="s">
         <v>436</v>
       </c>
-      <c r="B101" s="7" t="s">
+      <c r="C101" s="7" t="s">
         <v>437</v>
-      </c>
-      <c r="C101" s="7" t="s">
-        <v>438</v>
       </c>
       <c r="D101" s="7"/>
       <c r="E101" s="8"/>
       <c r="F101" s="7"/>
       <c r="G101" s="7" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="135">
       <c r="A102" s="7" t="s">
+        <v>439</v>
+      </c>
+      <c r="B102" s="7" t="s">
+        <v>439</v>
+      </c>
+      <c r="C102" s="7" t="s">
         <v>440</v>
-      </c>
-      <c r="B102" s="7" t="s">
-        <v>440</v>
-      </c>
-      <c r="C102" s="7" t="s">
-        <v>441</v>
       </c>
       <c r="D102" s="7"/>
       <c r="E102" s="8"/>
       <c r="F102" s="7"/>
       <c r="G102" s="7" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="103" spans="1:7" ht="75">
       <c r="A103" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="B103" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="C103" s="7" t="s">
         <v>443</v>
-      </c>
-      <c r="B103" s="7" t="s">
-        <v>443</v>
-      </c>
-      <c r="C103" s="7" t="s">
-        <v>444</v>
       </c>
       <c r="D103" s="7"/>
       <c r="E103" s="8"/>
@@ -4550,32 +4550,32 @@
     </row>
     <row r="104" spans="1:7" ht="105">
       <c r="A104" s="7" t="s">
+        <v>444</v>
+      </c>
+      <c r="B104" s="7" t="s">
         <v>445</v>
       </c>
-      <c r="B104" s="7" t="s">
+      <c r="C104" s="7" t="s">
         <v>446</v>
       </c>
-      <c r="C104" s="7" t="s">
+      <c r="D104" s="7" t="s">
         <v>447</v>
-      </c>
-      <c r="D104" s="7" t="s">
-        <v>448</v>
       </c>
       <c r="E104" s="8"/>
       <c r="F104" s="7"/>
       <c r="G104" s="7" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="75">
       <c r="A105" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="B105" s="7" t="s">
         <v>450</v>
       </c>
-      <c r="B105" s="7" t="s">
+      <c r="C105" s="7" t="s">
         <v>451</v>
-      </c>
-      <c r="C105" s="7" t="s">
-        <v>452</v>
       </c>
       <c r="D105" s="7"/>
       <c r="E105" s="8"/>
@@ -4584,13 +4584,13 @@
     </row>
     <row r="106" spans="1:7" ht="75">
       <c r="A106" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="B106" s="7" t="s">
         <v>453</v>
       </c>
-      <c r="B106" s="7" t="s">
+      <c r="C106" s="7" t="s">
         <v>454</v>
-      </c>
-      <c r="C106" s="7" t="s">
-        <v>455</v>
       </c>
       <c r="D106" s="7"/>
       <c r="E106" s="8"/>
@@ -4599,13 +4599,13 @@
     </row>
     <row r="107" spans="1:7" ht="105">
       <c r="A107" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="B107" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="C107" s="7" t="s">
         <v>456</v>
-      </c>
-      <c r="B107" s="7" t="s">
-        <v>456</v>
-      </c>
-      <c r="C107" s="7" t="s">
-        <v>457</v>
       </c>
       <c r="D107" s="7"/>
       <c r="E107" s="8"/>
@@ -4614,34 +4614,34 @@
     </row>
     <row r="108" spans="1:7" ht="180">
       <c r="A108" s="7" t="s">
+        <v>457</v>
+      </c>
+      <c r="B108" s="7" t="s">
         <v>458</v>
       </c>
-      <c r="B108" s="7" t="s">
+      <c r="C108" s="7" t="s">
         <v>459</v>
       </c>
-      <c r="C108" s="7" t="s">
+      <c r="D108" s="7" t="s">
         <v>460</v>
       </c>
-      <c r="D108" s="7" t="s">
-        <v>461</v>
-      </c>
       <c r="E108" s="8" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F108" s="7"/>
       <c r="G108" s="7" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="109" spans="1:7" ht="30">
       <c r="A109" s="7" t="s">
+        <v>462</v>
+      </c>
+      <c r="B109" s="7" t="s">
+        <v>462</v>
+      </c>
+      <c r="C109" s="7" t="s">
         <v>463</v>
-      </c>
-      <c r="B109" s="7" t="s">
-        <v>463</v>
-      </c>
-      <c r="C109" s="7" t="s">
-        <v>464</v>
       </c>
       <c r="D109" s="7"/>
       <c r="E109" s="8"/>
@@ -4650,59 +4650,59 @@
     </row>
     <row r="110" spans="1:7" ht="75">
       <c r="A110" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="B110" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="C110" s="7" t="s">
         <v>465</v>
-      </c>
-      <c r="B110" s="7" t="s">
-        <v>465</v>
-      </c>
-      <c r="C110" s="7" t="s">
-        <v>466</v>
       </c>
       <c r="D110" s="7"/>
       <c r="E110" s="8" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="F110" s="7"/>
       <c r="G110" s="7" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="111" spans="1:7" ht="105">
       <c r="A111" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="B111" s="7" t="s">
         <v>468</v>
       </c>
-      <c r="B111" s="7" t="s">
+      <c r="C111" s="7" t="s">
         <v>469</v>
       </c>
-      <c r="C111" s="7" t="s">
+      <c r="D111" s="7" t="s">
         <v>470</v>
-      </c>
-      <c r="D111" s="7" t="s">
-        <v>471</v>
       </c>
       <c r="E111" s="8"/>
       <c r="F111" s="7"/>
       <c r="G111" s="7" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="112" spans="1:7" ht="105">
       <c r="A112" s="7" t="s">
+        <v>472</v>
+      </c>
+      <c r="B112" s="7" t="s">
         <v>473</v>
       </c>
-      <c r="B112" s="7" t="s">
+      <c r="C112" s="7" t="s">
         <v>474</v>
       </c>
-      <c r="C112" s="7" t="s">
+      <c r="D112" s="7" t="s">
         <v>475</v>
-      </c>
-      <c r="D112" s="7" t="s">
-        <v>476</v>
       </c>
       <c r="E112" s="8"/>
       <c r="F112" s="7"/>
       <c r="G112" s="7" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="113" spans="1:7" ht="16">

--- a/input/StatGuide.xlsx
+++ b/input/StatGuide.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10114"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10715"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yannic/Dropbox/Code/StatAssist_V2/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5E60F48-AB6A-494C-A0BD-3E3E9A026513}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E2B378B-ECA5-5746-962E-7D7A3FE9E87E}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12560" yWindow="8220" windowWidth="23540" windowHeight="13260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="460" windowWidth="33600" windowHeight="20540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="429">
   <si>
     <t>Full Term Names</t>
-  </si>
-  <si>
-    <t>Statistical term</t>
   </si>
   <si>
     <t>Images + Name</t>
@@ -105,9 +102,6 @@
     <t>A high AR means that the presence of a risk factor in one group compared to the absence of said risk factor in the other group leads to a high probability for a certain event.</t>
   </si>
   <si>
-    <t>Bar graph / chart</t>
-  </si>
-  <si>
     <t>Bar Graph</t>
   </si>
   <si>
@@ -124,9 +118,6 @@
   </si>
   <si>
     <t>Image_2_BG</t>
-  </si>
-  <si>
-    <t>Bell (-shaped) Curve/Gaussian distribution/ Normal distribution</t>
   </si>
   <si>
     <t>Normal Distribution</t>
@@ -145,18 +136,12 @@
     <t>Image_3_ND</t>
   </si>
   <si>
-    <t>Binary variable</t>
-  </si>
-  <si>
     <t>Binary Variable</t>
   </si>
   <si>
     <t>A variable can take on more than one unique value. When a variable is binary, it means that the variable can only take on one out of two possible values.</t>
   </si>
   <si>
-    <t>Bonferroni correction</t>
-  </si>
-  <si>
     <t>Bonferroni Correction</t>
   </si>
   <si>
@@ -169,9 +154,6 @@
     <t>When a Bonferroni correction is done, it means that the p-value should be lower when using multiple statistical post hoc tests. (the formula is P = α/k for k tests)</t>
   </si>
   <si>
-    <t>Box plot</t>
-  </si>
-  <si>
     <t>Box Plot</t>
   </si>
   <si>
@@ -190,9 +172,6 @@
     <t>Image_4_BP</t>
   </si>
   <si>
-    <t>Case report</t>
-  </si>
-  <si>
     <t>Case Report</t>
   </si>
   <si>
@@ -202,9 +181,6 @@
     <t>Case reports are often used to outline a curious/special case/occurrence.</t>
   </si>
   <si>
-    <t>Case-control study</t>
-  </si>
-  <si>
     <t>Case-control Study</t>
   </si>
   <si>
@@ -214,16 +190,10 @@
     <t>Case control studies are performed to see if an exposure is related to an outcome. This is always done retrospectively.</t>
   </si>
   <si>
-    <t>Categorical Variable (nominal/ordinal)</t>
-  </si>
-  <si>
     <t>Categorical Variable</t>
   </si>
   <si>
     <t>A variable can take on more than one unique value. When a variable is categorical, the value of a variable can only take on a finite number of values which are mutually exclusive. If the values are ordinal, there is also a particular order present.</t>
-  </si>
-  <si>
-    <t>Chi-Square test</t>
   </si>
   <si>
     <t>Chi-Square Test</t>
@@ -242,9 +212,6 @@
 When the p-value of the chi-square test is lower than the determined alpha level, there is significant relation between the two variables. When the p-value of the chi-square test is higher than the determined alpha level, there is not a significant relation between the two variables.</t>
   </si>
   <si>
-    <t>Clinical relevance</t>
-  </si>
-  <si>
     <t>Clinical Relevance</t>
   </si>
   <si>
@@ -257,9 +224,6 @@
     <t>Clinical relevance means whether a treatment has any real or noticeable effect on the daily lives of patients.</t>
   </si>
   <si>
-    <t>Cohort study</t>
-  </si>
-  <si>
     <t>Cohort Study</t>
   </si>
   <si>
@@ -269,9 +233,6 @@
     <t>Cohort studies are used to follow a segment of the population for a longer period of time to generate a large dataset of many variables.</t>
   </si>
   <si>
-    <t>Lin’s Concordance correlation coefficient</t>
-  </si>
-  <si>
     <t>Lin’s Concordance Correlation Coefficient</t>
   </si>
   <si>
@@ -281,9 +242,6 @@
     <t>When calculated, it is a value between 0 and 1. The higher the value, the more likely it can be reproduced by other scientists using the same methods. The height of the variable to be significant is still a matter of discussion among statisticians.</t>
   </si>
   <si>
-    <t>Confidence interval</t>
-  </si>
-  <si>
     <t>Confidence Interval</t>
   </si>
   <si>
@@ -302,9 +260,6 @@
     <t>A ‘disturbing’ variable which influences the relationship between an exposure and an outcome due to the fact that said distortion is independently associated with the exposure and outcome.</t>
   </si>
   <si>
-    <t>Contingency table</t>
-  </si>
-  <si>
     <t>Contingency Table</t>
   </si>
   <si>
@@ -314,16 +269,10 @@
     <t>Contingency tables might be used to display the frequencies of different categories / groups. By doing so, information between groups can easily be compared.</t>
   </si>
   <si>
-    <t>Continuous variable (non-discrete)</t>
-  </si>
-  <si>
     <t>Continuous Variable</t>
   </si>
   <si>
     <t>A variable can take on more than one unique value. When a variable is continuous, it means that the variable may take on any value within a specific range.</t>
-  </si>
-  <si>
-    <t>Control group</t>
   </si>
   <si>
     <t>Control Group</t>
@@ -349,9 +298,6 @@
 However, it is important to understand that correlation does not imply causation. Correlation between two variables does not mean that one variable causes a change in the other. (9)</t>
   </si>
   <si>
-    <t>Cross-sectional study</t>
-  </si>
-  <si>
     <t>Cross-Sectional Study</t>
   </si>
   <si>
@@ -359,9 +305,6 @@
   </si>
   <si>
     <t>Cross-sectional is used to work out the existence and magnitude of effects of one or more independent variables upon a dependent variable at a given point in time (11)</t>
-  </si>
-  <si>
-    <t>Cox proportional hazard</t>
   </si>
   <si>
     <t>Cox Proportional Hazard</t>
@@ -380,9 +323,6 @@
     <t>Image_5_CPH</t>
   </si>
   <si>
-    <t>Cut-off value</t>
-  </si>
-  <si>
     <t>Cut-Off Value</t>
   </si>
   <si>
@@ -401,18 +341,12 @@
     <t>It can be used to outline the characteristics of the population in the study.</t>
   </si>
   <si>
-    <t>Dependent variable</t>
-  </si>
-  <si>
     <t>Dependent Variable</t>
   </si>
   <si>
     <t>A variable can take on more than one unique value. When a variable is dependent, it depends on one or more independent variables to change. Other terms for dependent variable are outcome variable or response variable.</t>
   </si>
   <si>
-    <t>Descriptive statistics</t>
-  </si>
-  <si>
     <t>Descriptive Statistics</t>
   </si>
   <si>
@@ -422,18 +356,12 @@
     <t>Descriptive statistics is used to describe the basic features of a population. Providing simple summaries of your dataset.</t>
   </si>
   <si>
-    <t>Discrete variable</t>
-  </si>
-  <si>
     <t>Discrete Variable</t>
   </si>
   <si>
     <t>A variable can take on more than one unique value. When a variable is discrete, it means that the value of said variable is only permitted to take on certain values within a specific range.</t>
   </si>
   <si>
-    <t>Effect size</t>
-  </si>
-  <si>
     <t>Effect Size</t>
   </si>
   <si>
@@ -467,9 +395,6 @@
     <t>Exposure are all external factors and should be accounted for when conducting analysis, since exposure can influence the testing variable. If it is not accounted for, it can skew the result positively or negatively.</t>
   </si>
   <si>
-    <t>Factorial study</t>
-  </si>
-  <si>
     <t>Factorial Study</t>
   </si>
   <si>
@@ -479,9 +404,6 @@
     <t>A factorial study allows researchers to look at how multiple factors affect a single dependent variable. Factors are tested independently and dependently (in combination).</t>
   </si>
   <si>
-    <t>Fisher's exact test</t>
-  </si>
-  <si>
     <t>Fisher's Exact Test</t>
   </si>
   <si>
@@ -492,9 +414,6 @@
   </si>
   <si>
     <t>When the fisher’s exact test is significant, it means that there is a statistically significant relationship(s) of one categorical variable on the other categorical variable.</t>
-  </si>
-  <si>
-    <t>Fixed effects model</t>
   </si>
   <si>
     <t>Fixed Effects Model</t>
@@ -508,9 +427,6 @@
   <si>
     <t>FE analysis assumes there is a common treatment effect across all study settings. Differences between observed effect sizes are due to within-study variance (sampling error). However, because of this, FE models usually have higher variance than other statistical models.
 The summary treatment effect is a weighted average of study- or group-specific effect sizes.</t>
-  </si>
-  <si>
-    <t>Forest plot</t>
   </si>
   <si>
     <t>Forest Plot</t>
@@ -541,9 +457,6 @@
     <t>The amount of times a certain observation occurs within the data set.</t>
   </si>
   <si>
-    <t>Frequency table</t>
-  </si>
-  <si>
     <t>Frequency Table</t>
   </si>
   <si>
@@ -554,9 +467,6 @@
   </si>
   <si>
     <t>Frequency tables start by grouping the variables into certain categories. The second step is to observe how often the category is present in the dataset.</t>
-  </si>
-  <si>
-    <t>Cumulative distribution table</t>
   </si>
   <si>
     <t>Cumulative Distribution Table</t>
@@ -585,9 +495,6 @@
 Analytic (theoretical) generalization: comparison of the results of a case study to a previously developed theory. The results of a case study might strengthen or weaken this previously developed theory. The theory should be made clear at the beginning of the case study and is grounded in a research literature rather than specifically related to the case study.</t>
   </si>
   <si>
-    <t>Gold standard</t>
-  </si>
-  <si>
     <t>Gold Standard</t>
   </si>
   <si>
@@ -597,9 +504,6 @@
     <t>The gold standard is used because it is the best possible reference a researcher can relate to when testing a new drug/treatment and evaluating its performance.</t>
   </si>
   <si>
-    <t>Hazard ratio</t>
-  </si>
-  <si>
     <t>Hazard Ratio</t>
   </si>
   <si>
@@ -624,16 +528,10 @@
     <t>A histogram consist of a series of vertically standing bars. Each bar represents a defined range of values of a the variable. The height of each bar is proportional to the frequency of values for a specific range within the dataset.</t>
   </si>
   <si>
-    <t>Independent variable</t>
-  </si>
-  <si>
     <t>Independent Variable</t>
   </si>
   <si>
     <t>A variable can take on more than one unique value. When a variable is independent, it means that the value of the variable does not change when the value of other variables is changed. The independent variable is usually the variable which is controlled or changes within the experiment. Other terms are explanatory variable and covariable.</t>
-  </si>
-  <si>
-    <t>Inferential statistics</t>
   </si>
   <si>
     <t>Inferential Statistics</t>
@@ -647,9 +545,6 @@
   <si>
     <t>When performing inferential statistics, a P-value is used as a measure to determine the significance of the results.
 The P-value is a number between 0 and 1. A small P-value (e.g. &lt; 0.05) indicates strong evidence that there is significant difference between the different measured phenomena / groups. A large P-value (e.g. &gt;0.05) indicates no or weak evidence that there is significant difference between different measured phenomena / groups.</t>
-  </si>
-  <si>
-    <t>Interquartile range</t>
   </si>
   <si>
     <t>Interquartile Range</t>
@@ -666,9 +561,6 @@
 When the statistical power is equal one can solve this problem another way by increasing the number of observations of the dataset with a large variation.</t>
   </si>
   <si>
-    <t>Least square method</t>
-  </si>
-  <si>
     <t>Least Square Method</t>
   </si>
   <si>
@@ -688,9 +580,6 @@
     <t>Image_9_LSM</t>
   </si>
   <si>
-    <t>Linear regression (simple, multiple)</t>
-  </si>
-  <si>
     <t>Linear Regression</t>
   </si>
   <si>
@@ -710,9 +599,6 @@
     <t>Image_10_LINR</t>
   </si>
   <si>
-    <t>Logarithmic transformation</t>
-  </si>
-  <si>
     <t>Logarithmic Transformation</t>
   </si>
   <si>
@@ -729,9 +615,6 @@
   </si>
   <si>
     <t>Image_11_LT</t>
-  </si>
-  <si>
-    <t>Logistic regression (simple, multiple)</t>
   </si>
   <si>
     <t>Logistic Regression</t>
@@ -754,9 +637,6 @@
     <t>Image_12_LOGR</t>
   </si>
   <si>
-    <t>Mann-Whitney U test / Wilcoxon rank-sum test</t>
-  </si>
-  <si>
     <t>Mann-Whitney U Test</t>
   </si>
   <si>
@@ -794,9 +674,6 @@
     <t>The median is often used as a measure for central tendency.</t>
   </si>
   <si>
-    <t>Meta-analysis</t>
-  </si>
-  <si>
     <t>Meta-Analysis</t>
   </si>
   <si>
@@ -806,9 +683,6 @@
     <t>A meta-analysis is used to compose one big research on multiple other researches so that existing data from several population samples can be combined.</t>
   </si>
   <si>
-    <t>Mixed effect model</t>
-  </si>
-  <si>
     <t>Mixed Effect Model</t>
   </si>
   <si>
@@ -833,9 +707,6 @@
     <t>The mode is the most common category of a categorical variable.</t>
   </si>
   <si>
-    <t>Morbidity rate</t>
-  </si>
-  <si>
     <t>Morbidity Rate</t>
   </si>
   <si>
@@ -848,9 +719,6 @@
     <t>Morbidity is another term for illness, it simply means how often a disease is present. This does not include deaths due to disease.</t>
   </si>
   <si>
-    <t>Mortality rate</t>
-  </si>
-  <si>
     <t>Mortality Rate</t>
   </si>
   <si>
@@ -869,9 +737,6 @@
     <t>Multivariate means that something depends or relies on two or more variables.</t>
   </si>
   <si>
-    <t>Negative predictive value (NPV)</t>
-  </si>
-  <si>
     <t>Negative Predictive Value</t>
   </si>
   <si>
@@ -884,9 +749,6 @@
     <t>If the negative predictive value is high (&gt;90%), it means that the test was very accurate at telling that someone does not have a disease.</t>
   </si>
   <si>
-    <t>Null hypothesis (H0)</t>
-  </si>
-  <si>
     <t>Null Hypothesis</t>
   </si>
   <si>
@@ -894,9 +756,6 @@
   </si>
   <si>
     <t>The null hypothesis is always used in statistical testing and acts as a reference point or what the normal (or neutral) situation is of a population.</t>
-  </si>
-  <si>
-    <t>Number needed to harm (NNH)</t>
   </si>
   <si>
     <t>Number Needed to Harm</t>
@@ -912,9 +771,6 @@
 Misconception: number needed to harm says nothing about the severity of the side-effect. Therefore, no conclusion can be made on the safety of the drug.</t>
   </si>
   <si>
-    <t>Number needed to treat (NNT)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Number Needed to Treat </t>
   </si>
   <si>
@@ -926,9 +782,6 @@
   <si>
     <t>When the number needed to treat is very high, the drug is not very good at curing the disease. When the number needed to treat is very low, it means that the drug is very good at curing the disease.
 Misconception: the number needed to treat says nothing about how safe a drug is or what side-effects may occur.</t>
-  </si>
-  <si>
-    <t>Odds ratio (OR)</t>
   </si>
   <si>
     <t>Odds Ratio</t>
@@ -982,9 +835,6 @@
     <t>A parameter is any characteristic to define a research population. Parameters are used to describe the research population statistically.</t>
   </si>
   <si>
-    <t>Pearson correlation coefficient (r)</t>
-  </si>
-  <si>
     <t>Pearson Correlation Coefficient</t>
   </si>
   <si>
@@ -1009,9 +859,6 @@
     <t>When an event/case falls in a high percentile, it means that in the dataset, very few participants have a higher observation, and a lot of participants have a lower value.</t>
   </si>
   <si>
-    <t>Pie chart</t>
-  </si>
-  <si>
     <t>Pie Chart</t>
   </si>
   <si>
@@ -1024,9 +871,6 @@
     <t>When a slice in the pie chart is much bigger than the others, it means that the numerical proportion of that variable is much bigger than the others.</t>
   </si>
   <si>
-    <t>Poisson distribution</t>
-  </si>
-  <si>
     <t>Poisson Distribution</t>
   </si>
   <si>
@@ -1048,9 +892,6 @@
     <t>The population is a well defined set of subjects or objects A statistical population can be a group of existing objects. This group can potentially be of infinite size.</t>
   </si>
   <si>
-    <t>Positive predictive value (PPV)</t>
-  </si>
-  <si>
     <t>Positive Predictive Value</t>
   </si>
   <si>
@@ -1085,9 +926,6 @@
   </si>
   <si>
     <t>When the difference between quantiles is big, it means that there is a high variety in the data.</t>
-  </si>
-  <si>
-    <t>Random effects model</t>
   </si>
   <si>
     <t>Random Effects Model</t>
@@ -1101,9 +939,6 @@
   <si>
     <t>RE analysis assumes that the treatment effects across different studies or groups are uncorrelated. Differences between observed treatment effects are due to within- study (sampling error) and between- study variance. Because RE models take in mind between-study variance, they generally have lower variance than fixed effect (FE) models. However, RE models tend to be more biased than FE models.
 The summary treatment effect is an estimate of the average distribution of study- or group-specific effect sizes.</t>
-  </si>
-  <si>
-    <t>Randomized controlled trial</t>
   </si>
   <si>
     <t>Randomized Controlled Trial</t>
@@ -1130,9 +965,6 @@
     <t>When the range is big, it means that there is large variety in the dataset. If the range is small, it means that there is little variety in the dataset.</t>
   </si>
   <si>
-    <t>Receiving operating characteristic curve (ROC curve)</t>
-  </si>
-  <si>
     <t>Receiving Operating Characteristic Curve</t>
   </si>
   <si>
@@ -1146,9 +978,6 @@
   </si>
   <si>
     <t>On the x-axis you can see the False positive rate (1 - specificity) plotted against the True positive rate (sensitivity) on the y-axis. Each point on the ROC curve is a sensitivity/specificity pairing that corresponds to a decision threshold. Therefore, a test that is completely perfectly discriminatory (i.e. 100% specific and sensitive) will pass through the top left corner of this model. Therefore, the closer any ROC curve is to the top left corner, the better and more accurate the testing method will be. Which in this case would be Method 2.</t>
-  </si>
-  <si>
-    <t>Reference curve</t>
   </si>
   <si>
     <t>Reference Curve</t>
@@ -1165,9 +994,6 @@
   </si>
   <si>
     <t>On this growth chart, there are 3 curves drawn. What can be concluded from this is that chicken 1 grows slower than the average chicken (reference curve) and chicken 2 grows faster than the average chicken.</t>
-  </si>
-  <si>
-    <t>Relative risk (RR; Risk ratio)</t>
   </si>
   <si>
     <t>Relative Risk</t>
@@ -1186,9 +1012,6 @@
 Take in mind that the effect of the relative risk can be overstated if it is not presented in combination with the absolute risk.</t>
   </si>
   <si>
-    <t>Reliability (=precision)</t>
-  </si>
-  <si>
     <t>Reliability</t>
   </si>
   <si>
@@ -1211,9 +1034,6 @@
     <t>Typically, samples are used because an entire population is simply too large and too varied to perform a research on making research impractical or impossible. We use samples and perform statistical tests and make inferences about the entire population.</t>
   </si>
   <si>
-    <t>Sampling variation</t>
-  </si>
-  <si>
     <t>Sampling Variation</t>
   </si>
   <si>
@@ -1224,9 +1044,6 @@
   </si>
   <si>
     <t>When the sampling variation is very large it is considered less reliable.</t>
-  </si>
-  <si>
-    <t>Scales (nominal, ordinal, interval, ratio)</t>
   </si>
   <si>
     <t>Scales</t>
@@ -1261,9 +1078,6 @@
     <t>Screening tests are used to identify a subset of the population who should have additional testing to determine the presence or absence of a disease. (29) These tests are not diagnostic. The goal is early detection of a disease so that lifestyle changes, surveillance or treatment may be initiated to reduce the risk or prevent disease.</t>
   </si>
   <si>
-    <t>Sensitivity</t>
-  </si>
-  <si>
     <t>Sensitivity (also called the true positive rate) measures the proportion of actual positives that are correctly identified as such (e.g., the percentage of diseased people who are correctly identified as having the condition). (30)</t>
   </si>
   <si>
@@ -1283,15 +1097,6 @@
 When the distribution of a dataset is negatively skewed, it means that there are more available values below the most frequent value of the distribution. Also the median and mean lie in this case below the most frequent value.</t>
   </si>
   <si>
-    <t>Spearman correlation coefficient</t>
-  </si>
-  <si>
-    <t>Spearman Correlation Coefficient</t>
-  </si>
-  <si>
-    <t>The Spearman correlation coefficient is a measure for how well a linear equation describes the relation between the ranks of two variables. It is different from the Pearson correlation test by that it uses rank numbers instead of the actual numbers. Pearson can be used if two continuous variables have reasonably normal distributions. If not, we prefer Spearman’s coeffciicent.</t>
-  </si>
-  <si>
     <t>The Spearman correlation test is used to test whether 2 variables have a positive or a negative relationship with each other. Next to positive / negative, it also gives an indication on how strong the relationship between the ranks in fact is.</t>
   </si>
   <si>
@@ -1310,9 +1115,6 @@
     <t>When the specificity is high, it means that a low amount of people who are actually not ill are tested positive on that test. When the specificity is low it means that a lot of people who are not ill are missed.</t>
   </si>
   <si>
-    <t>Standard deviation</t>
-  </si>
-  <si>
     <t>Standard Deviation</t>
   </si>
   <si>
@@ -1325,9 +1127,6 @@
     <t>If the standard deviation is large compared to the mean, this means that there is a high variety in the dataset and is therefore less reliable.</t>
   </si>
   <si>
-    <t>Standard error of the mean</t>
-  </si>
-  <si>
     <t>Standard Error of the Mean</t>
   </si>
   <si>
@@ -1338,9 +1137,6 @@
   </si>
   <si>
     <t>When the standard error of the mean is large, it means that the sample mean is an uncertain estimate for the mean of the entire population. When the standard error is small, it means the sample mean is a good estimate for the mean of the population.</t>
-  </si>
-  <si>
-    <t>Statistical power</t>
   </si>
   <si>
     <t>Statistical Power</t>
@@ -1381,9 +1177,6 @@
   </si>
   <si>
     <t>The graph above shows the Time on the x-axis (days, months, years etc.). The Y-axis is the survival rate of the studied population in percentages (%). The graphs are differentiated by the treated group and the untreated group. Measurements occur at specified time points (based on study design) where the survival of each group is measured. Some of this data might be censored. (i.e. the patient dropped out before the end of the study). Be aware of this incomplete information as it can skew the figure either positively (i.e. more survival than is actually true) or negatively (i.e. less survival than is actually true).</t>
-  </si>
-  <si>
-    <t>T-test (one-sample, 2-sample, unpaired, paired)</t>
   </si>
   <si>
     <t>T-Test</t>
@@ -1413,9 +1206,6 @@
     <t>The subjects that receive the to be evaluated treatment in an experiment. This group receives a treatment which is different from the standard treatment.</t>
   </si>
   <si>
-    <t>Tukey post hoc test</t>
-  </si>
-  <si>
     <t>Tukey Post Hoc Test</t>
   </si>
   <si>
@@ -1428,16 +1218,10 @@
     <t>When the Tukey post hoc test is significant for 2 particular groups, it means that they are statistically different from each other.</t>
   </si>
   <si>
-    <t>Type 1 error</t>
-  </si>
-  <si>
     <t>Type 1 Error</t>
   </si>
   <si>
     <t>Concluding that there is significant difference between the proposed test / treatment and the standard test / treatment when there actually is no real difference.</t>
-  </si>
-  <si>
-    <t>Type 2 error</t>
   </si>
   <si>
     <t>Type 2 Error</t>
@@ -1453,9 +1237,6 @@
 2. Unit of measurement: the type of measurement in which a certain magnitude is expressed</t>
   </si>
   <si>
-    <t>Validity (=accuracy)</t>
-  </si>
-  <si>
     <t>Validity</t>
   </si>
   <si>
@@ -1484,9 +1265,6 @@
     <t>When the variance in a dataset is very high, it generally is less reliable than a dataset which contains less variety.</t>
   </si>
   <si>
-    <t>Wilcoxon signed-rank test</t>
-  </si>
-  <si>
     <t>Wilcoxon Signed-Rank Test</t>
   </si>
   <si>
@@ -1499,9 +1277,6 @@
     <t>When the Wilcoxon test is statistically significant (p=&lt;0,05), it means that 2 groups are statistically different from each other.</t>
   </si>
   <si>
-    <t>Z-score</t>
-  </si>
-  <si>
     <t>Z-Score</t>
   </si>
   <si>
@@ -1577,14 +1352,29 @@
     <t>What does it mean?</t>
   </si>
   <si>
-    <t>p</t>
+    <t>The Spearman's rank correlation coefficient is a measure for how well a linear equation describes the relation between the ranks of two variables. It is different from the Pearson correlation test by that it uses rank numbers instead of the actual numbers. Pearson can be used if two continuous variables have reasonably normal distributions. If not, we prefer Spearman’s coeffciicent.</t>
+  </si>
+  <si>
+    <t>Spearman's rank correlation coefficients</t>
+  </si>
+  <si>
+    <t>Sensitivity for</t>
+  </si>
+  <si>
+    <t>proxy</t>
+  </si>
+  <si>
+    <t>Mean sd</t>
+  </si>
+  <si>
+    <t>exhibits Specificity</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2034,7 +1824,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:Y751"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.83203125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.83203125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="14.83203125" style="1"/>
     <col min="3" max="3" width="32.6640625" style="1" customWidth="1"/>
@@ -2045,27 +1835,27 @@
     <col min="8" max="16384" width="14.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="8" customFormat="1" ht="28">
+    <row r="1" spans="1:25" s="8" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
+        <v>426</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>402</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>421</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
-        <v>477</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>496</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>2</v>
-      </c>
       <c r="F1" s="13" t="s">
-        <v>478</v>
+        <v>403</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>497</v>
+        <v>422</v>
       </c>
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
@@ -2086,63 +1876,63 @@
       <c r="X1" s="6"/>
       <c r="Y1" s="6"/>
     </row>
-    <row r="2" spans="1:25" ht="150">
+    <row r="2" spans="1:25" ht="150" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="7" t="s">
+      <c r="D2" s="7" t="s">
         <v>4</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>5</v>
       </c>
       <c r="E2" s="8"/>
       <c r="F2" s="7"/>
       <c r="G2" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" ht="409.6" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:25" ht="409.6">
-      <c r="A3" s="7" t="s">
+      <c r="B3" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>9</v>
-      </c>
       <c r="E3" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F3" s="9"/>
       <c r="G3" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" ht="195">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" ht="195" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="7" t="s">
+      <c r="D4" s="7" t="s">
         <v>13</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>14</v>
       </c>
       <c r="E4" s="8"/>
       <c r="F4" s="7"/>
       <c r="G4" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
@@ -2163,42 +1953,42 @@
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
     </row>
-    <row r="5" spans="1:25" ht="225">
+    <row r="5" spans="1:25" ht="225" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="7" t="s">
         <v>17</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>18</v>
       </c>
       <c r="E5" s="8"/>
       <c r="F5" s="7"/>
       <c r="G5" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" ht="135" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" spans="1:25" ht="135">
-      <c r="A6" s="7" t="s">
+      <c r="B6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="7" t="s">
+      <c r="D6" s="7" t="s">
         <v>21</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>22</v>
       </c>
       <c r="E6" s="8"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
@@ -2219,27 +2009,27 @@
       <c r="X6" s="4"/>
       <c r="Y6" s="4"/>
     </row>
-    <row r="7" spans="1:25" ht="409.6">
+    <row r="7" spans="1:25" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="D7" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="E7" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>26</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>28</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
@@ -2260,25 +2050,25 @@
       <c r="X7" s="4"/>
       <c r="Y7" s="4"/>
     </row>
-    <row r="8" spans="1:25" ht="409.6">
+    <row r="8" spans="1:25" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="7" t="s">
+      <c r="E8" s="8" t="s">
         <v>33</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>36</v>
       </c>
       <c r="F8" s="9"/>
       <c r="G8" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
@@ -2299,15 +2089,15 @@
       <c r="X8" s="4"/>
       <c r="Y8" s="4"/>
     </row>
-    <row r="9" spans="1:25" ht="75">
+    <row r="9" spans="1:25" ht="75" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="8"/>
@@ -2332,23 +2122,23 @@
       <c r="X9" s="4"/>
       <c r="Y9" s="4"/>
     </row>
-    <row r="10" spans="1:25" ht="135">
+    <row r="10" spans="1:25" ht="135" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E10" s="8"/>
       <c r="F10" s="7"/>
       <c r="G10" s="7" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
@@ -2369,27 +2159,27 @@
       <c r="X10" s="4"/>
       <c r="Y10" s="4"/>
     </row>
-    <row r="11" spans="1:25" ht="409.6">
+    <row r="11" spans="1:25" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>51</v>
-      </c>
       <c r="F11" s="9" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
@@ -2410,18 +2200,18 @@
       <c r="X11" s="4"/>
       <c r="Y11" s="4"/>
     </row>
-    <row r="12" spans="1:25" ht="30">
+    <row r="12" spans="1:25" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E12" s="8"/>
       <c r="F12" s="7"/>
@@ -2445,18 +2235,18 @@
       <c r="X12" s="4"/>
       <c r="Y12" s="4"/>
     </row>
-    <row r="13" spans="1:25" ht="90">
+    <row r="13" spans="1:25" ht="90" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="E13" s="8"/>
       <c r="F13" s="7"/>
@@ -2480,15 +2270,15 @@
       <c r="X13" s="4"/>
       <c r="Y13" s="4"/>
     </row>
-    <row r="14" spans="1:25" ht="105">
+    <row r="14" spans="1:25" ht="105" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="D14" s="9"/>
       <c r="E14" s="8"/>
@@ -2513,23 +2303,23 @@
       <c r="X14" s="4"/>
       <c r="Y14" s="4"/>
     </row>
-    <row r="15" spans="1:25" ht="398">
+    <row r="15" spans="1:25" ht="398" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="E15" s="8"/>
       <c r="F15" s="7"/>
       <c r="G15" s="7" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
@@ -2550,23 +2340,23 @@
       <c r="X15" s="4"/>
       <c r="Y15" s="4"/>
     </row>
-    <row r="16" spans="1:25" ht="90">
+    <row r="16" spans="1:25" ht="90" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="E16" s="8"/>
       <c r="F16" s="7"/>
       <c r="G16" s="7" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
@@ -2587,38 +2377,38 @@
       <c r="X16" s="4"/>
       <c r="Y16" s="4"/>
     </row>
-    <row r="17" spans="1:25" ht="135">
+    <row r="17" spans="1:25" ht="135" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="E17" s="8"/>
       <c r="F17" s="7"/>
       <c r="G17" s="9"/>
     </row>
-    <row r="18" spans="1:25" ht="165">
+    <row r="18" spans="1:25" ht="165" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="D18" s="9"/>
       <c r="E18" s="8"/>
       <c r="F18" s="9"/>
       <c r="G18" s="7" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
@@ -2639,23 +2429,23 @@
       <c r="X18" s="4"/>
       <c r="Y18" s="4"/>
     </row>
-    <row r="19" spans="1:25" ht="180">
+    <row r="19" spans="1:25" ht="180" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="E19" s="8"/>
       <c r="F19" s="7"/>
       <c r="G19" s="7" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
@@ -2676,47 +2466,47 @@
       <c r="X19" s="4"/>
       <c r="Y19" s="4"/>
     </row>
-    <row r="20" spans="1:25" ht="90">
+    <row r="20" spans="1:25" ht="90" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="D20" s="9"/>
       <c r="E20" s="8"/>
       <c r="F20" s="7"/>
       <c r="G20" s="9"/>
     </row>
-    <row r="21" spans="1:25" ht="75">
+    <row r="21" spans="1:25" ht="75" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="E21" s="8"/>
       <c r="F21" s="7"/>
       <c r="G21" s="9"/>
     </row>
-    <row r="22" spans="1:25" ht="75">
+    <row r="22" spans="1:25" ht="75" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="D22" s="9"/>
       <c r="E22" s="8"/>
@@ -2741,18 +2531,18 @@
       <c r="X22" s="4"/>
       <c r="Y22" s="4"/>
     </row>
-    <row r="23" spans="1:25" ht="75">
+    <row r="23" spans="1:25" ht="75" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="E23" s="8"/>
       <c r="F23" s="7"/>
@@ -2776,23 +2566,23 @@
       <c r="X23" s="4"/>
       <c r="Y23" s="4"/>
     </row>
-    <row r="24" spans="1:25" ht="398">
+    <row r="24" spans="1:25" ht="398" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="E24" s="8"/>
       <c r="F24" s="7"/>
       <c r="G24" s="7" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
@@ -2813,18 +2603,18 @@
       <c r="X24" s="4"/>
       <c r="Y24" s="4"/>
     </row>
-    <row r="25" spans="1:25" ht="75">
+    <row r="25" spans="1:25" ht="75" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="E25" s="8"/>
       <c r="F25" s="7"/>
@@ -2848,25 +2638,25 @@
       <c r="X25" s="4"/>
       <c r="Y25" s="4"/>
     </row>
-    <row r="26" spans="1:25" ht="210">
+    <row r="26" spans="1:25" ht="210" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="F26" s="9"/>
       <c r="G26" s="7" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="H26" s="4"/>
       <c r="I26" s="4"/>
@@ -2887,18 +2677,18 @@
       <c r="X26" s="4"/>
       <c r="Y26" s="4"/>
     </row>
-    <row r="27" spans="1:25" ht="75">
+    <row r="27" spans="1:25" ht="75" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="E27" s="8"/>
       <c r="F27" s="7"/>
@@ -2922,18 +2712,18 @@
       <c r="X27" s="4"/>
       <c r="Y27" s="4"/>
     </row>
-    <row r="28" spans="1:25" ht="75">
+    <row r="28" spans="1:25" ht="75" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="E28" s="8"/>
       <c r="F28" s="7"/>
@@ -2957,15 +2747,15 @@
       <c r="X28" s="4"/>
       <c r="Y28" s="4"/>
     </row>
-    <row r="29" spans="1:25" ht="105">
+    <row r="29" spans="1:25" ht="105" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="D29" s="9"/>
       <c r="E29" s="8"/>
@@ -2990,18 +2780,18 @@
       <c r="X29" s="4"/>
       <c r="Y29" s="4"/>
     </row>
-    <row r="30" spans="1:25" ht="75">
+    <row r="30" spans="1:25" ht="75" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="E30" s="8"/>
       <c r="F30" s="7"/>
@@ -3025,15 +2815,15 @@
       <c r="X30" s="4"/>
       <c r="Y30" s="4"/>
     </row>
-    <row r="31" spans="1:25" ht="90">
+    <row r="31" spans="1:25" ht="90" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="D31" s="9"/>
       <c r="E31" s="8"/>
@@ -3058,23 +2848,23 @@
       <c r="X31" s="4"/>
       <c r="Y31" s="4"/>
     </row>
-    <row r="32" spans="1:25" ht="105">
+    <row r="32" spans="1:25" ht="105" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="E32" s="8"/>
       <c r="F32" s="7"/>
       <c r="G32" s="7" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
@@ -3095,15 +2885,15 @@
       <c r="X32" s="4"/>
       <c r="Y32" s="4"/>
     </row>
-    <row r="33" spans="1:25" ht="15">
+    <row r="33" spans="1:25" ht="15" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="D33" s="9"/>
       <c r="E33" s="8"/>
@@ -3128,15 +2918,15 @@
       <c r="X33" s="4"/>
       <c r="Y33" s="4"/>
     </row>
-    <row r="34" spans="1:25" ht="60">
+    <row r="34" spans="1:25" ht="60" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="D34" s="9"/>
       <c r="E34" s="8"/>
@@ -3161,21 +2951,21 @@
       <c r="X34" s="4"/>
       <c r="Y34" s="4"/>
     </row>
-    <row r="35" spans="1:25" ht="150">
+    <row r="35" spans="1:25" ht="150" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="D35" s="9"/>
       <c r="E35" s="8"/>
       <c r="F35" s="7"/>
       <c r="G35" s="7" t="s">
-        <v>141</v>
+        <v>117</v>
       </c>
       <c r="H35" s="4"/>
       <c r="I35" s="4"/>
@@ -3196,18 +2986,18 @@
       <c r="X35" s="4"/>
       <c r="Y35" s="4"/>
     </row>
-    <row r="36" spans="1:25" ht="75">
+    <row r="36" spans="1:25" ht="75" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>144</v>
+        <v>119</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="E36" s="8"/>
       <c r="F36" s="7"/>
@@ -3231,23 +3021,23 @@
       <c r="X36" s="4"/>
       <c r="Y36" s="4"/>
     </row>
-    <row r="37" spans="1:25" ht="120">
+    <row r="37" spans="1:25" ht="120" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>147</v>
+        <v>121</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>148</v>
+        <v>122</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>149</v>
+        <v>123</v>
       </c>
       <c r="E37" s="8"/>
       <c r="F37" s="7"/>
       <c r="G37" s="7" t="s">
-        <v>150</v>
+        <v>124</v>
       </c>
       <c r="H37" s="4"/>
       <c r="I37" s="4"/>
@@ -3268,23 +3058,23 @@
       <c r="X37" s="4"/>
       <c r="Y37" s="4"/>
     </row>
-    <row r="38" spans="1:25" ht="285">
+    <row r="38" spans="1:25" ht="285" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>151</v>
+        <v>125</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>152</v>
+        <v>125</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>154</v>
+        <v>127</v>
       </c>
       <c r="E38" s="8"/>
       <c r="F38" s="7"/>
       <c r="G38" s="7" t="s">
-        <v>155</v>
+        <v>128</v>
       </c>
       <c r="H38" s="4"/>
       <c r="I38" s="4"/>
@@ -3305,1407 +3095,1407 @@
       <c r="X38" s="4"/>
       <c r="Y38" s="4"/>
     </row>
-    <row r="39" spans="1:25" ht="409.6">
+    <row r="39" spans="1:25" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>156</v>
+        <v>129</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>157</v>
+        <v>129</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>158</v>
+        <v>130</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>159</v>
+        <v>131</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>161</v>
+        <v>133</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="40" spans="1:25" ht="86.25" customHeight="1">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" ht="86.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>164</v>
+        <v>136</v>
       </c>
       <c r="D40" s="7"/>
       <c r="E40" s="8"/>
       <c r="F40" s="7"/>
       <c r="G40" s="7"/>
     </row>
-    <row r="41" spans="1:25" ht="105">
+    <row r="41" spans="1:25" ht="105" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>167</v>
+        <v>138</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>168</v>
+        <v>139</v>
       </c>
       <c r="E41" s="8"/>
       <c r="F41" s="7"/>
       <c r="G41" s="7" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="42" spans="1:25" ht="180">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" ht="180" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>170</v>
+        <v>141</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>171</v>
+        <v>141</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>172</v>
+        <v>142</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>173</v>
+        <v>143</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>479</v>
+        <v>404</v>
       </c>
       <c r="F42" s="7"/>
       <c r="G42" s="7" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="43" spans="1:25" ht="409.6">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>175</v>
+        <v>145</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>175</v>
+        <v>145</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>176</v>
+        <v>146</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>177</v>
+        <v>147</v>
       </c>
       <c r="E43" s="8"/>
       <c r="F43" s="7"/>
       <c r="G43" s="7" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="44" spans="1:25" ht="105">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" ht="105" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>181</v>
+        <v>150</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="E44" s="8"/>
       <c r="F44" s="7"/>
       <c r="G44" s="7"/>
     </row>
-    <row r="45" spans="1:25" ht="240">
+    <row r="45" spans="1:25" ht="240" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>183</v>
+        <v>152</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>184</v>
+        <v>152</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>185</v>
+        <v>153</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>186</v>
+        <v>154</v>
       </c>
       <c r="E45" s="8"/>
       <c r="F45" s="7"/>
       <c r="G45" s="7" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="46" spans="1:25" ht="165">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25" ht="165" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>188</v>
+        <v>156</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>188</v>
+        <v>156</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>189</v>
+        <v>157</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>190</v>
+        <v>158</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>480</v>
+        <v>405</v>
       </c>
       <c r="F46" s="7"/>
       <c r="G46" s="7" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="47" spans="1:25" ht="150">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25" ht="150" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>193</v>
+        <v>160</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>194</v>
+        <v>161</v>
       </c>
       <c r="D47" s="7"/>
       <c r="E47" s="8"/>
       <c r="F47" s="7"/>
       <c r="G47" s="7"/>
     </row>
-    <row r="48" spans="1:25" ht="328">
+    <row r="48" spans="1:25" ht="328" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>195</v>
+        <v>162</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>196</v>
+        <v>162</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>197</v>
+        <v>163</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>198</v>
+        <v>164</v>
       </c>
       <c r="E48" s="8"/>
       <c r="F48" s="7"/>
       <c r="G48" s="7" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="328">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="328" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>200</v>
+        <v>166</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>201</v>
+        <v>166</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>202</v>
+        <v>167</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>203</v>
+        <v>168</v>
       </c>
       <c r="E49" s="8"/>
       <c r="F49" s="7"/>
       <c r="G49" s="7" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="409.6">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>205</v>
+        <v>170</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>206</v>
+        <v>170</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>207</v>
+        <v>171</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>208</v>
+        <v>172</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>211</v>
+        <v>175</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="409.6">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>212</v>
+        <v>176</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>213</v>
+        <v>176</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>214</v>
+        <v>177</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>215</v>
+        <v>178</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>218</v>
+        <v>181</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>217</v>
+        <v>180</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="409.6">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>219</v>
+        <v>182</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>220</v>
+        <v>182</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>221</v>
+        <v>183</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>222</v>
+        <v>184</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>225</v>
+        <v>187</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>224</v>
+        <v>186</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="409.6">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>226</v>
+        <v>188</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>227</v>
+        <v>188</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>228</v>
+        <v>189</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>229</v>
+        <v>190</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>232</v>
+        <v>193</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>231</v>
+        <v>192</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="135">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="135" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>233</v>
+        <v>194</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>234</v>
+        <v>194</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>235</v>
+        <v>195</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="E54" s="8"/>
       <c r="F54" s="7"/>
       <c r="G54" s="7" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="150">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="150" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>238</v>
+        <v>198</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>238</v>
+        <v>427</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>239</v>
+        <v>199</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="E55" s="8"/>
       <c r="F55" s="7"/>
       <c r="G55" s="7" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="120">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="120" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>242</v>
+        <v>202</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>242</v>
+        <v>202</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>243</v>
+        <v>203</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="E56" s="8"/>
       <c r="F56" s="7"/>
       <c r="G56" s="7" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="75">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>246</v>
+        <v>206</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>247</v>
+        <v>206</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>248</v>
+        <v>207</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>249</v>
+        <v>208</v>
       </c>
       <c r="E57" s="8"/>
       <c r="F57" s="7"/>
       <c r="G57" s="7"/>
     </row>
-    <row r="58" spans="1:7" ht="165">
+    <row r="58" spans="1:7" ht="165" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
-        <v>250</v>
+        <v>209</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>251</v>
+        <v>209</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>252</v>
+        <v>210</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>253</v>
+        <v>211</v>
       </c>
       <c r="E58" s="8"/>
       <c r="F58" s="7"/>
       <c r="G58" s="7" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="90">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>255</v>
+        <v>213</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>255</v>
+        <v>213</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>256</v>
+        <v>214</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>257</v>
+        <v>215</v>
       </c>
       <c r="E59" s="8"/>
       <c r="F59" s="7"/>
       <c r="G59" s="7" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="90">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>259</v>
+        <v>217</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>260</v>
+        <v>217</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>261</v>
+        <v>218</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>262</v>
+        <v>219</v>
       </c>
       <c r="E60" s="8"/>
       <c r="F60" s="7"/>
       <c r="G60" s="7" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="105">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>264</v>
+        <v>221</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>265</v>
+        <v>221</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>266</v>
+        <v>222</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>267</v>
+        <v>223</v>
       </c>
       <c r="E61" s="8"/>
       <c r="F61" s="7"/>
       <c r="G61" s="7" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="45">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
-        <v>269</v>
+        <v>225</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>269</v>
+        <v>225</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>270</v>
+        <v>226</v>
       </c>
       <c r="D62" s="7"/>
       <c r="E62" s="8"/>
       <c r="F62" s="7"/>
       <c r="G62" s="7"/>
     </row>
-    <row r="63" spans="1:7" ht="105">
+    <row r="63" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>271</v>
+        <v>227</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>272</v>
+        <v>227</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>273</v>
+        <v>228</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>274</v>
+        <v>229</v>
       </c>
       <c r="E63" s="8"/>
       <c r="F63" s="7"/>
       <c r="G63" s="7" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="75">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
-        <v>276</v>
+        <v>231</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>277</v>
+        <v>231</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>278</v>
+        <v>232</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>279</v>
+        <v>233</v>
       </c>
       <c r="E64" s="8"/>
       <c r="F64" s="7"/>
       <c r="G64" s="7"/>
     </row>
-    <row r="65" spans="1:7" ht="300">
+    <row r="65" spans="1:7" ht="300" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>280</v>
+        <v>234</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>281</v>
+        <v>234</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>282</v>
+        <v>235</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>283</v>
+        <v>236</v>
       </c>
       <c r="E65" s="8"/>
       <c r="F65" s="7"/>
       <c r="G65" s="7" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="240">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="240" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
-        <v>285</v>
+        <v>238</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>286</v>
+        <v>238</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>287</v>
+        <v>239</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>288</v>
+        <v>240</v>
       </c>
       <c r="E66" s="8"/>
       <c r="F66" s="7"/>
       <c r="G66" s="7" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="150">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="150" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>290</v>
+        <v>242</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>292</v>
+        <v>243</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>293</v>
+        <v>244</v>
       </c>
       <c r="E67" s="8"/>
       <c r="F67" s="7"/>
       <c r="G67" s="7" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="90">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
-        <v>295</v>
+        <v>246</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>295</v>
+        <v>246</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>296</v>
+        <v>247</v>
       </c>
       <c r="D68" s="7"/>
       <c r="E68" s="8"/>
       <c r="F68" s="7"/>
       <c r="G68" s="7" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" ht="409.6">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>298</v>
+        <v>249</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>298</v>
+        <v>249</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>299</v>
+        <v>250</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>300</v>
+        <v>251</v>
       </c>
       <c r="E69" s="8"/>
       <c r="F69" s="7"/>
       <c r="G69" s="7" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" ht="210">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="210" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
-        <v>498</v>
+        <v>253</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>302</v>
+        <v>253</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>303</v>
+        <v>254</v>
       </c>
       <c r="D70" s="7"/>
       <c r="E70" s="8"/>
       <c r="F70" s="7"/>
       <c r="G70" s="7" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="60">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>305</v>
+        <v>256</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>305</v>
+        <v>256</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>306</v>
+        <v>257</v>
       </c>
       <c r="D71" s="7"/>
       <c r="E71" s="8"/>
       <c r="F71" s="10"/>
       <c r="G71" s="7"/>
     </row>
-    <row r="72" spans="1:7" ht="285">
+    <row r="72" spans="1:7" ht="285" x14ac:dyDescent="0.25">
       <c r="A72" s="7" t="s">
-        <v>307</v>
+        <v>258</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>308</v>
+        <v>258</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>309</v>
+        <v>259</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>310</v>
+        <v>260</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>481</v>
+        <v>406</v>
       </c>
       <c r="F72" s="7"/>
       <c r="G72" s="7" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" ht="120">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="120" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>312</v>
+        <v>262</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>312</v>
+        <v>262</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>313</v>
+        <v>263</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>314</v>
+        <v>264</v>
       </c>
       <c r="E73" s="8"/>
       <c r="F73" s="7"/>
       <c r="G73" s="7" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" ht="105">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
-        <v>316</v>
+        <v>266</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>317</v>
+        <v>266</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>318</v>
+        <v>267</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>319</v>
+        <v>268</v>
       </c>
       <c r="E74" s="8" t="s">
-        <v>482</v>
+        <v>407</v>
       </c>
       <c r="F74" s="7"/>
       <c r="G74" s="7" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" ht="409.6">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>321</v>
+        <v>270</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>322</v>
+        <v>270</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>323</v>
+        <v>271</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>324</v>
+        <v>272</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>483</v>
+        <v>408</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>326</v>
+        <v>274</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="75">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A76" s="7" t="s">
-        <v>327</v>
+        <v>275</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>327</v>
+        <v>275</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>328</v>
+        <v>276</v>
       </c>
       <c r="D76" s="7"/>
       <c r="E76" s="8"/>
       <c r="F76" s="7"/>
       <c r="G76" s="7"/>
     </row>
-    <row r="77" spans="1:7" ht="90">
+    <row r="77" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>329</v>
+        <v>277</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>330</v>
+        <v>277</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>331</v>
+        <v>278</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>332</v>
+        <v>279</v>
       </c>
       <c r="E77" s="8"/>
       <c r="F77" s="7"/>
       <c r="G77" s="7" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" ht="120">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="120" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
-        <v>334</v>
+        <v>281</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>334</v>
+        <v>281</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>335</v>
+        <v>282</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>336</v>
+        <v>283</v>
       </c>
       <c r="E78" s="8"/>
       <c r="F78" s="7"/>
       <c r="G78" s="7" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="75">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>338</v>
+        <v>285</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>338</v>
+        <v>285</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>339</v>
+        <v>286</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>340</v>
+        <v>287</v>
       </c>
       <c r="E79" s="8"/>
       <c r="F79" s="7"/>
       <c r="G79" s="7" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="384">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="384" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
-        <v>342</v>
+        <v>289</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>343</v>
+        <v>289</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>344</v>
+        <v>290</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>345</v>
+        <v>291</v>
       </c>
       <c r="E80" s="8"/>
       <c r="F80" s="7"/>
       <c r="G80" s="7" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" ht="342">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="342" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>347</v>
+        <v>293</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>348</v>
+        <v>293</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>349</v>
+        <v>294</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>350</v>
+        <v>295</v>
       </c>
       <c r="E81" s="8"/>
       <c r="F81" s="7"/>
       <c r="G81" s="7"/>
     </row>
-    <row r="82" spans="1:7" ht="84">
+    <row r="82" spans="1:7" ht="84" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
-        <v>351</v>
+        <v>296</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>351</v>
+        <v>296</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>352</v>
+        <v>297</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>353</v>
+        <v>298</v>
       </c>
       <c r="E82" s="8"/>
       <c r="F82" s="7"/>
       <c r="G82" s="11" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" ht="409.6">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>355</v>
+        <v>300</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>356</v>
+        <v>300</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>357</v>
+        <v>301</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>358</v>
+        <v>302</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>484</v>
+        <v>409</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>360</v>
+        <v>304</v>
       </c>
       <c r="G83" s="7" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" ht="409.6">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
-        <v>361</v>
+        <v>305</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>362</v>
+        <v>305</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>363</v>
+        <v>306</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>364</v>
+        <v>307</v>
       </c>
       <c r="E84" s="8" t="s">
-        <v>485</v>
+        <v>410</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>366</v>
+        <v>309</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" ht="370">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="370" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>367</v>
+        <v>310</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>368</v>
+        <v>310</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>369</v>
+        <v>311</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>370</v>
+        <v>312</v>
       </c>
       <c r="E85" s="8"/>
       <c r="F85" s="7"/>
       <c r="G85" s="7" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" ht="195">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="195" x14ac:dyDescent="0.25">
       <c r="A86" s="7" t="s">
-        <v>372</v>
+        <v>314</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>373</v>
+        <v>314</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>374</v>
+        <v>315</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>375</v>
+        <v>316</v>
       </c>
       <c r="E86" s="8" t="s">
-        <v>486</v>
+        <v>411</v>
       </c>
       <c r="F86" s="7"/>
       <c r="G86" s="7" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" ht="105">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>377</v>
+        <v>318</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>377</v>
+        <v>318</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>378</v>
+        <v>319</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>379</v>
+        <v>320</v>
       </c>
       <c r="E87" s="8"/>
       <c r="F87" s="7"/>
       <c r="G87" s="7"/>
     </row>
-    <row r="88" spans="1:7" ht="105">
+    <row r="88" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A88" s="7" t="s">
-        <v>380</v>
+        <v>321</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>381</v>
+        <v>321</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>382</v>
+        <v>322</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>383</v>
+        <v>323</v>
       </c>
       <c r="E88" s="8" t="s">
-        <v>487</v>
+        <v>412</v>
       </c>
       <c r="F88" s="7"/>
       <c r="G88" s="7" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" ht="409.6">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>385</v>
+        <v>325</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>386</v>
+        <v>325</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>387</v>
+        <v>326</v>
       </c>
       <c r="D89" s="7"/>
       <c r="E89" s="8"/>
       <c r="F89" s="7"/>
       <c r="G89" s="7"/>
     </row>
-    <row r="90" spans="1:7" ht="409.6">
+    <row r="90" spans="1:7" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A90" s="7" t="s">
-        <v>388</v>
+        <v>327</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>388</v>
+        <v>327</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>389</v>
+        <v>328</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>390</v>
+        <v>329</v>
       </c>
       <c r="E90" s="8" t="s">
-        <v>488</v>
+        <v>413</v>
       </c>
       <c r="F90" s="7"/>
       <c r="G90" s="7" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" ht="126">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="126" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>392</v>
+        <v>331</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>392</v>
+        <v>331</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>393</v>
+        <v>332</v>
       </c>
       <c r="D91" s="11" t="s">
-        <v>394</v>
+        <v>333</v>
       </c>
       <c r="E91" s="8"/>
       <c r="F91" s="7"/>
       <c r="G91" s="7"/>
     </row>
-    <row r="92" spans="1:7" ht="150">
+    <row r="92" spans="1:7" ht="150" x14ac:dyDescent="0.25">
       <c r="A92" s="7" t="s">
-        <v>395</v>
+        <v>425</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>395</v>
+        <v>425</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>396</v>
+        <v>334</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>397</v>
+        <v>335</v>
       </c>
       <c r="E92" s="8"/>
       <c r="F92" s="7"/>
       <c r="G92" s="7" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" ht="342">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="342" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>399</v>
+        <v>337</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>399</v>
+        <v>337</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>400</v>
+        <v>338</v>
       </c>
       <c r="D93" s="7"/>
       <c r="E93" s="8" t="s">
-        <v>489</v>
+        <v>414</v>
       </c>
       <c r="F93" s="7"/>
       <c r="G93" s="7" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" ht="285">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="285" x14ac:dyDescent="0.25">
       <c r="A94" s="7" t="s">
-        <v>402</v>
+        <v>424</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>403</v>
+        <v>424</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>404</v>
+        <v>423</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>405</v>
+        <v>340</v>
       </c>
       <c r="E94" s="8" t="s">
-        <v>490</v>
+        <v>415</v>
       </c>
       <c r="F94" s="7"/>
       <c r="G94" s="7" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" ht="150">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="150" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>407</v>
+        <v>342</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>407</v>
+        <v>428</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>408</v>
+        <v>343</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>409</v>
+        <v>344</v>
       </c>
       <c r="E95" s="8"/>
       <c r="F95" s="7"/>
       <c r="G95" s="7" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" ht="135">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="135" x14ac:dyDescent="0.25">
       <c r="A96" s="7" t="s">
-        <v>411</v>
+        <v>346</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>412</v>
+        <v>346</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>413</v>
+        <v>347</v>
       </c>
       <c r="D96" s="7" t="s">
-        <v>414</v>
+        <v>348</v>
       </c>
       <c r="E96" s="8" t="s">
-        <v>491</v>
+        <v>416</v>
       </c>
       <c r="F96" s="7"/>
       <c r="G96" s="7" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" ht="180">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="180" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>416</v>
+        <v>350</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>417</v>
+        <v>350</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>418</v>
+        <v>351</v>
       </c>
       <c r="D97" s="7" t="s">
-        <v>419</v>
+        <v>352</v>
       </c>
       <c r="E97" s="8"/>
       <c r="F97" s="7"/>
       <c r="G97" s="7" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" ht="90">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A98" s="7" t="s">
-        <v>421</v>
+        <v>354</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>422</v>
+        <v>354</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>423</v>
+        <v>355</v>
       </c>
       <c r="D98" s="7" t="s">
-        <v>424</v>
+        <v>356</v>
       </c>
       <c r="E98" s="8"/>
       <c r="F98" s="7"/>
       <c r="G98" s="7" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" ht="409.6">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>426</v>
+        <v>358</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>426</v>
+        <v>358</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>427</v>
+        <v>359</v>
       </c>
       <c r="D99" s="7" t="s">
-        <v>428</v>
+        <v>360</v>
       </c>
       <c r="E99" s="8" t="s">
-        <v>492</v>
+        <v>417</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>429</v>
+        <v>361</v>
       </c>
       <c r="G99" s="7"/>
     </row>
-    <row r="100" spans="1:7" ht="409.6">
+    <row r="100" spans="1:7" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A100" s="7" t="s">
-        <v>430</v>
+        <v>362</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>430</v>
+        <v>362</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>431</v>
+        <v>363</v>
       </c>
       <c r="D100" s="7" t="s">
-        <v>432</v>
+        <v>364</v>
       </c>
       <c r="E100" s="8" t="s">
-        <v>493</v>
+        <v>418</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>434</v>
+        <v>366</v>
       </c>
       <c r="G100" s="7" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" ht="356">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" ht="356" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>435</v>
+        <v>367</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>436</v>
+        <v>367</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>437</v>
+        <v>368</v>
       </c>
       <c r="D101" s="7"/>
       <c r="E101" s="8"/>
       <c r="F101" s="7"/>
       <c r="G101" s="7" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" ht="135">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" ht="135" x14ac:dyDescent="0.25">
       <c r="A102" s="7" t="s">
-        <v>439</v>
+        <v>370</v>
       </c>
       <c r="B102" s="7" t="s">
-        <v>439</v>
+        <v>370</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>440</v>
+        <v>371</v>
       </c>
       <c r="D102" s="7"/>
       <c r="E102" s="8"/>
       <c r="F102" s="7"/>
       <c r="G102" s="7" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" ht="75">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>442</v>
+        <v>373</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>442</v>
+        <v>373</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>443</v>
+        <v>374</v>
       </c>
       <c r="D103" s="7"/>
       <c r="E103" s="8"/>
       <c r="F103" s="7"/>
       <c r="G103" s="7"/>
     </row>
-    <row r="104" spans="1:7" ht="105">
+    <row r="104" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A104" s="7" t="s">
-        <v>444</v>
+        <v>375</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>445</v>
+        <v>375</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>446</v>
+        <v>376</v>
       </c>
       <c r="D104" s="7" t="s">
-        <v>447</v>
+        <v>377</v>
       </c>
       <c r="E104" s="8"/>
       <c r="F104" s="7"/>
       <c r="G104" s="7" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" ht="75">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>449</v>
+        <v>379</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>450</v>
+        <v>379</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>451</v>
+        <v>380</v>
       </c>
       <c r="D105" s="7"/>
       <c r="E105" s="8"/>
       <c r="F105" s="7"/>
       <c r="G105" s="7"/>
     </row>
-    <row r="106" spans="1:7" ht="75">
+    <row r="106" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A106" s="7" t="s">
-        <v>452</v>
+        <v>381</v>
       </c>
       <c r="B106" s="7" t="s">
-        <v>453</v>
+        <v>381</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>454</v>
+        <v>382</v>
       </c>
       <c r="D106" s="7"/>
       <c r="E106" s="8"/>
       <c r="F106" s="7"/>
       <c r="G106" s="7"/>
     </row>
-    <row r="107" spans="1:7" ht="105">
+    <row r="107" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>455</v>
+        <v>383</v>
       </c>
       <c r="B107" s="7" t="s">
-        <v>455</v>
+        <v>383</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>456</v>
+        <v>384</v>
       </c>
       <c r="D107" s="7"/>
       <c r="E107" s="8"/>
       <c r="F107" s="7"/>
       <c r="G107" s="7"/>
     </row>
-    <row r="108" spans="1:7" ht="180">
+    <row r="108" spans="1:7" ht="180" x14ac:dyDescent="0.25">
       <c r="A108" s="7" t="s">
-        <v>457</v>
+        <v>385</v>
       </c>
       <c r="B108" s="7" t="s">
-        <v>458</v>
+        <v>385</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>459</v>
+        <v>386</v>
       </c>
       <c r="D108" s="7" t="s">
-        <v>460</v>
+        <v>387</v>
       </c>
       <c r="E108" s="8" t="s">
-        <v>494</v>
+        <v>419</v>
       </c>
       <c r="F108" s="7"/>
       <c r="G108" s="7" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" ht="30">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>462</v>
+        <v>389</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>462</v>
+        <v>389</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>463</v>
+        <v>390</v>
       </c>
       <c r="D109" s="7"/>
       <c r="E109" s="8"/>
       <c r="F109" s="7"/>
       <c r="G109" s="7"/>
     </row>
-    <row r="110" spans="1:7" ht="75">
+    <row r="110" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A110" s="7" t="s">
-        <v>464</v>
+        <v>391</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>464</v>
+        <v>391</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>465</v>
+        <v>392</v>
       </c>
       <c r="D110" s="7"/>
       <c r="E110" s="8" t="s">
-        <v>495</v>
+        <v>420</v>
       </c>
       <c r="F110" s="7"/>
       <c r="G110" s="7" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" ht="105">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>467</v>
+        <v>394</v>
       </c>
       <c r="B111" s="7" t="s">
-        <v>468</v>
+        <v>394</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>469</v>
+        <v>395</v>
       </c>
       <c r="D111" s="7" t="s">
-        <v>470</v>
+        <v>396</v>
       </c>
       <c r="E111" s="8"/>
       <c r="F111" s="7"/>
       <c r="G111" s="7" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" ht="105">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A112" s="7" t="s">
-        <v>472</v>
+        <v>398</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>473</v>
+        <v>398</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>474</v>
+        <v>399</v>
       </c>
       <c r="D112" s="7" t="s">
-        <v>475</v>
+        <v>400</v>
       </c>
       <c r="E112" s="8"/>
       <c r="F112" s="7"/>
       <c r="G112" s="7" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" ht="16">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" ht="16" x14ac:dyDescent="0.25">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="3"/>
@@ -4713,7 +4503,7 @@
       <c r="F113" s="3"/>
       <c r="G113" s="3"/>
     </row>
-    <row r="114" spans="1:7" ht="15">
+    <row r="114" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A114" s="4"/>
       <c r="B114" s="4"/>
       <c r="C114" s="4"/>
@@ -4721,7 +4511,7 @@
       <c r="F114" s="4"/>
       <c r="G114" s="4"/>
     </row>
-    <row r="115" spans="1:7" ht="15">
+    <row r="115" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A115" s="4"/>
       <c r="B115" s="4"/>
       <c r="C115" s="4"/>
@@ -4729,7 +4519,7 @@
       <c r="F115" s="4"/>
       <c r="G115" s="4"/>
     </row>
-    <row r="116" spans="1:7" ht="15">
+    <row r="116" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A116" s="4"/>
       <c r="B116" s="4"/>
       <c r="C116" s="4"/>
@@ -4737,7 +4527,7 @@
       <c r="F116" s="4"/>
       <c r="G116" s="4"/>
     </row>
-    <row r="117" spans="1:7" ht="15">
+    <row r="117" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A117" s="4"/>
       <c r="B117" s="4"/>
       <c r="C117" s="4"/>
@@ -4745,7 +4535,7 @@
       <c r="F117" s="4"/>
       <c r="G117" s="4"/>
     </row>
-    <row r="118" spans="1:7" ht="15">
+    <row r="118" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A118" s="4"/>
       <c r="B118" s="4"/>
       <c r="C118" s="4"/>
@@ -4753,7 +4543,7 @@
       <c r="F118" s="4"/>
       <c r="G118" s="4"/>
     </row>
-    <row r="119" spans="1:7" ht="15">
+    <row r="119" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A119" s="4"/>
       <c r="B119" s="4"/>
       <c r="C119" s="4"/>
@@ -4761,7 +4551,7 @@
       <c r="F119" s="4"/>
       <c r="G119" s="4"/>
     </row>
-    <row r="120" spans="1:7" ht="15">
+    <row r="120" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A120" s="4"/>
       <c r="B120" s="4"/>
       <c r="C120" s="4"/>
@@ -4769,7 +4559,7 @@
       <c r="F120" s="4"/>
       <c r="G120" s="4"/>
     </row>
-    <row r="121" spans="1:7" ht="15">
+    <row r="121" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A121" s="4"/>
       <c r="B121" s="4"/>
       <c r="C121" s="4"/>
@@ -4777,7 +4567,7 @@
       <c r="F121" s="4"/>
       <c r="G121" s="4"/>
     </row>
-    <row r="122" spans="1:7" ht="15">
+    <row r="122" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A122" s="4"/>
       <c r="B122" s="4"/>
       <c r="C122" s="4"/>
@@ -4785,7 +4575,7 @@
       <c r="F122" s="4"/>
       <c r="G122" s="4"/>
     </row>
-    <row r="123" spans="1:7" ht="15">
+    <row r="123" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A123" s="4"/>
       <c r="B123" s="4"/>
       <c r="C123" s="4"/>
@@ -4793,7 +4583,7 @@
       <c r="F123" s="4"/>
       <c r="G123" s="4"/>
     </row>
-    <row r="124" spans="1:7" ht="15">
+    <row r="124" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A124" s="4"/>
       <c r="B124" s="4"/>
       <c r="C124" s="4"/>
@@ -4801,7 +4591,7 @@
       <c r="F124" s="4"/>
       <c r="G124" s="4"/>
     </row>
-    <row r="125" spans="1:7" ht="15">
+    <row r="125" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A125" s="4"/>
       <c r="B125" s="4"/>
       <c r="C125" s="4"/>
@@ -4809,7 +4599,7 @@
       <c r="F125" s="4"/>
       <c r="G125" s="4"/>
     </row>
-    <row r="126" spans="1:7" ht="15">
+    <row r="126" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A126" s="4"/>
       <c r="B126" s="4"/>
       <c r="C126" s="4"/>
@@ -4817,7 +4607,7 @@
       <c r="F126" s="4"/>
       <c r="G126" s="4"/>
     </row>
-    <row r="127" spans="1:7" ht="15">
+    <row r="127" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A127" s="4"/>
       <c r="B127" s="4"/>
       <c r="C127" s="4"/>
@@ -4825,7 +4615,7 @@
       <c r="F127" s="4"/>
       <c r="G127" s="4"/>
     </row>
-    <row r="128" spans="1:7" ht="15">
+    <row r="128" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A128" s="4"/>
       <c r="B128" s="4"/>
       <c r="C128" s="4"/>
@@ -4833,7 +4623,7 @@
       <c r="F128" s="4"/>
       <c r="G128" s="4"/>
     </row>
-    <row r="129" spans="1:7" ht="15">
+    <row r="129" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A129" s="4"/>
       <c r="B129" s="4"/>
       <c r="C129" s="4"/>
@@ -4841,7 +4631,7 @@
       <c r="F129" s="4"/>
       <c r="G129" s="4"/>
     </row>
-    <row r="130" spans="1:7" ht="15">
+    <row r="130" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A130" s="4"/>
       <c r="B130" s="4"/>
       <c r="C130" s="4"/>
@@ -4849,7 +4639,7 @@
       <c r="F130" s="4"/>
       <c r="G130" s="4"/>
     </row>
-    <row r="131" spans="1:7" ht="15">
+    <row r="131" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A131" s="4"/>
       <c r="B131" s="4"/>
       <c r="C131" s="4"/>
@@ -4857,7 +4647,7 @@
       <c r="F131" s="4"/>
       <c r="G131" s="4"/>
     </row>
-    <row r="132" spans="1:7" ht="15">
+    <row r="132" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A132" s="4"/>
       <c r="B132" s="4"/>
       <c r="C132" s="4"/>
@@ -4865,7 +4655,7 @@
       <c r="F132" s="4"/>
       <c r="G132" s="4"/>
     </row>
-    <row r="133" spans="1:7" ht="15">
+    <row r="133" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A133" s="4"/>
       <c r="B133" s="4"/>
       <c r="C133" s="4"/>
@@ -4873,7 +4663,7 @@
       <c r="F133" s="4"/>
       <c r="G133" s="4"/>
     </row>
-    <row r="134" spans="1:7" ht="15">
+    <row r="134" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A134" s="4"/>
       <c r="B134" s="4"/>
       <c r="C134" s="4"/>
@@ -4881,7 +4671,7 @@
       <c r="F134" s="4"/>
       <c r="G134" s="4"/>
     </row>
-    <row r="135" spans="1:7" ht="15">
+    <row r="135" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A135" s="4"/>
       <c r="B135" s="4"/>
       <c r="C135" s="4"/>
@@ -4889,7 +4679,7 @@
       <c r="F135" s="4"/>
       <c r="G135" s="4"/>
     </row>
-    <row r="136" spans="1:7" ht="15">
+    <row r="136" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A136" s="4"/>
       <c r="B136" s="4"/>
       <c r="C136" s="4"/>
@@ -4897,7 +4687,7 @@
       <c r="F136" s="4"/>
       <c r="G136" s="4"/>
     </row>
-    <row r="137" spans="1:7" ht="15">
+    <row r="137" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A137" s="4"/>
       <c r="B137" s="4"/>
       <c r="C137" s="4"/>
@@ -4905,7 +4695,7 @@
       <c r="F137" s="4"/>
       <c r="G137" s="4"/>
     </row>
-    <row r="138" spans="1:7" ht="15">
+    <row r="138" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A138" s="4"/>
       <c r="B138" s="4"/>
       <c r="C138" s="4"/>
@@ -4913,7 +4703,7 @@
       <c r="F138" s="4"/>
       <c r="G138" s="4"/>
     </row>
-    <row r="139" spans="1:7" ht="15">
+    <row r="139" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A139" s="4"/>
       <c r="B139" s="4"/>
       <c r="C139" s="4"/>
@@ -4921,7 +4711,7 @@
       <c r="F139" s="4"/>
       <c r="G139" s="4"/>
     </row>
-    <row r="140" spans="1:7" ht="15">
+    <row r="140" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A140" s="4"/>
       <c r="B140" s="4"/>
       <c r="C140" s="4"/>
@@ -4929,7 +4719,7 @@
       <c r="F140" s="4"/>
       <c r="G140" s="4"/>
     </row>
-    <row r="141" spans="1:7" ht="15">
+    <row r="141" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A141" s="4"/>
       <c r="B141" s="4"/>
       <c r="C141" s="4"/>
@@ -4937,7 +4727,7 @@
       <c r="F141" s="4"/>
       <c r="G141" s="4"/>
     </row>
-    <row r="142" spans="1:7" ht="15">
+    <row r="142" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A142" s="4"/>
       <c r="B142" s="4"/>
       <c r="C142" s="4"/>
@@ -4945,7 +4735,7 @@
       <c r="F142" s="4"/>
       <c r="G142" s="4"/>
     </row>
-    <row r="143" spans="1:7" ht="15">
+    <row r="143" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A143" s="4"/>
       <c r="B143" s="4"/>
       <c r="C143" s="4"/>
@@ -4953,7 +4743,7 @@
       <c r="F143" s="4"/>
       <c r="G143" s="4"/>
     </row>
-    <row r="144" spans="1:7" ht="15">
+    <row r="144" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A144" s="4"/>
       <c r="B144" s="4"/>
       <c r="C144" s="4"/>
@@ -4961,7 +4751,7 @@
       <c r="F144" s="4"/>
       <c r="G144" s="4"/>
     </row>
-    <row r="145" spans="1:7" ht="15">
+    <row r="145" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A145" s="4"/>
       <c r="B145" s="4"/>
       <c r="C145" s="4"/>
@@ -4969,7 +4759,7 @@
       <c r="F145" s="4"/>
       <c r="G145" s="4"/>
     </row>
-    <row r="146" spans="1:7" ht="15">
+    <row r="146" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A146" s="4"/>
       <c r="B146" s="4"/>
       <c r="C146" s="4"/>
@@ -4977,7 +4767,7 @@
       <c r="F146" s="4"/>
       <c r="G146" s="4"/>
     </row>
-    <row r="147" spans="1:7" ht="15">
+    <row r="147" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A147" s="4"/>
       <c r="B147" s="4"/>
       <c r="C147" s="4"/>
@@ -4985,7 +4775,7 @@
       <c r="F147" s="4"/>
       <c r="G147" s="4"/>
     </row>
-    <row r="148" spans="1:7" ht="15">
+    <row r="148" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A148" s="4"/>
       <c r="B148" s="4"/>
       <c r="C148" s="4"/>
@@ -4993,7 +4783,7 @@
       <c r="F148" s="4"/>
       <c r="G148" s="4"/>
     </row>
-    <row r="149" spans="1:7" ht="15">
+    <row r="149" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A149" s="4"/>
       <c r="B149" s="4"/>
       <c r="C149" s="4"/>
@@ -5001,7 +4791,7 @@
       <c r="F149" s="4"/>
       <c r="G149" s="4"/>
     </row>
-    <row r="150" spans="1:7" ht="15">
+    <row r="150" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A150" s="4"/>
       <c r="B150" s="4"/>
       <c r="C150" s="4"/>
@@ -5009,7 +4799,7 @@
       <c r="F150" s="4"/>
       <c r="G150" s="4"/>
     </row>
-    <row r="151" spans="1:7" ht="15">
+    <row r="151" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A151" s="4"/>
       <c r="B151" s="4"/>
       <c r="C151" s="4"/>
@@ -5017,7 +4807,7 @@
       <c r="F151" s="4"/>
       <c r="G151" s="4"/>
     </row>
-    <row r="152" spans="1:7" ht="15">
+    <row r="152" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A152" s="4"/>
       <c r="B152" s="4"/>
       <c r="C152" s="4"/>
@@ -5025,7 +4815,7 @@
       <c r="F152" s="4"/>
       <c r="G152" s="4"/>
     </row>
-    <row r="153" spans="1:7" ht="15">
+    <row r="153" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A153" s="4"/>
       <c r="B153" s="4"/>
       <c r="C153" s="4"/>
@@ -5033,7 +4823,7 @@
       <c r="F153" s="4"/>
       <c r="G153" s="4"/>
     </row>
-    <row r="154" spans="1:7" ht="15">
+    <row r="154" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A154" s="4"/>
       <c r="B154" s="4"/>
       <c r="C154" s="4"/>
@@ -5041,7 +4831,7 @@
       <c r="F154" s="4"/>
       <c r="G154" s="4"/>
     </row>
-    <row r="155" spans="1:7" ht="15">
+    <row r="155" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A155" s="4"/>
       <c r="B155" s="4"/>
       <c r="C155" s="4"/>
@@ -5049,7 +4839,7 @@
       <c r="F155" s="4"/>
       <c r="G155" s="4"/>
     </row>
-    <row r="156" spans="1:7" ht="15">
+    <row r="156" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A156" s="4"/>
       <c r="B156" s="4"/>
       <c r="C156" s="4"/>
@@ -5057,7 +4847,7 @@
       <c r="F156" s="4"/>
       <c r="G156" s="4"/>
     </row>
-    <row r="157" spans="1:7" ht="15">
+    <row r="157" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A157" s="4"/>
       <c r="B157" s="4"/>
       <c r="C157" s="4"/>
@@ -5065,7 +4855,7 @@
       <c r="F157" s="4"/>
       <c r="G157" s="4"/>
     </row>
-    <row r="158" spans="1:7" ht="15">
+    <row r="158" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A158" s="4"/>
       <c r="B158" s="4"/>
       <c r="C158" s="4"/>
@@ -5073,7 +4863,7 @@
       <c r="F158" s="4"/>
       <c r="G158" s="4"/>
     </row>
-    <row r="159" spans="1:7" ht="15">
+    <row r="159" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A159" s="4"/>
       <c r="B159" s="4"/>
       <c r="C159" s="4"/>
@@ -5081,7 +4871,7 @@
       <c r="F159" s="4"/>
       <c r="G159" s="4"/>
     </row>
-    <row r="160" spans="1:7" ht="15">
+    <row r="160" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A160" s="4"/>
       <c r="B160" s="4"/>
       <c r="C160" s="4"/>
@@ -5089,7 +4879,7 @@
       <c r="F160" s="4"/>
       <c r="G160" s="4"/>
     </row>
-    <row r="161" spans="1:7" ht="15">
+    <row r="161" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A161" s="4"/>
       <c r="B161" s="4"/>
       <c r="C161" s="4"/>
@@ -5097,7 +4887,7 @@
       <c r="F161" s="4"/>
       <c r="G161" s="4"/>
     </row>
-    <row r="162" spans="1:7" ht="15">
+    <row r="162" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A162" s="4"/>
       <c r="B162" s="4"/>
       <c r="C162" s="4"/>
@@ -5105,7 +4895,7 @@
       <c r="F162" s="4"/>
       <c r="G162" s="4"/>
     </row>
-    <row r="163" spans="1:7" ht="15">
+    <row r="163" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A163" s="4"/>
       <c r="B163" s="4"/>
       <c r="C163" s="4"/>
@@ -5113,7 +4903,7 @@
       <c r="F163" s="4"/>
       <c r="G163" s="4"/>
     </row>
-    <row r="164" spans="1:7" ht="15">
+    <row r="164" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A164" s="4"/>
       <c r="B164" s="4"/>
       <c r="C164" s="4"/>
@@ -5121,7 +4911,7 @@
       <c r="F164" s="4"/>
       <c r="G164" s="4"/>
     </row>
-    <row r="165" spans="1:7" ht="15">
+    <row r="165" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A165" s="4"/>
       <c r="B165" s="4"/>
       <c r="C165" s="4"/>
@@ -5129,7 +4919,7 @@
       <c r="F165" s="4"/>
       <c r="G165" s="4"/>
     </row>
-    <row r="166" spans="1:7" ht="15">
+    <row r="166" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A166" s="4"/>
       <c r="B166" s="4"/>
       <c r="C166" s="4"/>
@@ -5137,7 +4927,7 @@
       <c r="F166" s="4"/>
       <c r="G166" s="4"/>
     </row>
-    <row r="167" spans="1:7" ht="15">
+    <row r="167" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A167" s="4"/>
       <c r="B167" s="4"/>
       <c r="C167" s="4"/>
@@ -5145,7 +4935,7 @@
       <c r="F167" s="4"/>
       <c r="G167" s="4"/>
     </row>
-    <row r="168" spans="1:7" ht="15">
+    <row r="168" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A168" s="4"/>
       <c r="B168" s="4"/>
       <c r="C168" s="4"/>
@@ -5153,7 +4943,7 @@
       <c r="F168" s="4"/>
       <c r="G168" s="4"/>
     </row>
-    <row r="169" spans="1:7" ht="15">
+    <row r="169" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A169" s="4"/>
       <c r="B169" s="4"/>
       <c r="C169" s="4"/>
@@ -5161,7 +4951,7 @@
       <c r="F169" s="4"/>
       <c r="G169" s="4"/>
     </row>
-    <row r="170" spans="1:7" ht="15">
+    <row r="170" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A170" s="4"/>
       <c r="B170" s="4"/>
       <c r="C170" s="4"/>
@@ -5169,7 +4959,7 @@
       <c r="F170" s="4"/>
       <c r="G170" s="4"/>
     </row>
-    <row r="171" spans="1:7" ht="15">
+    <row r="171" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A171" s="4"/>
       <c r="B171" s="4"/>
       <c r="C171" s="4"/>
@@ -5177,7 +4967,7 @@
       <c r="F171" s="4"/>
       <c r="G171" s="4"/>
     </row>
-    <row r="172" spans="1:7" ht="15">
+    <row r="172" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A172" s="4"/>
       <c r="B172" s="4"/>
       <c r="C172" s="4"/>
@@ -5185,7 +4975,7 @@
       <c r="F172" s="4"/>
       <c r="G172" s="4"/>
     </row>
-    <row r="173" spans="1:7" ht="15">
+    <row r="173" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A173" s="4"/>
       <c r="B173" s="4"/>
       <c r="C173" s="4"/>
@@ -5193,7 +4983,7 @@
       <c r="F173" s="4"/>
       <c r="G173" s="4"/>
     </row>
-    <row r="174" spans="1:7" ht="15">
+    <row r="174" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A174" s="4"/>
       <c r="B174" s="4"/>
       <c r="C174" s="4"/>
@@ -5201,7 +4991,7 @@
       <c r="F174" s="4"/>
       <c r="G174" s="4"/>
     </row>
-    <row r="175" spans="1:7" ht="15">
+    <row r="175" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A175" s="4"/>
       <c r="B175" s="4"/>
       <c r="C175" s="4"/>
@@ -5209,7 +4999,7 @@
       <c r="F175" s="4"/>
       <c r="G175" s="4"/>
     </row>
-    <row r="176" spans="1:7" ht="15">
+    <row r="176" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A176" s="4"/>
       <c r="B176" s="4"/>
       <c r="C176" s="4"/>
@@ -5217,7 +5007,7 @@
       <c r="F176" s="4"/>
       <c r="G176" s="4"/>
     </row>
-    <row r="177" spans="1:7" ht="15">
+    <row r="177" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A177" s="4"/>
       <c r="B177" s="4"/>
       <c r="C177" s="4"/>
@@ -5225,7 +5015,7 @@
       <c r="F177" s="4"/>
       <c r="G177" s="4"/>
     </row>
-    <row r="178" spans="1:7" ht="15">
+    <row r="178" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A178" s="4"/>
       <c r="B178" s="4"/>
       <c r="C178" s="4"/>
@@ -5233,7 +5023,7 @@
       <c r="F178" s="4"/>
       <c r="G178" s="4"/>
     </row>
-    <row r="179" spans="1:7" ht="15">
+    <row r="179" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A179" s="4"/>
       <c r="B179" s="4"/>
       <c r="C179" s="4"/>
@@ -5241,7 +5031,7 @@
       <c r="F179" s="4"/>
       <c r="G179" s="4"/>
     </row>
-    <row r="180" spans="1:7" ht="15">
+    <row r="180" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A180" s="4"/>
       <c r="B180" s="4"/>
       <c r="C180" s="4"/>
@@ -5249,7 +5039,7 @@
       <c r="F180" s="4"/>
       <c r="G180" s="4"/>
     </row>
-    <row r="181" spans="1:7" ht="15">
+    <row r="181" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A181" s="4"/>
       <c r="B181" s="4"/>
       <c r="C181" s="4"/>
@@ -5257,7 +5047,7 @@
       <c r="F181" s="4"/>
       <c r="G181" s="4"/>
     </row>
-    <row r="182" spans="1:7" ht="15">
+    <row r="182" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A182" s="4"/>
       <c r="B182" s="4"/>
       <c r="C182" s="4"/>
@@ -5265,7 +5055,7 @@
       <c r="F182" s="4"/>
       <c r="G182" s="4"/>
     </row>
-    <row r="183" spans="1:7" ht="15">
+    <row r="183" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A183" s="4"/>
       <c r="B183" s="4"/>
       <c r="C183" s="4"/>
@@ -5273,7 +5063,7 @@
       <c r="F183" s="4"/>
       <c r="G183" s="4"/>
     </row>
-    <row r="184" spans="1:7" ht="15">
+    <row r="184" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A184" s="4"/>
       <c r="B184" s="4"/>
       <c r="C184" s="4"/>
@@ -5281,7 +5071,7 @@
       <c r="F184" s="4"/>
       <c r="G184" s="4"/>
     </row>
-    <row r="185" spans="1:7" ht="15">
+    <row r="185" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A185" s="4"/>
       <c r="B185" s="4"/>
       <c r="C185" s="4"/>
@@ -5289,7 +5079,7 @@
       <c r="F185" s="4"/>
       <c r="G185" s="4"/>
     </row>
-    <row r="186" spans="1:7" ht="15">
+    <row r="186" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A186" s="4"/>
       <c r="B186" s="4"/>
       <c r="C186" s="4"/>
@@ -5297,7 +5087,7 @@
       <c r="F186" s="4"/>
       <c r="G186" s="4"/>
     </row>
-    <row r="187" spans="1:7" ht="15">
+    <row r="187" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A187" s="4"/>
       <c r="B187" s="4"/>
       <c r="C187" s="4"/>
@@ -5305,7 +5095,7 @@
       <c r="F187" s="4"/>
       <c r="G187" s="4"/>
     </row>
-    <row r="188" spans="1:7" ht="15">
+    <row r="188" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A188" s="4"/>
       <c r="B188" s="4"/>
       <c r="C188" s="4"/>
@@ -5313,7 +5103,7 @@
       <c r="F188" s="4"/>
       <c r="G188" s="4"/>
     </row>
-    <row r="189" spans="1:7" ht="15">
+    <row r="189" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A189" s="4"/>
       <c r="B189" s="4"/>
       <c r="C189" s="4"/>
@@ -5321,7 +5111,7 @@
       <c r="F189" s="4"/>
       <c r="G189" s="4"/>
     </row>
-    <row r="190" spans="1:7" ht="15">
+    <row r="190" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A190" s="4"/>
       <c r="B190" s="4"/>
       <c r="C190" s="4"/>
@@ -5329,7 +5119,7 @@
       <c r="F190" s="4"/>
       <c r="G190" s="4"/>
     </row>
-    <row r="191" spans="1:7" ht="15">
+    <row r="191" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A191" s="4"/>
       <c r="B191" s="4"/>
       <c r="C191" s="4"/>
@@ -5337,7 +5127,7 @@
       <c r="F191" s="4"/>
       <c r="G191" s="4"/>
     </row>
-    <row r="192" spans="1:7" ht="15">
+    <row r="192" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A192" s="4"/>
       <c r="B192" s="4"/>
       <c r="C192" s="4"/>
@@ -5345,7 +5135,7 @@
       <c r="F192" s="4"/>
       <c r="G192" s="4"/>
     </row>
-    <row r="193" spans="1:7" ht="15">
+    <row r="193" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A193" s="4"/>
       <c r="B193" s="4"/>
       <c r="C193" s="4"/>
@@ -5353,7 +5143,7 @@
       <c r="F193" s="4"/>
       <c r="G193" s="4"/>
     </row>
-    <row r="194" spans="1:7" ht="15">
+    <row r="194" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A194" s="4"/>
       <c r="B194" s="4"/>
       <c r="C194" s="4"/>
@@ -5361,7 +5151,7 @@
       <c r="F194" s="4"/>
       <c r="G194" s="4"/>
     </row>
-    <row r="195" spans="1:7" ht="15">
+    <row r="195" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A195" s="4"/>
       <c r="B195" s="4"/>
       <c r="C195" s="4"/>
@@ -5369,7 +5159,7 @@
       <c r="F195" s="4"/>
       <c r="G195" s="4"/>
     </row>
-    <row r="196" spans="1:7" ht="15">
+    <row r="196" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A196" s="4"/>
       <c r="B196" s="4"/>
       <c r="C196" s="4"/>
@@ -5377,7 +5167,7 @@
       <c r="F196" s="4"/>
       <c r="G196" s="4"/>
     </row>
-    <row r="197" spans="1:7" ht="15">
+    <row r="197" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A197" s="4"/>
       <c r="B197" s="4"/>
       <c r="C197" s="4"/>
@@ -5385,7 +5175,7 @@
       <c r="F197" s="4"/>
       <c r="G197" s="4"/>
     </row>
-    <row r="198" spans="1:7" ht="15">
+    <row r="198" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A198" s="4"/>
       <c r="B198" s="4"/>
       <c r="C198" s="4"/>
@@ -5393,7 +5183,7 @@
       <c r="F198" s="4"/>
       <c r="G198" s="4"/>
     </row>
-    <row r="199" spans="1:7" ht="15">
+    <row r="199" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A199" s="4"/>
       <c r="B199" s="4"/>
       <c r="C199" s="4"/>
@@ -5401,7 +5191,7 @@
       <c r="F199" s="4"/>
       <c r="G199" s="4"/>
     </row>
-    <row r="200" spans="1:7" ht="15">
+    <row r="200" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A200" s="4"/>
       <c r="B200" s="4"/>
       <c r="C200" s="4"/>
@@ -5409,7 +5199,7 @@
       <c r="F200" s="4"/>
       <c r="G200" s="4"/>
     </row>
-    <row r="201" spans="1:7" ht="15">
+    <row r="201" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A201" s="4"/>
       <c r="B201" s="4"/>
       <c r="C201" s="4"/>
@@ -5417,7 +5207,7 @@
       <c r="F201" s="4"/>
       <c r="G201" s="4"/>
     </row>
-    <row r="202" spans="1:7" ht="15">
+    <row r="202" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A202" s="4"/>
       <c r="B202" s="4"/>
       <c r="C202" s="4"/>
@@ -5425,7 +5215,7 @@
       <c r="F202" s="4"/>
       <c r="G202" s="4"/>
     </row>
-    <row r="203" spans="1:7" ht="15">
+    <row r="203" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A203" s="4"/>
       <c r="B203" s="4"/>
       <c r="C203" s="4"/>
@@ -5433,7 +5223,7 @@
       <c r="F203" s="4"/>
       <c r="G203" s="4"/>
     </row>
-    <row r="204" spans="1:7" ht="15">
+    <row r="204" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A204" s="4"/>
       <c r="B204" s="4"/>
       <c r="C204" s="4"/>
@@ -5441,7 +5231,7 @@
       <c r="F204" s="4"/>
       <c r="G204" s="4"/>
     </row>
-    <row r="205" spans="1:7" ht="15">
+    <row r="205" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A205" s="4"/>
       <c r="B205" s="4"/>
       <c r="C205" s="4"/>
@@ -5449,7 +5239,7 @@
       <c r="F205" s="4"/>
       <c r="G205" s="4"/>
     </row>
-    <row r="206" spans="1:7" ht="15">
+    <row r="206" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A206" s="4"/>
       <c r="B206" s="4"/>
       <c r="C206" s="4"/>
@@ -5457,7 +5247,7 @@
       <c r="F206" s="4"/>
       <c r="G206" s="4"/>
     </row>
-    <row r="207" spans="1:7" ht="15">
+    <row r="207" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A207" s="4"/>
       <c r="B207" s="4"/>
       <c r="C207" s="4"/>
@@ -5465,7 +5255,7 @@
       <c r="F207" s="4"/>
       <c r="G207" s="4"/>
     </row>
-    <row r="208" spans="1:7" ht="15">
+    <row r="208" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A208" s="4"/>
       <c r="B208" s="4"/>
       <c r="C208" s="4"/>
@@ -5473,7 +5263,7 @@
       <c r="F208" s="4"/>
       <c r="G208" s="4"/>
     </row>
-    <row r="209" spans="1:7" ht="15">
+    <row r="209" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A209" s="4"/>
       <c r="B209" s="4"/>
       <c r="C209" s="4"/>
@@ -5481,7 +5271,7 @@
       <c r="F209" s="4"/>
       <c r="G209" s="4"/>
     </row>
-    <row r="210" spans="1:7" ht="15">
+    <row r="210" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A210" s="4"/>
       <c r="B210" s="4"/>
       <c r="C210" s="4"/>
@@ -5489,7 +5279,7 @@
       <c r="F210" s="4"/>
       <c r="G210" s="4"/>
     </row>
-    <row r="211" spans="1:7" ht="15">
+    <row r="211" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A211" s="4"/>
       <c r="B211" s="4"/>
       <c r="C211" s="4"/>
@@ -5497,7 +5287,7 @@
       <c r="F211" s="4"/>
       <c r="G211" s="4"/>
     </row>
-    <row r="212" spans="1:7" ht="15">
+    <row r="212" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A212" s="4"/>
       <c r="B212" s="4"/>
       <c r="C212" s="4"/>
@@ -5505,7 +5295,7 @@
       <c r="F212" s="4"/>
       <c r="G212" s="4"/>
     </row>
-    <row r="213" spans="1:7" ht="15">
+    <row r="213" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A213" s="4"/>
       <c r="B213" s="4"/>
       <c r="C213" s="4"/>
@@ -5513,7 +5303,7 @@
       <c r="F213" s="4"/>
       <c r="G213" s="4"/>
     </row>
-    <row r="214" spans="1:7" ht="15">
+    <row r="214" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A214" s="4"/>
       <c r="B214" s="4"/>
       <c r="C214" s="4"/>
@@ -5521,7 +5311,7 @@
       <c r="F214" s="4"/>
       <c r="G214" s="4"/>
     </row>
-    <row r="215" spans="1:7" ht="15">
+    <row r="215" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A215" s="4"/>
       <c r="B215" s="4"/>
       <c r="C215" s="4"/>
@@ -5529,7 +5319,7 @@
       <c r="F215" s="4"/>
       <c r="G215" s="4"/>
     </row>
-    <row r="216" spans="1:7" ht="15">
+    <row r="216" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A216" s="4"/>
       <c r="B216" s="4"/>
       <c r="C216" s="4"/>
@@ -5537,7 +5327,7 @@
       <c r="F216" s="4"/>
       <c r="G216" s="4"/>
     </row>
-    <row r="217" spans="1:7" ht="15">
+    <row r="217" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A217" s="4"/>
       <c r="B217" s="4"/>
       <c r="C217" s="4"/>
@@ -5545,7 +5335,7 @@
       <c r="F217" s="4"/>
       <c r="G217" s="4"/>
     </row>
-    <row r="218" spans="1:7" ht="15">
+    <row r="218" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A218" s="4"/>
       <c r="B218" s="4"/>
       <c r="C218" s="4"/>
@@ -5553,7 +5343,7 @@
       <c r="F218" s="4"/>
       <c r="G218" s="4"/>
     </row>
-    <row r="219" spans="1:7" ht="15">
+    <row r="219" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A219" s="4"/>
       <c r="B219" s="4"/>
       <c r="C219" s="4"/>
@@ -5561,7 +5351,7 @@
       <c r="F219" s="4"/>
       <c r="G219" s="4"/>
     </row>
-    <row r="220" spans="1:7" ht="15">
+    <row r="220" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A220" s="4"/>
       <c r="B220" s="4"/>
       <c r="C220" s="4"/>
@@ -5569,7 +5359,7 @@
       <c r="F220" s="4"/>
       <c r="G220" s="4"/>
     </row>
-    <row r="221" spans="1:7" ht="15">
+    <row r="221" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A221" s="4"/>
       <c r="B221" s="4"/>
       <c r="C221" s="4"/>
@@ -5577,7 +5367,7 @@
       <c r="F221" s="4"/>
       <c r="G221" s="4"/>
     </row>
-    <row r="222" spans="1:7" ht="15">
+    <row r="222" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A222" s="4"/>
       <c r="B222" s="4"/>
       <c r="C222" s="4"/>
@@ -5585,7 +5375,7 @@
       <c r="F222" s="4"/>
       <c r="G222" s="4"/>
     </row>
-    <row r="223" spans="1:7" ht="15">
+    <row r="223" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A223" s="4"/>
       <c r="B223" s="4"/>
       <c r="C223" s="4"/>
@@ -5593,7 +5383,7 @@
       <c r="F223" s="4"/>
       <c r="G223" s="4"/>
     </row>
-    <row r="224" spans="1:7" ht="15">
+    <row r="224" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A224" s="4"/>
       <c r="B224" s="4"/>
       <c r="C224" s="4"/>
@@ -5601,7 +5391,7 @@
       <c r="F224" s="4"/>
       <c r="G224" s="4"/>
     </row>
-    <row r="225" spans="1:7" ht="15">
+    <row r="225" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A225" s="4"/>
       <c r="B225" s="4"/>
       <c r="C225" s="4"/>
@@ -5609,7 +5399,7 @@
       <c r="F225" s="4"/>
       <c r="G225" s="4"/>
     </row>
-    <row r="226" spans="1:7" ht="15">
+    <row r="226" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A226" s="4"/>
       <c r="B226" s="4"/>
       <c r="C226" s="4"/>
@@ -5617,7 +5407,7 @@
       <c r="F226" s="4"/>
       <c r="G226" s="4"/>
     </row>
-    <row r="227" spans="1:7" ht="15">
+    <row r="227" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A227" s="4"/>
       <c r="B227" s="4"/>
       <c r="C227" s="4"/>
@@ -5625,7 +5415,7 @@
       <c r="F227" s="4"/>
       <c r="G227" s="4"/>
     </row>
-    <row r="228" spans="1:7" ht="15">
+    <row r="228" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A228" s="4"/>
       <c r="B228" s="4"/>
       <c r="C228" s="4"/>
@@ -5633,7 +5423,7 @@
       <c r="F228" s="4"/>
       <c r="G228" s="4"/>
     </row>
-    <row r="229" spans="1:7" ht="15">
+    <row r="229" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A229" s="4"/>
       <c r="B229" s="4"/>
       <c r="C229" s="4"/>
@@ -5641,7 +5431,7 @@
       <c r="F229" s="4"/>
       <c r="G229" s="4"/>
     </row>
-    <row r="230" spans="1:7" ht="15">
+    <row r="230" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A230" s="4"/>
       <c r="B230" s="4"/>
       <c r="C230" s="4"/>
@@ -5649,7 +5439,7 @@
       <c r="F230" s="4"/>
       <c r="G230" s="4"/>
     </row>
-    <row r="231" spans="1:7" ht="15">
+    <row r="231" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A231" s="4"/>
       <c r="B231" s="4"/>
       <c r="C231" s="4"/>
@@ -5657,7 +5447,7 @@
       <c r="F231" s="4"/>
       <c r="G231" s="4"/>
     </row>
-    <row r="232" spans="1:7" ht="15">
+    <row r="232" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A232" s="4"/>
       <c r="B232" s="4"/>
       <c r="C232" s="4"/>
@@ -5665,7 +5455,7 @@
       <c r="F232" s="4"/>
       <c r="G232" s="4"/>
     </row>
-    <row r="233" spans="1:7" ht="15">
+    <row r="233" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A233" s="4"/>
       <c r="B233" s="4"/>
       <c r="C233" s="4"/>
@@ -5673,7 +5463,7 @@
       <c r="F233" s="4"/>
       <c r="G233" s="4"/>
     </row>
-    <row r="234" spans="1:7" ht="15">
+    <row r="234" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A234" s="4"/>
       <c r="B234" s="4"/>
       <c r="C234" s="4"/>
@@ -5681,7 +5471,7 @@
       <c r="F234" s="4"/>
       <c r="G234" s="4"/>
     </row>
-    <row r="235" spans="1:7" ht="15">
+    <row r="235" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A235" s="4"/>
       <c r="B235" s="4"/>
       <c r="C235" s="4"/>
@@ -5689,7 +5479,7 @@
       <c r="F235" s="4"/>
       <c r="G235" s="4"/>
     </row>
-    <row r="236" spans="1:7" ht="15">
+    <row r="236" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A236" s="4"/>
       <c r="B236" s="4"/>
       <c r="C236" s="4"/>
@@ -5697,7 +5487,7 @@
       <c r="F236" s="4"/>
       <c r="G236" s="4"/>
     </row>
-    <row r="237" spans="1:7" ht="15">
+    <row r="237" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A237" s="4"/>
       <c r="B237" s="4"/>
       <c r="C237" s="4"/>
@@ -5705,7 +5495,7 @@
       <c r="F237" s="4"/>
       <c r="G237" s="4"/>
     </row>
-    <row r="238" spans="1:7" ht="15">
+    <row r="238" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A238" s="4"/>
       <c r="B238" s="4"/>
       <c r="C238" s="4"/>
@@ -5713,7 +5503,7 @@
       <c r="F238" s="4"/>
       <c r="G238" s="4"/>
     </row>
-    <row r="239" spans="1:7" ht="15">
+    <row r="239" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A239" s="4"/>
       <c r="B239" s="4"/>
       <c r="C239" s="4"/>
@@ -5721,7 +5511,7 @@
       <c r="F239" s="4"/>
       <c r="G239" s="4"/>
     </row>
-    <row r="240" spans="1:7" ht="15">
+    <row r="240" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A240" s="4"/>
       <c r="B240" s="4"/>
       <c r="C240" s="4"/>
@@ -5729,7 +5519,7 @@
       <c r="F240" s="4"/>
       <c r="G240" s="4"/>
     </row>
-    <row r="241" spans="1:7" ht="15">
+    <row r="241" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A241" s="4"/>
       <c r="B241" s="4"/>
       <c r="C241" s="4"/>
@@ -5737,7 +5527,7 @@
       <c r="F241" s="4"/>
       <c r="G241" s="4"/>
     </row>
-    <row r="242" spans="1:7" ht="15">
+    <row r="242" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A242" s="4"/>
       <c r="B242" s="4"/>
       <c r="C242" s="4"/>
@@ -5745,7 +5535,7 @@
       <c r="F242" s="4"/>
       <c r="G242" s="4"/>
     </row>
-    <row r="243" spans="1:7" ht="15">
+    <row r="243" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A243" s="4"/>
       <c r="B243" s="4"/>
       <c r="C243" s="4"/>
@@ -5753,7 +5543,7 @@
       <c r="F243" s="4"/>
       <c r="G243" s="4"/>
     </row>
-    <row r="244" spans="1:7" ht="15">
+    <row r="244" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A244" s="4"/>
       <c r="B244" s="4"/>
       <c r="C244" s="4"/>
@@ -5761,7 +5551,7 @@
       <c r="F244" s="4"/>
       <c r="G244" s="4"/>
     </row>
-    <row r="245" spans="1:7" ht="15">
+    <row r="245" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A245" s="4"/>
       <c r="B245" s="4"/>
       <c r="C245" s="4"/>
@@ -5769,7 +5559,7 @@
       <c r="F245" s="4"/>
       <c r="G245" s="4"/>
     </row>
-    <row r="246" spans="1:7" ht="15">
+    <row r="246" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A246" s="4"/>
       <c r="B246" s="4"/>
       <c r="C246" s="4"/>
@@ -5777,7 +5567,7 @@
       <c r="F246" s="4"/>
       <c r="G246" s="4"/>
     </row>
-    <row r="247" spans="1:7" ht="15">
+    <row r="247" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A247" s="4"/>
       <c r="B247" s="4"/>
       <c r="C247" s="4"/>
@@ -5785,7 +5575,7 @@
       <c r="F247" s="4"/>
       <c r="G247" s="4"/>
     </row>
-    <row r="248" spans="1:7" ht="15">
+    <row r="248" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A248" s="4"/>
       <c r="B248" s="4"/>
       <c r="C248" s="4"/>
@@ -5793,7 +5583,7 @@
       <c r="F248" s="4"/>
       <c r="G248" s="4"/>
     </row>
-    <row r="249" spans="1:7" ht="15">
+    <row r="249" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A249" s="4"/>
       <c r="B249" s="4"/>
       <c r="C249" s="4"/>
@@ -5801,7 +5591,7 @@
       <c r="F249" s="4"/>
       <c r="G249" s="4"/>
     </row>
-    <row r="250" spans="1:7" ht="15">
+    <row r="250" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A250" s="4"/>
       <c r="B250" s="4"/>
       <c r="C250" s="4"/>
@@ -5809,7 +5599,7 @@
       <c r="F250" s="4"/>
       <c r="G250" s="4"/>
     </row>
-    <row r="251" spans="1:7" ht="15">
+    <row r="251" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A251" s="4"/>
       <c r="B251" s="4"/>
       <c r="C251" s="4"/>
@@ -5817,7 +5607,7 @@
       <c r="F251" s="4"/>
       <c r="G251" s="4"/>
     </row>
-    <row r="252" spans="1:7" ht="15">
+    <row r="252" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A252" s="4"/>
       <c r="B252" s="4"/>
       <c r="C252" s="4"/>
@@ -5825,7 +5615,7 @@
       <c r="F252" s="4"/>
       <c r="G252" s="4"/>
     </row>
-    <row r="253" spans="1:7" ht="15">
+    <row r="253" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A253" s="4"/>
       <c r="B253" s="4"/>
       <c r="C253" s="4"/>
@@ -5833,7 +5623,7 @@
       <c r="F253" s="4"/>
       <c r="G253" s="4"/>
     </row>
-    <row r="254" spans="1:7" ht="15">
+    <row r="254" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A254" s="4"/>
       <c r="B254" s="4"/>
       <c r="C254" s="4"/>
@@ -5841,7 +5631,7 @@
       <c r="F254" s="4"/>
       <c r="G254" s="4"/>
     </row>
-    <row r="255" spans="1:7" ht="15">
+    <row r="255" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A255" s="4"/>
       <c r="B255" s="4"/>
       <c r="C255" s="4"/>
@@ -5849,7 +5639,7 @@
       <c r="F255" s="4"/>
       <c r="G255" s="4"/>
     </row>
-    <row r="256" spans="1:7" ht="15">
+    <row r="256" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A256" s="4"/>
       <c r="B256" s="4"/>
       <c r="C256" s="4"/>
@@ -5857,7 +5647,7 @@
       <c r="F256" s="4"/>
       <c r="G256" s="4"/>
     </row>
-    <row r="257" spans="1:7" ht="15">
+    <row r="257" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A257" s="4"/>
       <c r="B257" s="4"/>
       <c r="C257" s="4"/>
@@ -5865,7 +5655,7 @@
       <c r="F257" s="4"/>
       <c r="G257" s="4"/>
     </row>
-    <row r="258" spans="1:7" ht="15">
+    <row r="258" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A258" s="4"/>
       <c r="B258" s="4"/>
       <c r="C258" s="4"/>
@@ -5873,7 +5663,7 @@
       <c r="F258" s="4"/>
       <c r="G258" s="4"/>
     </row>
-    <row r="259" spans="1:7" ht="15">
+    <row r="259" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A259" s="4"/>
       <c r="B259" s="4"/>
       <c r="C259" s="4"/>
@@ -5881,7 +5671,7 @@
       <c r="F259" s="4"/>
       <c r="G259" s="4"/>
     </row>
-    <row r="260" spans="1:7" ht="15">
+    <row r="260" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A260" s="4"/>
       <c r="B260" s="4"/>
       <c r="C260" s="4"/>
@@ -5889,7 +5679,7 @@
       <c r="F260" s="4"/>
       <c r="G260" s="4"/>
     </row>
-    <row r="261" spans="1:7" ht="15">
+    <row r="261" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A261" s="4"/>
       <c r="B261" s="4"/>
       <c r="C261" s="4"/>
@@ -5897,7 +5687,7 @@
       <c r="F261" s="4"/>
       <c r="G261" s="4"/>
     </row>
-    <row r="262" spans="1:7" ht="15">
+    <row r="262" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A262" s="4"/>
       <c r="B262" s="4"/>
       <c r="C262" s="4"/>
@@ -5905,7 +5695,7 @@
       <c r="F262" s="4"/>
       <c r="G262" s="4"/>
     </row>
-    <row r="263" spans="1:7" ht="15">
+    <row r="263" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A263" s="4"/>
       <c r="B263" s="4"/>
       <c r="C263" s="4"/>
@@ -5913,7 +5703,7 @@
       <c r="F263" s="4"/>
       <c r="G263" s="4"/>
     </row>
-    <row r="264" spans="1:7" ht="15">
+    <row r="264" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A264" s="4"/>
       <c r="B264" s="4"/>
       <c r="C264" s="4"/>
@@ -5921,7 +5711,7 @@
       <c r="F264" s="4"/>
       <c r="G264" s="4"/>
     </row>
-    <row r="265" spans="1:7" ht="15">
+    <row r="265" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A265" s="4"/>
       <c r="B265" s="4"/>
       <c r="C265" s="4"/>
@@ -5929,7 +5719,7 @@
       <c r="F265" s="4"/>
       <c r="G265" s="4"/>
     </row>
-    <row r="266" spans="1:7" ht="15">
+    <row r="266" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A266" s="4"/>
       <c r="B266" s="4"/>
       <c r="C266" s="4"/>
@@ -5937,7 +5727,7 @@
       <c r="F266" s="4"/>
       <c r="G266" s="4"/>
     </row>
-    <row r="267" spans="1:7" ht="15">
+    <row r="267" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A267" s="4"/>
       <c r="B267" s="4"/>
       <c r="C267" s="4"/>
@@ -5945,7 +5735,7 @@
       <c r="F267" s="4"/>
       <c r="G267" s="4"/>
     </row>
-    <row r="268" spans="1:7" ht="15">
+    <row r="268" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A268" s="4"/>
       <c r="B268" s="4"/>
       <c r="C268" s="4"/>
@@ -5953,7 +5743,7 @@
       <c r="F268" s="4"/>
       <c r="G268" s="4"/>
     </row>
-    <row r="269" spans="1:7" ht="15">
+    <row r="269" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A269" s="4"/>
       <c r="B269" s="4"/>
       <c r="C269" s="4"/>
@@ -5961,7 +5751,7 @@
       <c r="F269" s="4"/>
       <c r="G269" s="4"/>
     </row>
-    <row r="270" spans="1:7" ht="15">
+    <row r="270" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A270" s="4"/>
       <c r="B270" s="4"/>
       <c r="C270" s="4"/>
@@ -5969,7 +5759,7 @@
       <c r="F270" s="4"/>
       <c r="G270" s="4"/>
     </row>
-    <row r="271" spans="1:7" ht="15">
+    <row r="271" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A271" s="4"/>
       <c r="B271" s="4"/>
       <c r="C271" s="4"/>
@@ -5977,7 +5767,7 @@
       <c r="F271" s="4"/>
       <c r="G271" s="4"/>
     </row>
-    <row r="272" spans="1:7" ht="15">
+    <row r="272" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A272" s="4"/>
       <c r="B272" s="4"/>
       <c r="C272" s="4"/>
@@ -5985,7 +5775,7 @@
       <c r="F272" s="4"/>
       <c r="G272" s="4"/>
     </row>
-    <row r="273" spans="1:7" ht="15">
+    <row r="273" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A273" s="4"/>
       <c r="B273" s="4"/>
       <c r="C273" s="4"/>
@@ -5993,7 +5783,7 @@
       <c r="F273" s="4"/>
       <c r="G273" s="4"/>
     </row>
-    <row r="274" spans="1:7" ht="15">
+    <row r="274" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A274" s="4"/>
       <c r="B274" s="4"/>
       <c r="C274" s="4"/>
@@ -6001,7 +5791,7 @@
       <c r="F274" s="4"/>
       <c r="G274" s="4"/>
     </row>
-    <row r="275" spans="1:7" ht="15">
+    <row r="275" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A275" s="4"/>
       <c r="B275" s="4"/>
       <c r="C275" s="4"/>
@@ -6009,7 +5799,7 @@
       <c r="F275" s="4"/>
       <c r="G275" s="4"/>
     </row>
-    <row r="276" spans="1:7" ht="15">
+    <row r="276" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A276" s="4"/>
       <c r="B276" s="4"/>
       <c r="C276" s="4"/>
@@ -6017,7 +5807,7 @@
       <c r="F276" s="4"/>
       <c r="G276" s="4"/>
     </row>
-    <row r="277" spans="1:7" ht="15">
+    <row r="277" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A277" s="4"/>
       <c r="B277" s="4"/>
       <c r="C277" s="4"/>
@@ -6025,7 +5815,7 @@
       <c r="F277" s="4"/>
       <c r="G277" s="4"/>
     </row>
-    <row r="278" spans="1:7" ht="15">
+    <row r="278" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A278" s="4"/>
       <c r="B278" s="4"/>
       <c r="C278" s="4"/>
@@ -6033,7 +5823,7 @@
       <c r="F278" s="4"/>
       <c r="G278" s="4"/>
     </row>
-    <row r="279" spans="1:7" ht="15">
+    <row r="279" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A279" s="4"/>
       <c r="B279" s="4"/>
       <c r="C279" s="4"/>
@@ -6041,7 +5831,7 @@
       <c r="F279" s="4"/>
       <c r="G279" s="4"/>
     </row>
-    <row r="280" spans="1:7" ht="15">
+    <row r="280" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A280" s="4"/>
       <c r="B280" s="4"/>
       <c r="C280" s="4"/>
@@ -6049,7 +5839,7 @@
       <c r="F280" s="4"/>
       <c r="G280" s="4"/>
     </row>
-    <row r="281" spans="1:7" ht="15">
+    <row r="281" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A281" s="4"/>
       <c r="B281" s="4"/>
       <c r="C281" s="4"/>
@@ -6057,7 +5847,7 @@
       <c r="F281" s="4"/>
       <c r="G281" s="4"/>
     </row>
-    <row r="282" spans="1:7" ht="15">
+    <row r="282" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A282" s="4"/>
       <c r="B282" s="4"/>
       <c r="C282" s="4"/>
@@ -6065,7 +5855,7 @@
       <c r="F282" s="4"/>
       <c r="G282" s="4"/>
     </row>
-    <row r="283" spans="1:7" ht="15">
+    <row r="283" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A283" s="4"/>
       <c r="B283" s="4"/>
       <c r="C283" s="4"/>
@@ -6073,7 +5863,7 @@
       <c r="F283" s="4"/>
       <c r="G283" s="4"/>
     </row>
-    <row r="284" spans="1:7" ht="15">
+    <row r="284" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A284" s="4"/>
       <c r="B284" s="4"/>
       <c r="C284" s="4"/>
@@ -6081,7 +5871,7 @@
       <c r="F284" s="4"/>
       <c r="G284" s="4"/>
     </row>
-    <row r="285" spans="1:7" ht="15">
+    <row r="285" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A285" s="4"/>
       <c r="B285" s="4"/>
       <c r="C285" s="4"/>
@@ -6089,7 +5879,7 @@
       <c r="F285" s="4"/>
       <c r="G285" s="4"/>
     </row>
-    <row r="286" spans="1:7" ht="15">
+    <row r="286" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A286" s="4"/>
       <c r="B286" s="4"/>
       <c r="C286" s="4"/>
@@ -6097,7 +5887,7 @@
       <c r="F286" s="4"/>
       <c r="G286" s="4"/>
     </row>
-    <row r="287" spans="1:7" ht="15">
+    <row r="287" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A287" s="4"/>
       <c r="B287" s="4"/>
       <c r="C287" s="4"/>
@@ -6105,7 +5895,7 @@
       <c r="F287" s="4"/>
       <c r="G287" s="4"/>
     </row>
-    <row r="288" spans="1:7" ht="15">
+    <row r="288" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A288" s="4"/>
       <c r="B288" s="4"/>
       <c r="C288" s="4"/>
@@ -6113,7 +5903,7 @@
       <c r="F288" s="4"/>
       <c r="G288" s="4"/>
     </row>
-    <row r="289" spans="1:7" ht="15">
+    <row r="289" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A289" s="4"/>
       <c r="B289" s="4"/>
       <c r="C289" s="4"/>
@@ -6121,7 +5911,7 @@
       <c r="F289" s="4"/>
       <c r="G289" s="4"/>
     </row>
-    <row r="290" spans="1:7" ht="15">
+    <row r="290" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A290" s="4"/>
       <c r="B290" s="4"/>
       <c r="C290" s="4"/>
@@ -6129,7 +5919,7 @@
       <c r="F290" s="4"/>
       <c r="G290" s="4"/>
     </row>
-    <row r="291" spans="1:7" ht="15">
+    <row r="291" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A291" s="4"/>
       <c r="B291" s="4"/>
       <c r="C291" s="4"/>
@@ -6137,7 +5927,7 @@
       <c r="F291" s="4"/>
       <c r="G291" s="4"/>
     </row>
-    <row r="292" spans="1:7" ht="15">
+    <row r="292" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A292" s="4"/>
       <c r="B292" s="4"/>
       <c r="C292" s="4"/>
@@ -6145,7 +5935,7 @@
       <c r="F292" s="4"/>
       <c r="G292" s="4"/>
     </row>
-    <row r="293" spans="1:7" ht="15">
+    <row r="293" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A293" s="4"/>
       <c r="B293" s="4"/>
       <c r="C293" s="4"/>
@@ -6153,7 +5943,7 @@
       <c r="F293" s="4"/>
       <c r="G293" s="4"/>
     </row>
-    <row r="294" spans="1:7" ht="15">
+    <row r="294" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A294" s="4"/>
       <c r="B294" s="4"/>
       <c r="C294" s="4"/>
@@ -6161,7 +5951,7 @@
       <c r="F294" s="4"/>
       <c r="G294" s="4"/>
     </row>
-    <row r="295" spans="1:7" ht="15">
+    <row r="295" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A295" s="4"/>
       <c r="B295" s="4"/>
       <c r="C295" s="4"/>
@@ -6169,7 +5959,7 @@
       <c r="F295" s="4"/>
       <c r="G295" s="4"/>
     </row>
-    <row r="296" spans="1:7" ht="15">
+    <row r="296" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A296" s="4"/>
       <c r="B296" s="4"/>
       <c r="C296" s="4"/>
@@ -6177,7 +5967,7 @@
       <c r="F296" s="4"/>
       <c r="G296" s="4"/>
     </row>
-    <row r="297" spans="1:7" ht="15">
+    <row r="297" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A297" s="4"/>
       <c r="B297" s="4"/>
       <c r="C297" s="4"/>
@@ -6185,7 +5975,7 @@
       <c r="F297" s="4"/>
       <c r="G297" s="4"/>
     </row>
-    <row r="298" spans="1:7" ht="15">
+    <row r="298" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A298" s="4"/>
       <c r="B298" s="4"/>
       <c r="C298" s="4"/>
@@ -6193,7 +5983,7 @@
       <c r="F298" s="4"/>
       <c r="G298" s="4"/>
     </row>
-    <row r="299" spans="1:7" ht="15">
+    <row r="299" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A299" s="4"/>
       <c r="B299" s="4"/>
       <c r="C299" s="4"/>
@@ -6201,7 +5991,7 @@
       <c r="F299" s="4"/>
       <c r="G299" s="4"/>
     </row>
-    <row r="300" spans="1:7" ht="15">
+    <row r="300" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A300" s="4"/>
       <c r="B300" s="4"/>
       <c r="C300" s="4"/>
@@ -6209,7 +5999,7 @@
       <c r="F300" s="4"/>
       <c r="G300" s="4"/>
     </row>
-    <row r="301" spans="1:7" ht="15">
+    <row r="301" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A301" s="4"/>
       <c r="B301" s="4"/>
       <c r="C301" s="4"/>
@@ -6217,7 +6007,7 @@
       <c r="F301" s="4"/>
       <c r="G301" s="4"/>
     </row>
-    <row r="302" spans="1:7" ht="15">
+    <row r="302" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A302" s="4"/>
       <c r="B302" s="4"/>
       <c r="C302" s="4"/>
@@ -6225,7 +6015,7 @@
       <c r="F302" s="4"/>
       <c r="G302" s="4"/>
     </row>
-    <row r="303" spans="1:7" ht="15">
+    <row r="303" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A303" s="4"/>
       <c r="B303" s="4"/>
       <c r="C303" s="4"/>
@@ -6233,7 +6023,7 @@
       <c r="F303" s="4"/>
       <c r="G303" s="4"/>
     </row>
-    <row r="304" spans="1:7" ht="15">
+    <row r="304" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A304" s="4"/>
       <c r="B304" s="4"/>
       <c r="C304" s="4"/>
@@ -6241,7 +6031,7 @@
       <c r="F304" s="4"/>
       <c r="G304" s="4"/>
     </row>
-    <row r="305" spans="1:7" ht="15">
+    <row r="305" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A305" s="4"/>
       <c r="B305" s="4"/>
       <c r="C305" s="4"/>
@@ -6249,7 +6039,7 @@
       <c r="F305" s="4"/>
       <c r="G305" s="4"/>
     </row>
-    <row r="306" spans="1:7" ht="15">
+    <row r="306" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A306" s="4"/>
       <c r="B306" s="4"/>
       <c r="C306" s="4"/>
@@ -6257,7 +6047,7 @@
       <c r="F306" s="4"/>
       <c r="G306" s="4"/>
     </row>
-    <row r="307" spans="1:7" ht="15">
+    <row r="307" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A307" s="4"/>
       <c r="B307" s="4"/>
       <c r="C307" s="4"/>
@@ -6265,7 +6055,7 @@
       <c r="F307" s="4"/>
       <c r="G307" s="4"/>
     </row>
-    <row r="308" spans="1:7" ht="15">
+    <row r="308" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A308" s="4"/>
       <c r="B308" s="4"/>
       <c r="C308" s="4"/>
@@ -6273,7 +6063,7 @@
       <c r="F308" s="4"/>
       <c r="G308" s="4"/>
     </row>
-    <row r="309" spans="1:7" ht="15">
+    <row r="309" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A309" s="4"/>
       <c r="B309" s="4"/>
       <c r="C309" s="4"/>
@@ -6281,7 +6071,7 @@
       <c r="F309" s="4"/>
       <c r="G309" s="4"/>
     </row>
-    <row r="310" spans="1:7" ht="15">
+    <row r="310" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A310" s="4"/>
       <c r="B310" s="4"/>
       <c r="C310" s="4"/>
@@ -6289,7 +6079,7 @@
       <c r="F310" s="4"/>
       <c r="G310" s="4"/>
     </row>
-    <row r="311" spans="1:7" ht="15">
+    <row r="311" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A311" s="4"/>
       <c r="B311" s="4"/>
       <c r="C311" s="4"/>
@@ -6297,7 +6087,7 @@
       <c r="F311" s="4"/>
       <c r="G311" s="4"/>
     </row>
-    <row r="312" spans="1:7" ht="15">
+    <row r="312" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A312" s="4"/>
       <c r="B312" s="4"/>
       <c r="C312" s="4"/>
@@ -6305,7 +6095,7 @@
       <c r="F312" s="4"/>
       <c r="G312" s="4"/>
     </row>
-    <row r="313" spans="1:7" ht="15">
+    <row r="313" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A313" s="4"/>
       <c r="B313" s="4"/>
       <c r="C313" s="4"/>
@@ -6313,7 +6103,7 @@
       <c r="F313" s="4"/>
       <c r="G313" s="4"/>
     </row>
-    <row r="314" spans="1:7" ht="15">
+    <row r="314" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A314" s="4"/>
       <c r="B314" s="4"/>
       <c r="C314" s="4"/>
@@ -6321,7 +6111,7 @@
       <c r="F314" s="4"/>
       <c r="G314" s="4"/>
     </row>
-    <row r="315" spans="1:7" ht="15">
+    <row r="315" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A315" s="4"/>
       <c r="B315" s="4"/>
       <c r="C315" s="4"/>
@@ -6329,7 +6119,7 @@
       <c r="F315" s="4"/>
       <c r="G315" s="4"/>
     </row>
-    <row r="316" spans="1:7" ht="15">
+    <row r="316" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A316" s="4"/>
       <c r="B316" s="4"/>
       <c r="C316" s="4"/>
@@ -6337,7 +6127,7 @@
       <c r="F316" s="4"/>
       <c r="G316" s="4"/>
     </row>
-    <row r="317" spans="1:7" ht="15">
+    <row r="317" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A317" s="4"/>
       <c r="B317" s="4"/>
       <c r="C317" s="4"/>
@@ -6345,7 +6135,7 @@
       <c r="F317" s="4"/>
       <c r="G317" s="4"/>
     </row>
-    <row r="318" spans="1:7" ht="15">
+    <row r="318" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A318" s="4"/>
       <c r="B318" s="4"/>
       <c r="C318" s="4"/>
@@ -6353,7 +6143,7 @@
       <c r="F318" s="4"/>
       <c r="G318" s="4"/>
     </row>
-    <row r="319" spans="1:7" ht="15">
+    <row r="319" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A319" s="4"/>
       <c r="B319" s="4"/>
       <c r="C319" s="4"/>
@@ -6361,7 +6151,7 @@
       <c r="F319" s="4"/>
       <c r="G319" s="4"/>
     </row>
-    <row r="320" spans="1:7" ht="15">
+    <row r="320" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A320" s="4"/>
       <c r="B320" s="4"/>
       <c r="C320" s="4"/>
@@ -6369,7 +6159,7 @@
       <c r="F320" s="4"/>
       <c r="G320" s="4"/>
     </row>
-    <row r="321" spans="1:7" ht="15">
+    <row r="321" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A321" s="4"/>
       <c r="B321" s="4"/>
       <c r="C321" s="4"/>
@@ -6377,7 +6167,7 @@
       <c r="F321" s="4"/>
       <c r="G321" s="4"/>
     </row>
-    <row r="322" spans="1:7" ht="15">
+    <row r="322" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A322" s="4"/>
       <c r="B322" s="4"/>
       <c r="C322" s="4"/>
@@ -6385,7 +6175,7 @@
       <c r="F322" s="4"/>
       <c r="G322" s="4"/>
     </row>
-    <row r="323" spans="1:7" ht="15">
+    <row r="323" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A323" s="4"/>
       <c r="B323" s="4"/>
       <c r="C323" s="4"/>
@@ -6393,7 +6183,7 @@
       <c r="F323" s="4"/>
       <c r="G323" s="4"/>
     </row>
-    <row r="324" spans="1:7" ht="15">
+    <row r="324" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A324" s="4"/>
       <c r="B324" s="4"/>
       <c r="C324" s="4"/>
@@ -6401,7 +6191,7 @@
       <c r="F324" s="4"/>
       <c r="G324" s="4"/>
     </row>
-    <row r="325" spans="1:7" ht="15">
+    <row r="325" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A325" s="4"/>
       <c r="B325" s="4"/>
       <c r="C325" s="4"/>
@@ -6409,7 +6199,7 @@
       <c r="F325" s="4"/>
       <c r="G325" s="4"/>
     </row>
-    <row r="326" spans="1:7" ht="15">
+    <row r="326" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A326" s="4"/>
       <c r="B326" s="4"/>
       <c r="C326" s="4"/>
@@ -6417,7 +6207,7 @@
       <c r="F326" s="4"/>
       <c r="G326" s="4"/>
     </row>
-    <row r="327" spans="1:7" ht="15">
+    <row r="327" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A327" s="4"/>
       <c r="B327" s="4"/>
       <c r="C327" s="4"/>
@@ -6425,7 +6215,7 @@
       <c r="F327" s="4"/>
       <c r="G327" s="4"/>
     </row>
-    <row r="328" spans="1:7" ht="15">
+    <row r="328" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A328" s="4"/>
       <c r="B328" s="4"/>
       <c r="C328" s="4"/>
@@ -6433,7 +6223,7 @@
       <c r="F328" s="4"/>
       <c r="G328" s="4"/>
     </row>
-    <row r="329" spans="1:7" ht="15">
+    <row r="329" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A329" s="4"/>
       <c r="B329" s="4"/>
       <c r="C329" s="4"/>
@@ -6441,7 +6231,7 @@
       <c r="F329" s="4"/>
       <c r="G329" s="4"/>
     </row>
-    <row r="330" spans="1:7" ht="15">
+    <row r="330" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A330" s="4"/>
       <c r="B330" s="4"/>
       <c r="C330" s="4"/>
@@ -6449,7 +6239,7 @@
       <c r="F330" s="4"/>
       <c r="G330" s="4"/>
     </row>
-    <row r="331" spans="1:7" ht="15">
+    <row r="331" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A331" s="4"/>
       <c r="B331" s="4"/>
       <c r="C331" s="4"/>
@@ -6457,7 +6247,7 @@
       <c r="F331" s="4"/>
       <c r="G331" s="4"/>
     </row>
-    <row r="332" spans="1:7" ht="15">
+    <row r="332" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A332" s="4"/>
       <c r="B332" s="4"/>
       <c r="C332" s="4"/>
@@ -6465,7 +6255,7 @@
       <c r="F332" s="4"/>
       <c r="G332" s="4"/>
     </row>
-    <row r="333" spans="1:7" ht="15">
+    <row r="333" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A333" s="4"/>
       <c r="B333" s="4"/>
       <c r="C333" s="4"/>
@@ -6473,7 +6263,7 @@
       <c r="F333" s="4"/>
       <c r="G333" s="4"/>
     </row>
-    <row r="334" spans="1:7" ht="15">
+    <row r="334" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A334" s="4"/>
       <c r="B334" s="4"/>
       <c r="C334" s="4"/>
@@ -6481,7 +6271,7 @@
       <c r="F334" s="4"/>
       <c r="G334" s="4"/>
     </row>
-    <row r="335" spans="1:7" ht="15">
+    <row r="335" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A335" s="4"/>
       <c r="B335" s="4"/>
       <c r="C335" s="4"/>
@@ -6489,7 +6279,7 @@
       <c r="F335" s="4"/>
       <c r="G335" s="4"/>
     </row>
-    <row r="336" spans="1:7" ht="15">
+    <row r="336" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A336" s="4"/>
       <c r="B336" s="4"/>
       <c r="C336" s="4"/>
@@ -6497,7 +6287,7 @@
       <c r="F336" s="4"/>
       <c r="G336" s="4"/>
     </row>
-    <row r="337" spans="1:7" ht="15">
+    <row r="337" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A337" s="4"/>
       <c r="B337" s="4"/>
       <c r="C337" s="4"/>
@@ -6505,7 +6295,7 @@
       <c r="F337" s="4"/>
       <c r="G337" s="4"/>
     </row>
-    <row r="338" spans="1:7" ht="15">
+    <row r="338" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A338" s="4"/>
       <c r="B338" s="4"/>
       <c r="C338" s="4"/>
@@ -6513,7 +6303,7 @@
       <c r="F338" s="4"/>
       <c r="G338" s="4"/>
     </row>
-    <row r="339" spans="1:7" ht="15">
+    <row r="339" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A339" s="4"/>
       <c r="B339" s="4"/>
       <c r="C339" s="4"/>
@@ -6521,7 +6311,7 @@
       <c r="F339" s="4"/>
       <c r="G339" s="4"/>
     </row>
-    <row r="340" spans="1:7" ht="15">
+    <row r="340" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A340" s="4"/>
       <c r="B340" s="4"/>
       <c r="C340" s="4"/>
@@ -6529,7 +6319,7 @@
       <c r="F340" s="4"/>
       <c r="G340" s="4"/>
     </row>
-    <row r="341" spans="1:7" ht="15">
+    <row r="341" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A341" s="4"/>
       <c r="B341" s="4"/>
       <c r="C341" s="4"/>
@@ -6537,7 +6327,7 @@
       <c r="F341" s="4"/>
       <c r="G341" s="4"/>
     </row>
-    <row r="342" spans="1:7" ht="15">
+    <row r="342" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A342" s="4"/>
       <c r="B342" s="4"/>
       <c r="C342" s="4"/>
@@ -6545,7 +6335,7 @@
       <c r="F342" s="4"/>
       <c r="G342" s="4"/>
     </row>
-    <row r="343" spans="1:7" ht="15">
+    <row r="343" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A343" s="4"/>
       <c r="B343" s="4"/>
       <c r="C343" s="4"/>
@@ -6553,7 +6343,7 @@
       <c r="F343" s="4"/>
       <c r="G343" s="4"/>
     </row>
-    <row r="344" spans="1:7" ht="15">
+    <row r="344" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A344" s="4"/>
       <c r="B344" s="4"/>
       <c r="C344" s="4"/>
@@ -6561,7 +6351,7 @@
       <c r="F344" s="4"/>
       <c r="G344" s="4"/>
     </row>
-    <row r="345" spans="1:7" ht="15">
+    <row r="345" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A345" s="4"/>
       <c r="B345" s="4"/>
       <c r="C345" s="4"/>
@@ -6569,7 +6359,7 @@
       <c r="F345" s="4"/>
       <c r="G345" s="4"/>
     </row>
-    <row r="346" spans="1:7" ht="15">
+    <row r="346" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A346" s="4"/>
       <c r="B346" s="4"/>
       <c r="C346" s="4"/>
@@ -6577,7 +6367,7 @@
       <c r="F346" s="4"/>
       <c r="G346" s="4"/>
     </row>
-    <row r="347" spans="1:7" ht="15">
+    <row r="347" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A347" s="4"/>
       <c r="B347" s="4"/>
       <c r="C347" s="4"/>
@@ -6585,7 +6375,7 @@
       <c r="F347" s="4"/>
       <c r="G347" s="4"/>
     </row>
-    <row r="348" spans="1:7" ht="15">
+    <row r="348" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A348" s="4"/>
       <c r="B348" s="4"/>
       <c r="C348" s="4"/>
@@ -6593,7 +6383,7 @@
       <c r="F348" s="4"/>
       <c r="G348" s="4"/>
     </row>
-    <row r="349" spans="1:7" ht="15">
+    <row r="349" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A349" s="4"/>
       <c r="B349" s="4"/>
       <c r="C349" s="4"/>
@@ -6601,7 +6391,7 @@
       <c r="F349" s="4"/>
       <c r="G349" s="4"/>
     </row>
-    <row r="350" spans="1:7" ht="15">
+    <row r="350" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A350" s="4"/>
       <c r="B350" s="4"/>
       <c r="C350" s="4"/>
@@ -6609,7 +6399,7 @@
       <c r="F350" s="4"/>
       <c r="G350" s="4"/>
     </row>
-    <row r="351" spans="1:7" ht="15">
+    <row r="351" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A351" s="4"/>
       <c r="B351" s="4"/>
       <c r="C351" s="4"/>
@@ -6617,7 +6407,7 @@
       <c r="F351" s="4"/>
       <c r="G351" s="4"/>
     </row>
-    <row r="352" spans="1:7" ht="15">
+    <row r="352" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A352" s="4"/>
       <c r="B352" s="4"/>
       <c r="C352" s="4"/>
@@ -6625,7 +6415,7 @@
       <c r="F352" s="4"/>
       <c r="G352" s="4"/>
     </row>
-    <row r="353" spans="1:7" ht="15">
+    <row r="353" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A353" s="4"/>
       <c r="B353" s="4"/>
       <c r="C353" s="4"/>
@@ -6633,7 +6423,7 @@
       <c r="F353" s="4"/>
       <c r="G353" s="4"/>
     </row>
-    <row r="354" spans="1:7" ht="15">
+    <row r="354" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A354" s="4"/>
       <c r="B354" s="4"/>
       <c r="C354" s="4"/>
@@ -6641,7 +6431,7 @@
       <c r="F354" s="4"/>
       <c r="G354" s="4"/>
     </row>
-    <row r="355" spans="1:7" ht="15">
+    <row r="355" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A355" s="4"/>
       <c r="B355" s="4"/>
       <c r="C355" s="4"/>
@@ -6649,7 +6439,7 @@
       <c r="F355" s="4"/>
       <c r="G355" s="4"/>
     </row>
-    <row r="356" spans="1:7" ht="15">
+    <row r="356" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A356" s="4"/>
       <c r="B356" s="4"/>
       <c r="C356" s="4"/>
@@ -6657,7 +6447,7 @@
       <c r="F356" s="4"/>
       <c r="G356" s="4"/>
     </row>
-    <row r="357" spans="1:7" ht="15">
+    <row r="357" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A357" s="4"/>
       <c r="B357" s="4"/>
       <c r="C357" s="4"/>
@@ -6665,7 +6455,7 @@
       <c r="F357" s="4"/>
       <c r="G357" s="4"/>
     </row>
-    <row r="358" spans="1:7" ht="15">
+    <row r="358" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A358" s="4"/>
       <c r="B358" s="4"/>
       <c r="C358" s="4"/>
@@ -6673,7 +6463,7 @@
       <c r="F358" s="4"/>
       <c r="G358" s="4"/>
     </row>
-    <row r="359" spans="1:7" ht="15">
+    <row r="359" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A359" s="4"/>
       <c r="B359" s="4"/>
       <c r="C359" s="4"/>
@@ -6681,7 +6471,7 @@
       <c r="F359" s="4"/>
       <c r="G359" s="4"/>
     </row>
-    <row r="360" spans="1:7" ht="15">
+    <row r="360" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A360" s="4"/>
       <c r="B360" s="4"/>
       <c r="C360" s="4"/>
@@ -6689,7 +6479,7 @@
       <c r="F360" s="4"/>
       <c r="G360" s="4"/>
     </row>
-    <row r="361" spans="1:7" ht="15">
+    <row r="361" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A361" s="4"/>
       <c r="B361" s="4"/>
       <c r="C361" s="4"/>
@@ -6697,7 +6487,7 @@
       <c r="F361" s="4"/>
       <c r="G361" s="4"/>
     </row>
-    <row r="362" spans="1:7" ht="15">
+    <row r="362" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A362" s="4"/>
       <c r="B362" s="4"/>
       <c r="C362" s="4"/>
@@ -6705,7 +6495,7 @@
       <c r="F362" s="4"/>
       <c r="G362" s="4"/>
     </row>
-    <row r="363" spans="1:7" ht="15">
+    <row r="363" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A363" s="4"/>
       <c r="B363" s="4"/>
       <c r="C363" s="4"/>
@@ -6713,7 +6503,7 @@
       <c r="F363" s="4"/>
       <c r="G363" s="4"/>
     </row>
-    <row r="364" spans="1:7" ht="15">
+    <row r="364" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A364" s="4"/>
       <c r="B364" s="4"/>
       <c r="C364" s="4"/>
@@ -6721,7 +6511,7 @@
       <c r="F364" s="4"/>
       <c r="G364" s="4"/>
     </row>
-    <row r="365" spans="1:7" ht="15">
+    <row r="365" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A365" s="4"/>
       <c r="B365" s="4"/>
       <c r="C365" s="4"/>
@@ -6729,7 +6519,7 @@
       <c r="F365" s="4"/>
       <c r="G365" s="4"/>
     </row>
-    <row r="366" spans="1:7" ht="15">
+    <row r="366" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A366" s="4"/>
       <c r="B366" s="4"/>
       <c r="C366" s="4"/>
@@ -6737,7 +6527,7 @@
       <c r="F366" s="4"/>
       <c r="G366" s="4"/>
     </row>
-    <row r="367" spans="1:7" ht="15">
+    <row r="367" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A367" s="4"/>
       <c r="B367" s="4"/>
       <c r="C367" s="4"/>
@@ -6745,7 +6535,7 @@
       <c r="F367" s="4"/>
       <c r="G367" s="4"/>
     </row>
-    <row r="368" spans="1:7" ht="15">
+    <row r="368" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A368" s="4"/>
       <c r="B368" s="4"/>
       <c r="C368" s="4"/>
@@ -6753,7 +6543,7 @@
       <c r="F368" s="4"/>
       <c r="G368" s="4"/>
     </row>
-    <row r="369" spans="1:7" ht="15">
+    <row r="369" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A369" s="4"/>
       <c r="B369" s="4"/>
       <c r="C369" s="4"/>
@@ -6761,7 +6551,7 @@
       <c r="F369" s="4"/>
       <c r="G369" s="4"/>
     </row>
-    <row r="370" spans="1:7" ht="15">
+    <row r="370" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A370" s="4"/>
       <c r="B370" s="4"/>
       <c r="C370" s="4"/>
@@ -6769,7 +6559,7 @@
       <c r="F370" s="4"/>
       <c r="G370" s="4"/>
     </row>
-    <row r="371" spans="1:7" ht="15">
+    <row r="371" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A371" s="4"/>
       <c r="B371" s="4"/>
       <c r="C371" s="4"/>
@@ -6777,7 +6567,7 @@
       <c r="F371" s="4"/>
       <c r="G371" s="4"/>
     </row>
-    <row r="372" spans="1:7" ht="15">
+    <row r="372" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A372" s="4"/>
       <c r="B372" s="4"/>
       <c r="C372" s="4"/>
@@ -6785,7 +6575,7 @@
       <c r="F372" s="4"/>
       <c r="G372" s="4"/>
     </row>
-    <row r="373" spans="1:7" ht="15">
+    <row r="373" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A373" s="4"/>
       <c r="B373" s="4"/>
       <c r="C373" s="4"/>
@@ -6793,7 +6583,7 @@
       <c r="F373" s="4"/>
       <c r="G373" s="4"/>
     </row>
-    <row r="374" spans="1:7" ht="15">
+    <row r="374" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A374" s="4"/>
       <c r="B374" s="4"/>
       <c r="C374" s="4"/>
@@ -6801,7 +6591,7 @@
       <c r="F374" s="4"/>
       <c r="G374" s="4"/>
     </row>
-    <row r="375" spans="1:7" ht="15">
+    <row r="375" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A375" s="4"/>
       <c r="B375" s="4"/>
       <c r="C375" s="4"/>
@@ -6809,7 +6599,7 @@
       <c r="F375" s="4"/>
       <c r="G375" s="4"/>
     </row>
-    <row r="376" spans="1:7" ht="15">
+    <row r="376" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A376" s="4"/>
       <c r="B376" s="4"/>
       <c r="C376" s="4"/>
@@ -6817,7 +6607,7 @@
       <c r="F376" s="4"/>
       <c r="G376" s="4"/>
     </row>
-    <row r="377" spans="1:7" ht="15">
+    <row r="377" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A377" s="4"/>
       <c r="B377" s="4"/>
       <c r="C377" s="4"/>
@@ -6825,7 +6615,7 @@
       <c r="F377" s="4"/>
       <c r="G377" s="4"/>
     </row>
-    <row r="378" spans="1:7" ht="15">
+    <row r="378" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A378" s="4"/>
       <c r="B378" s="4"/>
       <c r="C378" s="4"/>
@@ -6833,7 +6623,7 @@
       <c r="F378" s="4"/>
       <c r="G378" s="4"/>
     </row>
-    <row r="379" spans="1:7" ht="15">
+    <row r="379" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A379" s="4"/>
       <c r="B379" s="4"/>
       <c r="C379" s="4"/>
@@ -6841,7 +6631,7 @@
       <c r="F379" s="4"/>
       <c r="G379" s="4"/>
     </row>
-    <row r="380" spans="1:7" ht="15">
+    <row r="380" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A380" s="4"/>
       <c r="B380" s="4"/>
       <c r="C380" s="4"/>
@@ -6849,7 +6639,7 @@
       <c r="F380" s="4"/>
       <c r="G380" s="4"/>
     </row>
-    <row r="381" spans="1:7" ht="15">
+    <row r="381" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A381" s="4"/>
       <c r="B381" s="4"/>
       <c r="C381" s="4"/>
@@ -6857,7 +6647,7 @@
       <c r="F381" s="4"/>
       <c r="G381" s="4"/>
     </row>
-    <row r="382" spans="1:7" ht="15">
+    <row r="382" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A382" s="4"/>
       <c r="B382" s="4"/>
       <c r="C382" s="4"/>
@@ -6865,7 +6655,7 @@
       <c r="F382" s="4"/>
       <c r="G382" s="4"/>
     </row>
-    <row r="383" spans="1:7" ht="15">
+    <row r="383" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A383" s="4"/>
       <c r="B383" s="4"/>
       <c r="C383" s="4"/>
@@ -6873,7 +6663,7 @@
       <c r="F383" s="4"/>
       <c r="G383" s="4"/>
     </row>
-    <row r="384" spans="1:7" ht="15">
+    <row r="384" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A384" s="4"/>
       <c r="B384" s="4"/>
       <c r="C384" s="4"/>
@@ -6881,7 +6671,7 @@
       <c r="F384" s="4"/>
       <c r="G384" s="4"/>
     </row>
-    <row r="385" spans="1:7" ht="15">
+    <row r="385" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A385" s="4"/>
       <c r="B385" s="4"/>
       <c r="C385" s="4"/>
@@ -6889,7 +6679,7 @@
       <c r="F385" s="4"/>
       <c r="G385" s="4"/>
     </row>
-    <row r="386" spans="1:7" ht="15">
+    <row r="386" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A386" s="4"/>
       <c r="B386" s="4"/>
       <c r="C386" s="4"/>
@@ -6897,7 +6687,7 @@
       <c r="F386" s="4"/>
       <c r="G386" s="4"/>
     </row>
-    <row r="387" spans="1:7" ht="15">
+    <row r="387" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A387" s="4"/>
       <c r="B387" s="4"/>
       <c r="C387" s="4"/>
@@ -6905,7 +6695,7 @@
       <c r="F387" s="4"/>
       <c r="G387" s="4"/>
     </row>
-    <row r="388" spans="1:7" ht="15">
+    <row r="388" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A388" s="4"/>
       <c r="B388" s="4"/>
       <c r="C388" s="4"/>
@@ -6913,7 +6703,7 @@
       <c r="F388" s="4"/>
       <c r="G388" s="4"/>
     </row>
-    <row r="389" spans="1:7" ht="15">
+    <row r="389" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A389" s="4"/>
       <c r="B389" s="4"/>
       <c r="C389" s="4"/>
@@ -6921,7 +6711,7 @@
       <c r="F389" s="4"/>
       <c r="G389" s="4"/>
     </row>
-    <row r="390" spans="1:7" ht="15">
+    <row r="390" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A390" s="4"/>
       <c r="B390" s="4"/>
       <c r="C390" s="4"/>
@@ -6929,7 +6719,7 @@
       <c r="F390" s="4"/>
       <c r="G390" s="4"/>
     </row>
-    <row r="391" spans="1:7" ht="15">
+    <row r="391" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A391" s="4"/>
       <c r="B391" s="4"/>
       <c r="C391" s="4"/>
@@ -6937,7 +6727,7 @@
       <c r="F391" s="4"/>
       <c r="G391" s="4"/>
     </row>
-    <row r="392" spans="1:7" ht="15">
+    <row r="392" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A392" s="4"/>
       <c r="B392" s="4"/>
       <c r="C392" s="4"/>
@@ -6945,7 +6735,7 @@
       <c r="F392" s="4"/>
       <c r="G392" s="4"/>
     </row>
-    <row r="393" spans="1:7" ht="15">
+    <row r="393" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A393" s="4"/>
       <c r="B393" s="4"/>
       <c r="C393" s="4"/>
@@ -6953,7 +6743,7 @@
       <c r="F393" s="4"/>
       <c r="G393" s="4"/>
     </row>
-    <row r="394" spans="1:7" ht="15">
+    <row r="394" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A394" s="4"/>
       <c r="B394" s="4"/>
       <c r="C394" s="4"/>
@@ -6961,7 +6751,7 @@
       <c r="F394" s="4"/>
       <c r="G394" s="4"/>
     </row>
-    <row r="395" spans="1:7" ht="15">
+    <row r="395" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A395" s="4"/>
       <c r="B395" s="4"/>
       <c r="C395" s="4"/>
@@ -6969,7 +6759,7 @@
       <c r="F395" s="4"/>
       <c r="G395" s="4"/>
     </row>
-    <row r="396" spans="1:7" ht="15">
+    <row r="396" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A396" s="4"/>
       <c r="B396" s="4"/>
       <c r="C396" s="4"/>
@@ -6977,7 +6767,7 @@
       <c r="F396" s="4"/>
       <c r="G396" s="4"/>
     </row>
-    <row r="397" spans="1:7" ht="15">
+    <row r="397" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A397" s="4"/>
       <c r="B397" s="4"/>
       <c r="C397" s="4"/>
@@ -6985,7 +6775,7 @@
       <c r="F397" s="4"/>
       <c r="G397" s="4"/>
     </row>
-    <row r="398" spans="1:7" ht="15">
+    <row r="398" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A398" s="4"/>
       <c r="B398" s="4"/>
       <c r="C398" s="4"/>
@@ -6993,7 +6783,7 @@
       <c r="F398" s="4"/>
       <c r="G398" s="4"/>
     </row>
-    <row r="399" spans="1:7" ht="15">
+    <row r="399" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A399" s="4"/>
       <c r="B399" s="4"/>
       <c r="C399" s="4"/>
@@ -7001,7 +6791,7 @@
       <c r="F399" s="4"/>
       <c r="G399" s="4"/>
     </row>
-    <row r="400" spans="1:7" ht="15">
+    <row r="400" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A400" s="4"/>
       <c r="B400" s="4"/>
       <c r="C400" s="4"/>
@@ -7009,7 +6799,7 @@
       <c r="F400" s="4"/>
       <c r="G400" s="4"/>
     </row>
-    <row r="401" spans="1:7" ht="15">
+    <row r="401" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A401" s="4"/>
       <c r="B401" s="4"/>
       <c r="C401" s="4"/>
@@ -7017,7 +6807,7 @@
       <c r="F401" s="4"/>
       <c r="G401" s="4"/>
     </row>
-    <row r="402" spans="1:7" ht="15">
+    <row r="402" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A402" s="4"/>
       <c r="B402" s="4"/>
       <c r="C402" s="4"/>
@@ -7025,7 +6815,7 @@
       <c r="F402" s="4"/>
       <c r="G402" s="4"/>
     </row>
-    <row r="403" spans="1:7" ht="15">
+    <row r="403" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A403" s="4"/>
       <c r="B403" s="4"/>
       <c r="C403" s="4"/>
@@ -7033,7 +6823,7 @@
       <c r="F403" s="4"/>
       <c r="G403" s="4"/>
     </row>
-    <row r="404" spans="1:7" ht="15">
+    <row r="404" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A404" s="4"/>
       <c r="B404" s="4"/>
       <c r="C404" s="4"/>
@@ -7041,7 +6831,7 @@
       <c r="F404" s="4"/>
       <c r="G404" s="4"/>
     </row>
-    <row r="405" spans="1:7" ht="15">
+    <row r="405" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A405" s="4"/>
       <c r="B405" s="4"/>
       <c r="C405" s="4"/>
@@ -7049,7 +6839,7 @@
       <c r="F405" s="4"/>
       <c r="G405" s="4"/>
     </row>
-    <row r="406" spans="1:7" ht="15">
+    <row r="406" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A406" s="4"/>
       <c r="B406" s="4"/>
       <c r="C406" s="4"/>
@@ -7057,7 +6847,7 @@
       <c r="F406" s="4"/>
       <c r="G406" s="4"/>
     </row>
-    <row r="407" spans="1:7" ht="15">
+    <row r="407" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A407" s="4"/>
       <c r="B407" s="4"/>
       <c r="C407" s="4"/>
@@ -7065,7 +6855,7 @@
       <c r="F407" s="4"/>
       <c r="G407" s="4"/>
     </row>
-    <row r="408" spans="1:7" ht="15">
+    <row r="408" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A408" s="4"/>
       <c r="B408" s="4"/>
       <c r="C408" s="4"/>
@@ -7073,7 +6863,7 @@
       <c r="F408" s="4"/>
       <c r="G408" s="4"/>
     </row>
-    <row r="409" spans="1:7" ht="15">
+    <row r="409" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A409" s="4"/>
       <c r="B409" s="4"/>
       <c r="C409" s="4"/>
@@ -7081,7 +6871,7 @@
       <c r="F409" s="4"/>
       <c r="G409" s="4"/>
     </row>
-    <row r="410" spans="1:7" ht="15">
+    <row r="410" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A410" s="4"/>
       <c r="B410" s="4"/>
       <c r="C410" s="4"/>
@@ -7089,7 +6879,7 @@
       <c r="F410" s="4"/>
       <c r="G410" s="4"/>
     </row>
-    <row r="411" spans="1:7" ht="15">
+    <row r="411" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A411" s="4"/>
       <c r="B411" s="4"/>
       <c r="C411" s="4"/>
@@ -7097,7 +6887,7 @@
       <c r="F411" s="4"/>
       <c r="G411" s="4"/>
     </row>
-    <row r="412" spans="1:7" ht="15">
+    <row r="412" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A412" s="4"/>
       <c r="B412" s="4"/>
       <c r="C412" s="4"/>
@@ -7105,7 +6895,7 @@
       <c r="F412" s="4"/>
       <c r="G412" s="4"/>
     </row>
-    <row r="413" spans="1:7" ht="15">
+    <row r="413" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A413" s="4"/>
       <c r="B413" s="4"/>
       <c r="C413" s="4"/>
@@ -7113,7 +6903,7 @@
       <c r="F413" s="4"/>
       <c r="G413" s="4"/>
     </row>
-    <row r="414" spans="1:7" ht="15">
+    <row r="414" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A414" s="4"/>
       <c r="B414" s="4"/>
       <c r="C414" s="4"/>
@@ -7121,7 +6911,7 @@
       <c r="F414" s="4"/>
       <c r="G414" s="4"/>
     </row>
-    <row r="415" spans="1:7" ht="15">
+    <row r="415" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A415" s="4"/>
       <c r="B415" s="4"/>
       <c r="C415" s="4"/>
@@ -7129,7 +6919,7 @@
       <c r="F415" s="4"/>
       <c r="G415" s="4"/>
     </row>
-    <row r="416" spans="1:7" ht="15">
+    <row r="416" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A416" s="4"/>
       <c r="B416" s="4"/>
       <c r="C416" s="4"/>
@@ -7137,7 +6927,7 @@
       <c r="F416" s="4"/>
       <c r="G416" s="4"/>
     </row>
-    <row r="417" spans="1:7" ht="15">
+    <row r="417" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A417" s="4"/>
       <c r="B417" s="4"/>
       <c r="C417" s="4"/>
@@ -7145,7 +6935,7 @@
       <c r="F417" s="4"/>
       <c r="G417" s="4"/>
     </row>
-    <row r="418" spans="1:7" ht="15">
+    <row r="418" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A418" s="4"/>
       <c r="B418" s="4"/>
       <c r="C418" s="4"/>
@@ -7153,7 +6943,7 @@
       <c r="F418" s="4"/>
       <c r="G418" s="4"/>
     </row>
-    <row r="419" spans="1:7" ht="15">
+    <row r="419" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A419" s="4"/>
       <c r="B419" s="4"/>
       <c r="C419" s="4"/>
@@ -7161,7 +6951,7 @@
       <c r="F419" s="4"/>
       <c r="G419" s="4"/>
     </row>
-    <row r="420" spans="1:7" ht="15">
+    <row r="420" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A420" s="4"/>
       <c r="B420" s="4"/>
       <c r="C420" s="4"/>
@@ -7169,7 +6959,7 @@
       <c r="F420" s="4"/>
       <c r="G420" s="4"/>
     </row>
-    <row r="421" spans="1:7" ht="15">
+    <row r="421" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A421" s="4"/>
       <c r="B421" s="4"/>
       <c r="C421" s="4"/>
@@ -7177,7 +6967,7 @@
       <c r="F421" s="4"/>
       <c r="G421" s="4"/>
     </row>
-    <row r="422" spans="1:7" ht="15">
+    <row r="422" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A422" s="4"/>
       <c r="B422" s="4"/>
       <c r="C422" s="4"/>
@@ -7185,7 +6975,7 @@
       <c r="F422" s="4"/>
       <c r="G422" s="4"/>
     </row>
-    <row r="423" spans="1:7" ht="15">
+    <row r="423" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A423" s="4"/>
       <c r="B423" s="4"/>
       <c r="C423" s="4"/>
@@ -7193,7 +6983,7 @@
       <c r="F423" s="4"/>
       <c r="G423" s="4"/>
     </row>
-    <row r="424" spans="1:7" ht="15">
+    <row r="424" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A424" s="4"/>
       <c r="B424" s="4"/>
       <c r="C424" s="4"/>
@@ -7201,7 +6991,7 @@
       <c r="F424" s="4"/>
       <c r="G424" s="4"/>
     </row>
-    <row r="425" spans="1:7" ht="15">
+    <row r="425" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A425" s="4"/>
       <c r="B425" s="4"/>
       <c r="C425" s="4"/>
@@ -7209,7 +6999,7 @@
       <c r="F425" s="4"/>
       <c r="G425" s="4"/>
     </row>
-    <row r="426" spans="1:7" ht="15">
+    <row r="426" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A426" s="4"/>
       <c r="B426" s="4"/>
       <c r="C426" s="4"/>
@@ -7217,7 +7007,7 @@
       <c r="F426" s="4"/>
       <c r="G426" s="4"/>
     </row>
-    <row r="427" spans="1:7" ht="15">
+    <row r="427" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A427" s="4"/>
       <c r="B427" s="4"/>
       <c r="C427" s="4"/>
@@ -7225,7 +7015,7 @@
       <c r="F427" s="4"/>
       <c r="G427" s="4"/>
     </row>
-    <row r="428" spans="1:7" ht="15">
+    <row r="428" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A428" s="4"/>
       <c r="B428" s="4"/>
       <c r="C428" s="4"/>
@@ -7233,7 +7023,7 @@
       <c r="F428" s="4"/>
       <c r="G428" s="4"/>
     </row>
-    <row r="429" spans="1:7" ht="15">
+    <row r="429" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A429" s="4"/>
       <c r="B429" s="4"/>
       <c r="C429" s="4"/>
@@ -7241,7 +7031,7 @@
       <c r="F429" s="4"/>
       <c r="G429" s="4"/>
     </row>
-    <row r="430" spans="1:7" ht="15">
+    <row r="430" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A430" s="4"/>
       <c r="B430" s="4"/>
       <c r="C430" s="4"/>
@@ -7249,7 +7039,7 @@
       <c r="F430" s="4"/>
       <c r="G430" s="4"/>
     </row>
-    <row r="431" spans="1:7" ht="15">
+    <row r="431" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A431" s="4"/>
       <c r="B431" s="4"/>
       <c r="C431" s="4"/>
@@ -7257,7 +7047,7 @@
       <c r="F431" s="4"/>
       <c r="G431" s="4"/>
     </row>
-    <row r="432" spans="1:7" ht="15">
+    <row r="432" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A432" s="4"/>
       <c r="B432" s="4"/>
       <c r="C432" s="4"/>
@@ -7265,7 +7055,7 @@
       <c r="F432" s="4"/>
       <c r="G432" s="4"/>
     </row>
-    <row r="433" spans="1:7" ht="15">
+    <row r="433" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A433" s="4"/>
       <c r="B433" s="4"/>
       <c r="C433" s="4"/>
@@ -7273,7 +7063,7 @@
       <c r="F433" s="4"/>
       <c r="G433" s="4"/>
     </row>
-    <row r="434" spans="1:7" ht="15">
+    <row r="434" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A434" s="4"/>
       <c r="B434" s="4"/>
       <c r="C434" s="4"/>
@@ -7281,7 +7071,7 @@
       <c r="F434" s="4"/>
       <c r="G434" s="4"/>
     </row>
-    <row r="435" spans="1:7" ht="15">
+    <row r="435" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A435" s="4"/>
       <c r="B435" s="4"/>
       <c r="C435" s="4"/>
@@ -7289,7 +7079,7 @@
       <c r="F435" s="4"/>
       <c r="G435" s="4"/>
     </row>
-    <row r="436" spans="1:7" ht="15">
+    <row r="436" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A436" s="4"/>
       <c r="B436" s="4"/>
       <c r="C436" s="4"/>
@@ -7297,7 +7087,7 @@
       <c r="F436" s="4"/>
       <c r="G436" s="4"/>
     </row>
-    <row r="437" spans="1:7" ht="15">
+    <row r="437" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A437" s="4"/>
       <c r="B437" s="4"/>
       <c r="C437" s="4"/>
@@ -7305,7 +7095,7 @@
       <c r="F437" s="4"/>
       <c r="G437" s="4"/>
     </row>
-    <row r="438" spans="1:7" ht="15">
+    <row r="438" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A438" s="4"/>
       <c r="B438" s="4"/>
       <c r="C438" s="4"/>
@@ -7313,7 +7103,7 @@
       <c r="F438" s="4"/>
       <c r="G438" s="4"/>
     </row>
-    <row r="439" spans="1:7" ht="15">
+    <row r="439" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A439" s="4"/>
       <c r="B439" s="4"/>
       <c r="C439" s="4"/>
@@ -7321,7 +7111,7 @@
       <c r="F439" s="4"/>
       <c r="G439" s="4"/>
     </row>
-    <row r="440" spans="1:7" ht="15">
+    <row r="440" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A440" s="4"/>
       <c r="B440" s="4"/>
       <c r="C440" s="4"/>
@@ -7329,7 +7119,7 @@
       <c r="F440" s="4"/>
       <c r="G440" s="4"/>
     </row>
-    <row r="441" spans="1:7" ht="15">
+    <row r="441" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A441" s="4"/>
       <c r="B441" s="4"/>
       <c r="C441" s="4"/>
@@ -7337,7 +7127,7 @@
       <c r="F441" s="4"/>
       <c r="G441" s="4"/>
     </row>
-    <row r="442" spans="1:7" ht="15">
+    <row r="442" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A442" s="4"/>
       <c r="B442" s="4"/>
       <c r="C442" s="4"/>
@@ -7345,7 +7135,7 @@
       <c r="F442" s="4"/>
       <c r="G442" s="4"/>
     </row>
-    <row r="443" spans="1:7" ht="15">
+    <row r="443" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A443" s="4"/>
       <c r="B443" s="4"/>
       <c r="C443" s="4"/>
@@ -7353,7 +7143,7 @@
       <c r="F443" s="4"/>
       <c r="G443" s="4"/>
     </row>
-    <row r="444" spans="1:7" ht="15">
+    <row r="444" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A444" s="4"/>
       <c r="B444" s="4"/>
       <c r="C444" s="4"/>
@@ -7361,7 +7151,7 @@
       <c r="F444" s="4"/>
       <c r="G444" s="4"/>
     </row>
-    <row r="445" spans="1:7" ht="15">
+    <row r="445" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A445" s="4"/>
       <c r="B445" s="4"/>
       <c r="C445" s="4"/>
@@ -7369,7 +7159,7 @@
       <c r="F445" s="4"/>
       <c r="G445" s="4"/>
     </row>
-    <row r="446" spans="1:7" ht="15">
+    <row r="446" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A446" s="4"/>
       <c r="B446" s="4"/>
       <c r="C446" s="4"/>
@@ -7377,7 +7167,7 @@
       <c r="F446" s="4"/>
       <c r="G446" s="4"/>
     </row>
-    <row r="447" spans="1:7" ht="15">
+    <row r="447" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A447" s="4"/>
       <c r="B447" s="4"/>
       <c r="C447" s="4"/>
@@ -7385,7 +7175,7 @@
       <c r="F447" s="4"/>
       <c r="G447" s="4"/>
     </row>
-    <row r="448" spans="1:7" ht="15">
+    <row r="448" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A448" s="4"/>
       <c r="B448" s="4"/>
       <c r="C448" s="4"/>
@@ -7393,7 +7183,7 @@
       <c r="F448" s="4"/>
       <c r="G448" s="4"/>
     </row>
-    <row r="449" spans="1:7" ht="15">
+    <row r="449" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A449" s="4"/>
       <c r="B449" s="4"/>
       <c r="C449" s="4"/>
@@ -7401,7 +7191,7 @@
       <c r="F449" s="4"/>
       <c r="G449" s="4"/>
     </row>
-    <row r="450" spans="1:7" ht="15">
+    <row r="450" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A450" s="4"/>
       <c r="B450" s="4"/>
       <c r="C450" s="4"/>
@@ -7409,7 +7199,7 @@
       <c r="F450" s="4"/>
       <c r="G450" s="4"/>
     </row>
-    <row r="451" spans="1:7" ht="15">
+    <row r="451" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A451" s="4"/>
       <c r="B451" s="4"/>
       <c r="C451" s="4"/>
@@ -7417,7 +7207,7 @@
       <c r="F451" s="4"/>
       <c r="G451" s="4"/>
     </row>
-    <row r="452" spans="1:7" ht="15">
+    <row r="452" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A452" s="4"/>
       <c r="B452" s="4"/>
       <c r="C452" s="4"/>
@@ -7425,7 +7215,7 @@
       <c r="F452" s="4"/>
       <c r="G452" s="4"/>
     </row>
-    <row r="453" spans="1:7" ht="15">
+    <row r="453" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A453" s="4"/>
       <c r="B453" s="4"/>
       <c r="C453" s="4"/>
@@ -7433,7 +7223,7 @@
       <c r="F453" s="4"/>
       <c r="G453" s="4"/>
     </row>
-    <row r="454" spans="1:7" ht="15">
+    <row r="454" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A454" s="4"/>
       <c r="B454" s="4"/>
       <c r="C454" s="4"/>
@@ -7441,7 +7231,7 @@
       <c r="F454" s="4"/>
       <c r="G454" s="4"/>
     </row>
-    <row r="455" spans="1:7" ht="15">
+    <row r="455" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A455" s="4"/>
       <c r="B455" s="4"/>
       <c r="C455" s="4"/>
@@ -7449,7 +7239,7 @@
       <c r="F455" s="4"/>
       <c r="G455" s="4"/>
     </row>
-    <row r="456" spans="1:7" ht="15">
+    <row r="456" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A456" s="4"/>
       <c r="B456" s="4"/>
       <c r="C456" s="4"/>
@@ -7457,7 +7247,7 @@
       <c r="F456" s="4"/>
       <c r="G456" s="4"/>
     </row>
-    <row r="457" spans="1:7" ht="15">
+    <row r="457" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A457" s="4"/>
       <c r="B457" s="4"/>
       <c r="C457" s="4"/>
@@ -7465,7 +7255,7 @@
       <c r="F457" s="4"/>
       <c r="G457" s="4"/>
     </row>
-    <row r="458" spans="1:7" ht="15">
+    <row r="458" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A458" s="4"/>
       <c r="B458" s="4"/>
       <c r="C458" s="4"/>
@@ -7473,7 +7263,7 @@
       <c r="F458" s="4"/>
       <c r="G458" s="4"/>
     </row>
-    <row r="459" spans="1:7" ht="15">
+    <row r="459" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A459" s="4"/>
       <c r="B459" s="4"/>
       <c r="C459" s="4"/>
@@ -7481,7 +7271,7 @@
       <c r="F459" s="4"/>
       <c r="G459" s="4"/>
     </row>
-    <row r="460" spans="1:7" ht="15">
+    <row r="460" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A460" s="4"/>
       <c r="B460" s="4"/>
       <c r="C460" s="4"/>
@@ -7489,7 +7279,7 @@
       <c r="F460" s="4"/>
       <c r="G460" s="4"/>
     </row>
-    <row r="461" spans="1:7" ht="15">
+    <row r="461" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A461" s="4"/>
       <c r="B461" s="4"/>
       <c r="C461" s="4"/>
@@ -7497,7 +7287,7 @@
       <c r="F461" s="4"/>
       <c r="G461" s="4"/>
     </row>
-    <row r="462" spans="1:7" ht="15">
+    <row r="462" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A462" s="4"/>
       <c r="B462" s="4"/>
       <c r="C462" s="4"/>
@@ -7505,7 +7295,7 @@
       <c r="F462" s="4"/>
       <c r="G462" s="4"/>
     </row>
-    <row r="463" spans="1:7" ht="15">
+    <row r="463" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A463" s="4"/>
       <c r="B463" s="4"/>
       <c r="C463" s="4"/>
@@ -7513,7 +7303,7 @@
       <c r="F463" s="4"/>
       <c r="G463" s="4"/>
     </row>
-    <row r="464" spans="1:7" ht="15">
+    <row r="464" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A464" s="4"/>
       <c r="B464" s="4"/>
       <c r="C464" s="4"/>
@@ -7521,7 +7311,7 @@
       <c r="F464" s="4"/>
       <c r="G464" s="4"/>
     </row>
-    <row r="465" spans="1:7" ht="15">
+    <row r="465" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A465" s="4"/>
       <c r="B465" s="4"/>
       <c r="C465" s="4"/>
@@ -7529,7 +7319,7 @@
       <c r="F465" s="4"/>
       <c r="G465" s="4"/>
     </row>
-    <row r="466" spans="1:7" ht="15">
+    <row r="466" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A466" s="4"/>
       <c r="B466" s="4"/>
       <c r="C466" s="4"/>
@@ -7537,7 +7327,7 @@
       <c r="F466" s="4"/>
       <c r="G466" s="4"/>
     </row>
-    <row r="467" spans="1:7" ht="15">
+    <row r="467" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A467" s="4"/>
       <c r="B467" s="4"/>
       <c r="C467" s="4"/>
@@ -7545,7 +7335,7 @@
       <c r="F467" s="4"/>
       <c r="G467" s="4"/>
     </row>
-    <row r="468" spans="1:7" ht="15">
+    <row r="468" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A468" s="4"/>
       <c r="B468" s="4"/>
       <c r="C468" s="4"/>
@@ -7553,7 +7343,7 @@
       <c r="F468" s="4"/>
       <c r="G468" s="4"/>
     </row>
-    <row r="469" spans="1:7" ht="15">
+    <row r="469" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A469" s="4"/>
       <c r="B469" s="4"/>
       <c r="C469" s="4"/>
@@ -7561,7 +7351,7 @@
       <c r="F469" s="4"/>
       <c r="G469" s="4"/>
     </row>
-    <row r="470" spans="1:7" ht="15">
+    <row r="470" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A470" s="4"/>
       <c r="B470" s="4"/>
       <c r="C470" s="4"/>
@@ -7569,7 +7359,7 @@
       <c r="F470" s="4"/>
       <c r="G470" s="4"/>
     </row>
-    <row r="471" spans="1:7" ht="15">
+    <row r="471" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A471" s="4"/>
       <c r="B471" s="4"/>
       <c r="C471" s="4"/>
@@ -7577,7 +7367,7 @@
       <c r="F471" s="4"/>
       <c r="G471" s="4"/>
     </row>
-    <row r="472" spans="1:7" ht="15">
+    <row r="472" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A472" s="4"/>
       <c r="B472" s="4"/>
       <c r="C472" s="4"/>
@@ -7585,7 +7375,7 @@
       <c r="F472" s="4"/>
       <c r="G472" s="4"/>
     </row>
-    <row r="473" spans="1:7" ht="15">
+    <row r="473" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A473" s="4"/>
       <c r="B473" s="4"/>
       <c r="C473" s="4"/>
@@ -7593,7 +7383,7 @@
       <c r="F473" s="4"/>
       <c r="G473" s="4"/>
     </row>
-    <row r="474" spans="1:7" ht="15">
+    <row r="474" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A474" s="4"/>
       <c r="B474" s="4"/>
       <c r="C474" s="4"/>
@@ -7601,7 +7391,7 @@
       <c r="F474" s="4"/>
       <c r="G474" s="4"/>
     </row>
-    <row r="475" spans="1:7" ht="15">
+    <row r="475" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A475" s="4"/>
       <c r="B475" s="4"/>
       <c r="C475" s="4"/>
@@ -7609,7 +7399,7 @@
       <c r="F475" s="4"/>
       <c r="G475" s="4"/>
     </row>
-    <row r="476" spans="1:7" ht="15">
+    <row r="476" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A476" s="4"/>
       <c r="B476" s="4"/>
       <c r="C476" s="4"/>
@@ -7617,7 +7407,7 @@
       <c r="F476" s="4"/>
       <c r="G476" s="4"/>
     </row>
-    <row r="477" spans="1:7" ht="15">
+    <row r="477" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A477" s="4"/>
       <c r="B477" s="4"/>
       <c r="C477" s="4"/>
@@ -7625,7 +7415,7 @@
       <c r="F477" s="4"/>
       <c r="G477" s="4"/>
     </row>
-    <row r="478" spans="1:7" ht="15">
+    <row r="478" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A478" s="4"/>
       <c r="B478" s="4"/>
       <c r="C478" s="4"/>
@@ -7633,7 +7423,7 @@
       <c r="F478" s="4"/>
       <c r="G478" s="4"/>
     </row>
-    <row r="479" spans="1:7" ht="15">
+    <row r="479" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A479" s="4"/>
       <c r="B479" s="4"/>
       <c r="C479" s="4"/>
@@ -7641,7 +7431,7 @@
       <c r="F479" s="4"/>
       <c r="G479" s="4"/>
     </row>
-    <row r="480" spans="1:7" ht="15">
+    <row r="480" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A480" s="4"/>
       <c r="B480" s="4"/>
       <c r="C480" s="4"/>
@@ -7649,7 +7439,7 @@
       <c r="F480" s="4"/>
       <c r="G480" s="4"/>
     </row>
-    <row r="481" spans="1:7" ht="15">
+    <row r="481" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A481" s="4"/>
       <c r="B481" s="4"/>
       <c r="C481" s="4"/>
@@ -7657,7 +7447,7 @@
       <c r="F481" s="4"/>
       <c r="G481" s="4"/>
     </row>
-    <row r="482" spans="1:7" ht="15">
+    <row r="482" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A482" s="4"/>
       <c r="B482" s="4"/>
       <c r="C482" s="4"/>
@@ -7665,7 +7455,7 @@
       <c r="F482" s="4"/>
       <c r="G482" s="4"/>
     </row>
-    <row r="483" spans="1:7" ht="15">
+    <row r="483" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A483" s="4"/>
       <c r="B483" s="4"/>
       <c r="C483" s="4"/>
@@ -7673,7 +7463,7 @@
       <c r="F483" s="4"/>
       <c r="G483" s="4"/>
     </row>
-    <row r="484" spans="1:7" ht="15">
+    <row r="484" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A484" s="4"/>
       <c r="B484" s="4"/>
       <c r="C484" s="4"/>
@@ -7681,7 +7471,7 @@
       <c r="F484" s="4"/>
       <c r="G484" s="4"/>
     </row>
-    <row r="485" spans="1:7" ht="15">
+    <row r="485" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A485" s="4"/>
       <c r="B485" s="4"/>
       <c r="C485" s="4"/>
@@ -7689,7 +7479,7 @@
       <c r="F485" s="4"/>
       <c r="G485" s="4"/>
     </row>
-    <row r="486" spans="1:7" ht="15">
+    <row r="486" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A486" s="4"/>
       <c r="B486" s="4"/>
       <c r="C486" s="4"/>
@@ -7697,7 +7487,7 @@
       <c r="F486" s="4"/>
       <c r="G486" s="4"/>
     </row>
-    <row r="487" spans="1:7" ht="15">
+    <row r="487" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A487" s="4"/>
       <c r="B487" s="4"/>
       <c r="C487" s="4"/>
@@ -7705,7 +7495,7 @@
       <c r="F487" s="4"/>
       <c r="G487" s="4"/>
     </row>
-    <row r="488" spans="1:7" ht="15">
+    <row r="488" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A488" s="4"/>
       <c r="B488" s="4"/>
       <c r="C488" s="4"/>
@@ -7713,7 +7503,7 @@
       <c r="F488" s="4"/>
       <c r="G488" s="4"/>
     </row>
-    <row r="489" spans="1:7" ht="15">
+    <row r="489" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A489" s="4"/>
       <c r="B489" s="4"/>
       <c r="C489" s="4"/>
@@ -7721,7 +7511,7 @@
       <c r="F489" s="4"/>
       <c r="G489" s="4"/>
     </row>
-    <row r="490" spans="1:7" ht="15">
+    <row r="490" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A490" s="4"/>
       <c r="B490" s="4"/>
       <c r="C490" s="4"/>
@@ -7729,7 +7519,7 @@
       <c r="F490" s="4"/>
       <c r="G490" s="4"/>
     </row>
-    <row r="491" spans="1:7" ht="15">
+    <row r="491" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A491" s="4"/>
       <c r="B491" s="4"/>
       <c r="C491" s="4"/>
@@ -7737,7 +7527,7 @@
       <c r="F491" s="4"/>
       <c r="G491" s="4"/>
     </row>
-    <row r="492" spans="1:7" ht="15">
+    <row r="492" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A492" s="4"/>
       <c r="B492" s="4"/>
       <c r="C492" s="4"/>
@@ -7745,7 +7535,7 @@
       <c r="F492" s="4"/>
       <c r="G492" s="4"/>
     </row>
-    <row r="493" spans="1:7" ht="15">
+    <row r="493" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A493" s="4"/>
       <c r="B493" s="4"/>
       <c r="C493" s="4"/>
@@ -7753,7 +7543,7 @@
       <c r="F493" s="4"/>
       <c r="G493" s="4"/>
     </row>
-    <row r="494" spans="1:7" ht="15">
+    <row r="494" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A494" s="4"/>
       <c r="B494" s="4"/>
       <c r="C494" s="4"/>
@@ -7761,7 +7551,7 @@
       <c r="F494" s="4"/>
       <c r="G494" s="4"/>
     </row>
-    <row r="495" spans="1:7" ht="15">
+    <row r="495" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A495" s="4"/>
       <c r="B495" s="4"/>
       <c r="C495" s="4"/>
@@ -7769,7 +7559,7 @@
       <c r="F495" s="4"/>
       <c r="G495" s="4"/>
     </row>
-    <row r="496" spans="1:7" ht="15">
+    <row r="496" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A496" s="4"/>
       <c r="B496" s="4"/>
       <c r="C496" s="4"/>
@@ -7777,7 +7567,7 @@
       <c r="F496" s="4"/>
       <c r="G496" s="4"/>
     </row>
-    <row r="497" spans="1:7" ht="15">
+    <row r="497" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A497" s="4"/>
       <c r="B497" s="4"/>
       <c r="C497" s="4"/>
@@ -7785,7 +7575,7 @@
       <c r="F497" s="4"/>
       <c r="G497" s="4"/>
     </row>
-    <row r="498" spans="1:7" ht="15">
+    <row r="498" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A498" s="4"/>
       <c r="B498" s="4"/>
       <c r="C498" s="4"/>
@@ -7793,7 +7583,7 @@
       <c r="F498" s="4"/>
       <c r="G498" s="4"/>
     </row>
-    <row r="499" spans="1:7" ht="15">
+    <row r="499" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A499" s="4"/>
       <c r="B499" s="4"/>
       <c r="C499" s="4"/>
@@ -7801,7 +7591,7 @@
       <c r="F499" s="4"/>
       <c r="G499" s="4"/>
     </row>
-    <row r="500" spans="1:7" ht="15">
+    <row r="500" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A500" s="4"/>
       <c r="B500" s="4"/>
       <c r="C500" s="4"/>
@@ -7809,7 +7599,7 @@
       <c r="F500" s="4"/>
       <c r="G500" s="4"/>
     </row>
-    <row r="501" spans="1:7" ht="15">
+    <row r="501" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A501" s="4"/>
       <c r="B501" s="4"/>
       <c r="C501" s="4"/>
@@ -7817,7 +7607,7 @@
       <c r="F501" s="4"/>
       <c r="G501" s="4"/>
     </row>
-    <row r="502" spans="1:7" ht="15">
+    <row r="502" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A502" s="4"/>
       <c r="B502" s="4"/>
       <c r="C502" s="4"/>
@@ -7825,7 +7615,7 @@
       <c r="F502" s="4"/>
       <c r="G502" s="4"/>
     </row>
-    <row r="503" spans="1:7" ht="15">
+    <row r="503" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A503" s="4"/>
       <c r="B503" s="4"/>
       <c r="C503" s="4"/>
@@ -7833,7 +7623,7 @@
       <c r="F503" s="4"/>
       <c r="G503" s="4"/>
     </row>
-    <row r="504" spans="1:7" ht="15">
+    <row r="504" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A504" s="4"/>
       <c r="B504" s="4"/>
       <c r="C504" s="4"/>
@@ -7841,7 +7631,7 @@
       <c r="F504" s="4"/>
       <c r="G504" s="4"/>
     </row>
-    <row r="505" spans="1:7" ht="15">
+    <row r="505" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A505" s="4"/>
       <c r="B505" s="4"/>
       <c r="C505" s="4"/>
@@ -7849,7 +7639,7 @@
       <c r="F505" s="4"/>
       <c r="G505" s="4"/>
     </row>
-    <row r="506" spans="1:7" ht="15">
+    <row r="506" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A506" s="4"/>
       <c r="B506" s="4"/>
       <c r="C506" s="4"/>
@@ -7857,7 +7647,7 @@
       <c r="F506" s="4"/>
       <c r="G506" s="4"/>
     </row>
-    <row r="507" spans="1:7" ht="15">
+    <row r="507" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A507" s="4"/>
       <c r="B507" s="4"/>
       <c r="C507" s="4"/>
@@ -7865,7 +7655,7 @@
       <c r="F507" s="4"/>
       <c r="G507" s="4"/>
     </row>
-    <row r="508" spans="1:7" ht="15">
+    <row r="508" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A508" s="4"/>
       <c r="B508" s="4"/>
       <c r="C508" s="4"/>
@@ -7873,7 +7663,7 @@
       <c r="F508" s="4"/>
       <c r="G508" s="4"/>
     </row>
-    <row r="509" spans="1:7" ht="15">
+    <row r="509" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A509" s="4"/>
       <c r="B509" s="4"/>
       <c r="C509" s="4"/>
@@ -7881,7 +7671,7 @@
       <c r="F509" s="4"/>
       <c r="G509" s="4"/>
     </row>
-    <row r="510" spans="1:7" ht="15">
+    <row r="510" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A510" s="4"/>
       <c r="B510" s="4"/>
       <c r="C510" s="4"/>
@@ -7889,7 +7679,7 @@
       <c r="F510" s="4"/>
       <c r="G510" s="4"/>
     </row>
-    <row r="511" spans="1:7" ht="15">
+    <row r="511" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A511" s="4"/>
       <c r="B511" s="4"/>
       <c r="C511" s="4"/>
@@ -7897,7 +7687,7 @@
       <c r="F511" s="4"/>
       <c r="G511" s="4"/>
     </row>
-    <row r="512" spans="1:7" ht="15">
+    <row r="512" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A512" s="4"/>
       <c r="B512" s="4"/>
       <c r="C512" s="4"/>
@@ -7905,7 +7695,7 @@
       <c r="F512" s="4"/>
       <c r="G512" s="4"/>
     </row>
-    <row r="513" spans="1:7" ht="15">
+    <row r="513" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A513" s="4"/>
       <c r="B513" s="4"/>
       <c r="C513" s="4"/>
@@ -7913,7 +7703,7 @@
       <c r="F513" s="4"/>
       <c r="G513" s="4"/>
     </row>
-    <row r="514" spans="1:7" ht="15">
+    <row r="514" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A514" s="4"/>
       <c r="B514" s="4"/>
       <c r="C514" s="4"/>
@@ -7921,7 +7711,7 @@
       <c r="F514" s="4"/>
       <c r="G514" s="4"/>
     </row>
-    <row r="515" spans="1:7" ht="15">
+    <row r="515" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A515" s="4"/>
       <c r="B515" s="4"/>
       <c r="C515" s="4"/>
@@ -7929,7 +7719,7 @@
       <c r="F515" s="4"/>
       <c r="G515" s="4"/>
     </row>
-    <row r="516" spans="1:7" ht="15">
+    <row r="516" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A516" s="4"/>
       <c r="B516" s="4"/>
       <c r="C516" s="4"/>
@@ -7937,7 +7727,7 @@
       <c r="F516" s="4"/>
       <c r="G516" s="4"/>
     </row>
-    <row r="517" spans="1:7" ht="15">
+    <row r="517" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A517" s="4"/>
       <c r="B517" s="4"/>
       <c r="C517" s="4"/>
@@ -7945,7 +7735,7 @@
       <c r="F517" s="4"/>
       <c r="G517" s="4"/>
     </row>
-    <row r="518" spans="1:7" ht="15">
+    <row r="518" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A518" s="4"/>
       <c r="B518" s="4"/>
       <c r="C518" s="4"/>
@@ -7953,7 +7743,7 @@
       <c r="F518" s="4"/>
       <c r="G518" s="4"/>
     </row>
-    <row r="519" spans="1:7" ht="15">
+    <row r="519" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A519" s="4"/>
       <c r="B519" s="4"/>
       <c r="C519" s="4"/>
@@ -7961,7 +7751,7 @@
       <c r="F519" s="4"/>
       <c r="G519" s="4"/>
     </row>
-    <row r="520" spans="1:7" ht="15">
+    <row r="520" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A520" s="4"/>
       <c r="B520" s="4"/>
       <c r="C520" s="4"/>
@@ -7969,7 +7759,7 @@
       <c r="F520" s="4"/>
       <c r="G520" s="4"/>
     </row>
-    <row r="521" spans="1:7" ht="15">
+    <row r="521" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A521" s="4"/>
       <c r="B521" s="4"/>
       <c r="C521" s="4"/>
@@ -7977,7 +7767,7 @@
       <c r="F521" s="4"/>
       <c r="G521" s="4"/>
     </row>
-    <row r="522" spans="1:7" ht="15">
+    <row r="522" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A522" s="4"/>
       <c r="B522" s="4"/>
       <c r="C522" s="4"/>
@@ -7985,7 +7775,7 @@
       <c r="F522" s="4"/>
       <c r="G522" s="4"/>
     </row>
-    <row r="523" spans="1:7" ht="15">
+    <row r="523" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A523" s="4"/>
       <c r="B523" s="4"/>
       <c r="C523" s="4"/>
@@ -7993,7 +7783,7 @@
       <c r="F523" s="4"/>
       <c r="G523" s="4"/>
     </row>
-    <row r="524" spans="1:7" ht="15">
+    <row r="524" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A524" s="4"/>
       <c r="B524" s="4"/>
       <c r="C524" s="4"/>
@@ -8001,7 +7791,7 @@
       <c r="F524" s="4"/>
       <c r="G524" s="4"/>
     </row>
-    <row r="525" spans="1:7" ht="15">
+    <row r="525" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A525" s="4"/>
       <c r="B525" s="4"/>
       <c r="C525" s="4"/>
@@ -8009,7 +7799,7 @@
       <c r="F525" s="4"/>
       <c r="G525" s="4"/>
     </row>
-    <row r="526" spans="1:7" ht="15">
+    <row r="526" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A526" s="4"/>
       <c r="B526" s="4"/>
       <c r="C526" s="4"/>
@@ -8017,7 +7807,7 @@
       <c r="F526" s="4"/>
       <c r="G526" s="4"/>
     </row>
-    <row r="527" spans="1:7" ht="15">
+    <row r="527" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A527" s="4"/>
       <c r="B527" s="4"/>
       <c r="C527" s="4"/>
@@ -8025,7 +7815,7 @@
       <c r="F527" s="4"/>
       <c r="G527" s="4"/>
     </row>
-    <row r="528" spans="1:7" ht="15">
+    <row r="528" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A528" s="4"/>
       <c r="B528" s="4"/>
       <c r="C528" s="4"/>
@@ -8033,7 +7823,7 @@
       <c r="F528" s="4"/>
       <c r="G528" s="4"/>
     </row>
-    <row r="529" spans="1:7" ht="15">
+    <row r="529" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A529" s="4"/>
       <c r="B529" s="4"/>
       <c r="C529" s="4"/>
@@ -8041,7 +7831,7 @@
       <c r="F529" s="4"/>
       <c r="G529" s="4"/>
     </row>
-    <row r="530" spans="1:7" ht="15">
+    <row r="530" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A530" s="4"/>
       <c r="B530" s="4"/>
       <c r="C530" s="4"/>
@@ -8049,7 +7839,7 @@
       <c r="F530" s="4"/>
       <c r="G530" s="4"/>
     </row>
-    <row r="531" spans="1:7" ht="15">
+    <row r="531" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A531" s="4"/>
       <c r="B531" s="4"/>
       <c r="C531" s="4"/>
@@ -8057,7 +7847,7 @@
       <c r="F531" s="4"/>
       <c r="G531" s="4"/>
     </row>
-    <row r="532" spans="1:7" ht="15">
+    <row r="532" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A532" s="4"/>
       <c r="B532" s="4"/>
       <c r="C532" s="4"/>
@@ -8065,7 +7855,7 @@
       <c r="F532" s="4"/>
       <c r="G532" s="4"/>
     </row>
-    <row r="533" spans="1:7" ht="15">
+    <row r="533" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A533" s="4"/>
       <c r="B533" s="4"/>
       <c r="C533" s="4"/>
@@ -8073,7 +7863,7 @@
       <c r="F533" s="4"/>
       <c r="G533" s="4"/>
     </row>
-    <row r="534" spans="1:7" ht="15">
+    <row r="534" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A534" s="4"/>
       <c r="B534" s="4"/>
       <c r="C534" s="4"/>
@@ -8081,7 +7871,7 @@
       <c r="F534" s="4"/>
       <c r="G534" s="4"/>
     </row>
-    <row r="535" spans="1:7" ht="15">
+    <row r="535" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A535" s="4"/>
       <c r="B535" s="4"/>
       <c r="C535" s="4"/>
@@ -8089,7 +7879,7 @@
       <c r="F535" s="4"/>
       <c r="G535" s="4"/>
     </row>
-    <row r="536" spans="1:7" ht="15">
+    <row r="536" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A536" s="4"/>
       <c r="B536" s="4"/>
       <c r="C536" s="4"/>
@@ -8097,7 +7887,7 @@
       <c r="F536" s="4"/>
       <c r="G536" s="4"/>
     </row>
-    <row r="537" spans="1:7" ht="15">
+    <row r="537" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A537" s="4"/>
       <c r="B537" s="4"/>
       <c r="C537" s="4"/>
@@ -8105,7 +7895,7 @@
       <c r="F537" s="4"/>
       <c r="G537" s="4"/>
     </row>
-    <row r="538" spans="1:7" ht="15">
+    <row r="538" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A538" s="4"/>
       <c r="B538" s="4"/>
       <c r="C538" s="4"/>
@@ -8113,7 +7903,7 @@
       <c r="F538" s="4"/>
       <c r="G538" s="4"/>
     </row>
-    <row r="539" spans="1:7" ht="15">
+    <row r="539" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A539" s="4"/>
       <c r="B539" s="4"/>
       <c r="C539" s="4"/>
@@ -8121,7 +7911,7 @@
       <c r="F539" s="4"/>
       <c r="G539" s="4"/>
     </row>
-    <row r="540" spans="1:7" ht="15">
+    <row r="540" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A540" s="4"/>
       <c r="B540" s="4"/>
       <c r="C540" s="4"/>
@@ -8129,7 +7919,7 @@
       <c r="F540" s="4"/>
       <c r="G540" s="4"/>
     </row>
-    <row r="541" spans="1:7" ht="15">
+    <row r="541" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A541" s="4"/>
       <c r="B541" s="4"/>
       <c r="C541" s="4"/>
@@ -8137,7 +7927,7 @@
       <c r="F541" s="4"/>
       <c r="G541" s="4"/>
     </row>
-    <row r="542" spans="1:7" ht="15">
+    <row r="542" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A542" s="4"/>
       <c r="B542" s="4"/>
       <c r="C542" s="4"/>
@@ -8145,7 +7935,7 @@
       <c r="F542" s="4"/>
       <c r="G542" s="4"/>
     </row>
-    <row r="543" spans="1:7" ht="15">
+    <row r="543" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A543" s="4"/>
       <c r="B543" s="4"/>
       <c r="C543" s="4"/>
@@ -8153,7 +7943,7 @@
       <c r="F543" s="4"/>
       <c r="G543" s="4"/>
     </row>
-    <row r="544" spans="1:7" ht="15">
+    <row r="544" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A544" s="4"/>
       <c r="B544" s="4"/>
       <c r="C544" s="4"/>
@@ -8161,7 +7951,7 @@
       <c r="F544" s="4"/>
       <c r="G544" s="4"/>
     </row>
-    <row r="545" spans="1:7" ht="15">
+    <row r="545" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A545" s="4"/>
       <c r="B545" s="4"/>
       <c r="C545" s="4"/>
@@ -8169,7 +7959,7 @@
       <c r="F545" s="4"/>
       <c r="G545" s="4"/>
     </row>
-    <row r="546" spans="1:7" ht="15">
+    <row r="546" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A546" s="4"/>
       <c r="B546" s="4"/>
       <c r="C546" s="4"/>
@@ -8177,7 +7967,7 @@
       <c r="F546" s="4"/>
       <c r="G546" s="4"/>
     </row>
-    <row r="547" spans="1:7" ht="15">
+    <row r="547" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A547" s="4"/>
       <c r="B547" s="4"/>
       <c r="C547" s="4"/>
@@ -8185,7 +7975,7 @@
       <c r="F547" s="4"/>
       <c r="G547" s="4"/>
     </row>
-    <row r="548" spans="1:7" ht="15">
+    <row r="548" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A548" s="4"/>
       <c r="B548" s="4"/>
       <c r="C548" s="4"/>
@@ -8193,7 +7983,7 @@
       <c r="F548" s="4"/>
       <c r="G548" s="4"/>
     </row>
-    <row r="549" spans="1:7" ht="15">
+    <row r="549" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A549" s="4"/>
       <c r="B549" s="4"/>
       <c r="C549" s="4"/>
@@ -8201,7 +7991,7 @@
       <c r="F549" s="4"/>
       <c r="G549" s="4"/>
     </row>
-    <row r="550" spans="1:7" ht="15">
+    <row r="550" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A550" s="4"/>
       <c r="B550" s="4"/>
       <c r="C550" s="4"/>
@@ -8209,7 +7999,7 @@
       <c r="F550" s="4"/>
       <c r="G550" s="4"/>
     </row>
-    <row r="551" spans="1:7" ht="15">
+    <row r="551" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A551" s="4"/>
       <c r="B551" s="4"/>
       <c r="C551" s="4"/>
@@ -8217,7 +8007,7 @@
       <c r="F551" s="4"/>
       <c r="G551" s="4"/>
     </row>
-    <row r="552" spans="1:7" ht="15">
+    <row r="552" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A552" s="4"/>
       <c r="B552" s="4"/>
       <c r="C552" s="4"/>
@@ -8225,7 +8015,7 @@
       <c r="F552" s="4"/>
       <c r="G552" s="4"/>
     </row>
-    <row r="553" spans="1:7" ht="15">
+    <row r="553" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A553" s="4"/>
       <c r="B553" s="4"/>
       <c r="C553" s="4"/>
@@ -8233,7 +8023,7 @@
       <c r="F553" s="4"/>
       <c r="G553" s="4"/>
     </row>
-    <row r="554" spans="1:7" ht="15">
+    <row r="554" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A554" s="4"/>
       <c r="B554" s="4"/>
       <c r="C554" s="4"/>
@@ -8241,7 +8031,7 @@
       <c r="F554" s="4"/>
       <c r="G554" s="4"/>
     </row>
-    <row r="555" spans="1:7" ht="15">
+    <row r="555" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A555" s="4"/>
       <c r="B555" s="4"/>
       <c r="C555" s="4"/>
@@ -8249,7 +8039,7 @@
       <c r="F555" s="4"/>
       <c r="G555" s="4"/>
     </row>
-    <row r="556" spans="1:7" ht="15">
+    <row r="556" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A556" s="4"/>
       <c r="B556" s="4"/>
       <c r="C556" s="4"/>
@@ -8257,7 +8047,7 @@
       <c r="F556" s="4"/>
       <c r="G556" s="4"/>
     </row>
-    <row r="557" spans="1:7" ht="15">
+    <row r="557" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A557" s="4"/>
       <c r="B557" s="4"/>
       <c r="C557" s="4"/>
@@ -8265,7 +8055,7 @@
       <c r="F557" s="4"/>
       <c r="G557" s="4"/>
     </row>
-    <row r="558" spans="1:7" ht="15">
+    <row r="558" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A558" s="4"/>
       <c r="B558" s="4"/>
       <c r="C558" s="4"/>
@@ -8273,7 +8063,7 @@
       <c r="F558" s="4"/>
       <c r="G558" s="4"/>
     </row>
-    <row r="559" spans="1:7" ht="15">
+    <row r="559" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A559" s="4"/>
       <c r="B559" s="4"/>
       <c r="C559" s="4"/>
@@ -8281,7 +8071,7 @@
       <c r="F559" s="4"/>
       <c r="G559" s="4"/>
     </row>
-    <row r="560" spans="1:7" ht="15">
+    <row r="560" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A560" s="4"/>
       <c r="B560" s="4"/>
       <c r="C560" s="4"/>
@@ -8289,7 +8079,7 @@
       <c r="F560" s="4"/>
       <c r="G560" s="4"/>
     </row>
-    <row r="561" spans="1:7" ht="15">
+    <row r="561" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A561" s="4"/>
       <c r="B561" s="4"/>
       <c r="C561" s="4"/>
@@ -8297,7 +8087,7 @@
       <c r="F561" s="4"/>
       <c r="G561" s="4"/>
     </row>
-    <row r="562" spans="1:7" ht="15">
+    <row r="562" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A562" s="4"/>
       <c r="B562" s="4"/>
       <c r="C562" s="4"/>
@@ -8305,7 +8095,7 @@
       <c r="F562" s="4"/>
       <c r="G562" s="4"/>
     </row>
-    <row r="563" spans="1:7" ht="15">
+    <row r="563" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A563" s="4"/>
       <c r="B563" s="4"/>
       <c r="C563" s="4"/>
@@ -8313,7 +8103,7 @@
       <c r="F563" s="4"/>
       <c r="G563" s="4"/>
     </row>
-    <row r="564" spans="1:7" ht="15">
+    <row r="564" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A564" s="4"/>
       <c r="B564" s="4"/>
       <c r="C564" s="4"/>
@@ -8321,7 +8111,7 @@
       <c r="F564" s="4"/>
       <c r="G564" s="4"/>
     </row>
-    <row r="565" spans="1:7" ht="15">
+    <row r="565" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A565" s="4"/>
       <c r="B565" s="4"/>
       <c r="C565" s="4"/>
@@ -8329,7 +8119,7 @@
       <c r="F565" s="4"/>
       <c r="G565" s="4"/>
     </row>
-    <row r="566" spans="1:7" ht="15">
+    <row r="566" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A566" s="4"/>
       <c r="B566" s="4"/>
       <c r="C566" s="4"/>
@@ -8337,7 +8127,7 @@
       <c r="F566" s="4"/>
       <c r="G566" s="4"/>
     </row>
-    <row r="567" spans="1:7" ht="15">
+    <row r="567" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A567" s="4"/>
       <c r="B567" s="4"/>
       <c r="C567" s="4"/>
@@ -8345,7 +8135,7 @@
       <c r="F567" s="4"/>
       <c r="G567" s="4"/>
     </row>
-    <row r="568" spans="1:7" ht="15">
+    <row r="568" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A568" s="4"/>
       <c r="B568" s="4"/>
       <c r="C568" s="4"/>
@@ -8353,7 +8143,7 @@
       <c r="F568" s="4"/>
       <c r="G568" s="4"/>
     </row>
-    <row r="569" spans="1:7" ht="15">
+    <row r="569" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A569" s="4"/>
       <c r="B569" s="4"/>
       <c r="C569" s="4"/>
@@ -8361,7 +8151,7 @@
       <c r="F569" s="4"/>
       <c r="G569" s="4"/>
     </row>
-    <row r="570" spans="1:7" ht="15">
+    <row r="570" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A570" s="4"/>
       <c r="B570" s="4"/>
       <c r="C570" s="4"/>
@@ -8369,7 +8159,7 @@
       <c r="F570" s="4"/>
       <c r="G570" s="4"/>
     </row>
-    <row r="571" spans="1:7" ht="15">
+    <row r="571" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A571" s="4"/>
       <c r="B571" s="4"/>
       <c r="C571" s="4"/>
@@ -8377,7 +8167,7 @@
       <c r="F571" s="4"/>
       <c r="G571" s="4"/>
     </row>
-    <row r="572" spans="1:7" ht="15">
+    <row r="572" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A572" s="4"/>
       <c r="B572" s="4"/>
       <c r="C572" s="4"/>
@@ -8385,7 +8175,7 @@
       <c r="F572" s="4"/>
       <c r="G572" s="4"/>
     </row>
-    <row r="573" spans="1:7" ht="15">
+    <row r="573" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A573" s="4"/>
       <c r="B573" s="4"/>
       <c r="C573" s="4"/>
@@ -8393,7 +8183,7 @@
       <c r="F573" s="4"/>
       <c r="G573" s="4"/>
     </row>
-    <row r="574" spans="1:7" ht="15">
+    <row r="574" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A574" s="4"/>
       <c r="B574" s="4"/>
       <c r="C574" s="4"/>
@@ -8401,7 +8191,7 @@
       <c r="F574" s="4"/>
       <c r="G574" s="4"/>
     </row>
-    <row r="575" spans="1:7" ht="15">
+    <row r="575" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A575" s="4"/>
       <c r="B575" s="4"/>
       <c r="C575" s="4"/>
@@ -8409,7 +8199,7 @@
       <c r="F575" s="4"/>
       <c r="G575" s="4"/>
     </row>
-    <row r="576" spans="1:7" ht="15">
+    <row r="576" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A576" s="4"/>
       <c r="B576" s="4"/>
       <c r="C576" s="4"/>
@@ -8417,7 +8207,7 @@
       <c r="F576" s="4"/>
       <c r="G576" s="4"/>
     </row>
-    <row r="577" spans="1:7" ht="15">
+    <row r="577" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A577" s="4"/>
       <c r="B577" s="4"/>
       <c r="C577" s="4"/>
@@ -8425,7 +8215,7 @@
       <c r="F577" s="4"/>
       <c r="G577" s="4"/>
     </row>
-    <row r="578" spans="1:7" ht="15">
+    <row r="578" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A578" s="4"/>
       <c r="B578" s="4"/>
       <c r="C578" s="4"/>
@@ -8433,7 +8223,7 @@
       <c r="F578" s="4"/>
       <c r="G578" s="4"/>
     </row>
-    <row r="579" spans="1:7" ht="15">
+    <row r="579" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A579" s="4"/>
       <c r="B579" s="4"/>
       <c r="C579" s="4"/>
@@ -8441,7 +8231,7 @@
       <c r="F579" s="4"/>
       <c r="G579" s="4"/>
     </row>
-    <row r="580" spans="1:7" ht="15">
+    <row r="580" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A580" s="4"/>
       <c r="B580" s="4"/>
       <c r="C580" s="4"/>
@@ -8449,7 +8239,7 @@
       <c r="F580" s="4"/>
       <c r="G580" s="4"/>
     </row>
-    <row r="581" spans="1:7" ht="15">
+    <row r="581" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A581" s="4"/>
       <c r="B581" s="4"/>
       <c r="C581" s="4"/>
@@ -8457,7 +8247,7 @@
       <c r="F581" s="4"/>
       <c r="G581" s="4"/>
     </row>
-    <row r="582" spans="1:7" ht="15">
+    <row r="582" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A582" s="4"/>
       <c r="B582" s="4"/>
       <c r="C582" s="4"/>
@@ -8465,7 +8255,7 @@
       <c r="F582" s="4"/>
       <c r="G582" s="4"/>
     </row>
-    <row r="583" spans="1:7" ht="15">
+    <row r="583" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A583" s="4"/>
       <c r="B583" s="4"/>
       <c r="C583" s="4"/>
@@ -8473,7 +8263,7 @@
       <c r="F583" s="4"/>
       <c r="G583" s="4"/>
     </row>
-    <row r="584" spans="1:7" ht="15">
+    <row r="584" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A584" s="4"/>
       <c r="B584" s="4"/>
       <c r="C584" s="4"/>
@@ -8481,7 +8271,7 @@
       <c r="F584" s="4"/>
       <c r="G584" s="4"/>
     </row>
-    <row r="585" spans="1:7" ht="15">
+    <row r="585" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A585" s="4"/>
       <c r="B585" s="4"/>
       <c r="C585" s="4"/>
@@ -8489,7 +8279,7 @@
       <c r="F585" s="4"/>
       <c r="G585" s="4"/>
     </row>
-    <row r="586" spans="1:7" ht="15">
+    <row r="586" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A586" s="4"/>
       <c r="B586" s="4"/>
       <c r="C586" s="4"/>
@@ -8497,7 +8287,7 @@
       <c r="F586" s="4"/>
       <c r="G586" s="4"/>
     </row>
-    <row r="587" spans="1:7" ht="15">
+    <row r="587" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A587" s="4"/>
       <c r="B587" s="4"/>
       <c r="C587" s="4"/>
@@ -8505,7 +8295,7 @@
       <c r="F587" s="4"/>
       <c r="G587" s="4"/>
     </row>
-    <row r="588" spans="1:7" ht="15">
+    <row r="588" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A588" s="4"/>
       <c r="B588" s="4"/>
       <c r="C588" s="4"/>
@@ -8513,7 +8303,7 @@
       <c r="F588" s="4"/>
       <c r="G588" s="4"/>
     </row>
-    <row r="589" spans="1:7" ht="15">
+    <row r="589" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A589" s="4"/>
       <c r="B589" s="4"/>
       <c r="C589" s="4"/>
@@ -8521,7 +8311,7 @@
       <c r="F589" s="4"/>
       <c r="G589" s="4"/>
     </row>
-    <row r="590" spans="1:7" ht="15">
+    <row r="590" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A590" s="4"/>
       <c r="B590" s="4"/>
       <c r="C590" s="4"/>
@@ -8529,7 +8319,7 @@
       <c r="F590" s="4"/>
       <c r="G590" s="4"/>
     </row>
-    <row r="591" spans="1:7" ht="15">
+    <row r="591" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A591" s="4"/>
       <c r="B591" s="4"/>
       <c r="C591" s="4"/>
@@ -8537,7 +8327,7 @@
       <c r="F591" s="4"/>
       <c r="G591" s="4"/>
     </row>
-    <row r="592" spans="1:7" ht="15">
+    <row r="592" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A592" s="4"/>
       <c r="B592" s="4"/>
       <c r="C592" s="4"/>
@@ -8545,7 +8335,7 @@
       <c r="F592" s="4"/>
       <c r="G592" s="4"/>
     </row>
-    <row r="593" spans="1:7" ht="15">
+    <row r="593" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A593" s="4"/>
       <c r="B593" s="4"/>
       <c r="C593" s="4"/>
@@ -8553,7 +8343,7 @@
       <c r="F593" s="4"/>
       <c r="G593" s="4"/>
     </row>
-    <row r="594" spans="1:7" ht="15">
+    <row r="594" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A594" s="4"/>
       <c r="B594" s="4"/>
       <c r="C594" s="4"/>
@@ -8561,7 +8351,7 @@
       <c r="F594" s="4"/>
       <c r="G594" s="4"/>
     </row>
-    <row r="595" spans="1:7" ht="15">
+    <row r="595" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A595" s="4"/>
       <c r="B595" s="4"/>
       <c r="C595" s="4"/>
@@ -8569,7 +8359,7 @@
       <c r="F595" s="4"/>
       <c r="G595" s="4"/>
     </row>
-    <row r="596" spans="1:7" ht="15">
+    <row r="596" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A596" s="4"/>
       <c r="B596" s="4"/>
       <c r="C596" s="4"/>
@@ -8577,7 +8367,7 @@
       <c r="F596" s="4"/>
       <c r="G596" s="4"/>
     </row>
-    <row r="597" spans="1:7" ht="15">
+    <row r="597" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A597" s="4"/>
       <c r="B597" s="4"/>
       <c r="C597" s="4"/>
@@ -8585,7 +8375,7 @@
       <c r="F597" s="4"/>
       <c r="G597" s="4"/>
     </row>
-    <row r="598" spans="1:7" ht="15">
+    <row r="598" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A598" s="4"/>
       <c r="B598" s="4"/>
       <c r="C598" s="4"/>
@@ -8593,7 +8383,7 @@
       <c r="F598" s="4"/>
       <c r="G598" s="4"/>
     </row>
-    <row r="599" spans="1:7" ht="15">
+    <row r="599" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A599" s="4"/>
       <c r="B599" s="4"/>
       <c r="C599" s="4"/>
@@ -8601,7 +8391,7 @@
       <c r="F599" s="4"/>
       <c r="G599" s="4"/>
     </row>
-    <row r="600" spans="1:7" ht="15">
+    <row r="600" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A600" s="4"/>
       <c r="B600" s="4"/>
       <c r="C600" s="4"/>
@@ -8609,7 +8399,7 @@
       <c r="F600" s="4"/>
       <c r="G600" s="4"/>
     </row>
-    <row r="601" spans="1:7" ht="15">
+    <row r="601" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A601" s="4"/>
       <c r="B601" s="4"/>
       <c r="C601" s="4"/>
@@ -8617,7 +8407,7 @@
       <c r="F601" s="4"/>
       <c r="G601" s="4"/>
     </row>
-    <row r="602" spans="1:7" ht="15">
+    <row r="602" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A602" s="4"/>
       <c r="B602" s="4"/>
       <c r="C602" s="4"/>
@@ -8625,7 +8415,7 @@
       <c r="F602" s="4"/>
       <c r="G602" s="4"/>
     </row>
-    <row r="603" spans="1:7" ht="15">
+    <row r="603" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A603" s="4"/>
       <c r="B603" s="4"/>
       <c r="C603" s="4"/>
@@ -8633,7 +8423,7 @@
       <c r="F603" s="4"/>
       <c r="G603" s="4"/>
     </row>
-    <row r="604" spans="1:7" ht="15">
+    <row r="604" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A604" s="4"/>
       <c r="B604" s="4"/>
       <c r="C604" s="4"/>
@@ -8641,7 +8431,7 @@
       <c r="F604" s="4"/>
       <c r="G604" s="4"/>
     </row>
-    <row r="605" spans="1:7" ht="15">
+    <row r="605" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A605" s="4"/>
       <c r="B605" s="4"/>
       <c r="C605" s="4"/>
@@ -8649,7 +8439,7 @@
       <c r="F605" s="4"/>
       <c r="G605" s="4"/>
     </row>
-    <row r="606" spans="1:7" ht="15">
+    <row r="606" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A606" s="4"/>
       <c r="B606" s="4"/>
       <c r="C606" s="4"/>
@@ -8657,7 +8447,7 @@
       <c r="F606" s="4"/>
       <c r="G606" s="4"/>
     </row>
-    <row r="607" spans="1:7" ht="15">
+    <row r="607" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A607" s="4"/>
       <c r="B607" s="4"/>
       <c r="C607" s="4"/>
@@ -8665,7 +8455,7 @@
       <c r="F607" s="4"/>
       <c r="G607" s="4"/>
     </row>
-    <row r="608" spans="1:7" ht="15">
+    <row r="608" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A608" s="4"/>
       <c r="B608" s="4"/>
       <c r="C608" s="4"/>
@@ -8673,7 +8463,7 @@
       <c r="F608" s="4"/>
       <c r="G608" s="4"/>
     </row>
-    <row r="609" spans="1:7" ht="15">
+    <row r="609" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A609" s="4"/>
       <c r="B609" s="4"/>
       <c r="C609" s="4"/>
@@ -8681,7 +8471,7 @@
       <c r="F609" s="4"/>
       <c r="G609" s="4"/>
     </row>
-    <row r="610" spans="1:7" ht="15">
+    <row r="610" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A610" s="4"/>
       <c r="B610" s="4"/>
       <c r="C610" s="4"/>
@@ -8689,7 +8479,7 @@
       <c r="F610" s="4"/>
       <c r="G610" s="4"/>
     </row>
-    <row r="611" spans="1:7" ht="15">
+    <row r="611" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A611" s="4"/>
       <c r="B611" s="4"/>
       <c r="C611" s="4"/>
@@ -8697,7 +8487,7 @@
       <c r="F611" s="4"/>
       <c r="G611" s="4"/>
     </row>
-    <row r="612" spans="1:7" ht="15">
+    <row r="612" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A612" s="4"/>
       <c r="B612" s="4"/>
       <c r="C612" s="4"/>
@@ -8705,7 +8495,7 @@
       <c r="F612" s="4"/>
       <c r="G612" s="4"/>
     </row>
-    <row r="613" spans="1:7" ht="15">
+    <row r="613" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A613" s="4"/>
       <c r="B613" s="4"/>
       <c r="C613" s="4"/>
@@ -8713,7 +8503,7 @@
       <c r="F613" s="4"/>
       <c r="G613" s="4"/>
     </row>
-    <row r="614" spans="1:7" ht="15">
+    <row r="614" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A614" s="4"/>
       <c r="B614" s="4"/>
       <c r="C614" s="4"/>
@@ -8721,7 +8511,7 @@
       <c r="F614" s="4"/>
       <c r="G614" s="4"/>
     </row>
-    <row r="615" spans="1:7" ht="15">
+    <row r="615" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A615" s="4"/>
       <c r="B615" s="4"/>
       <c r="C615" s="4"/>
@@ -8729,7 +8519,7 @@
       <c r="F615" s="4"/>
       <c r="G615" s="4"/>
     </row>
-    <row r="616" spans="1:7" ht="15">
+    <row r="616" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A616" s="4"/>
       <c r="B616" s="4"/>
       <c r="C616" s="4"/>
@@ -8737,7 +8527,7 @@
       <c r="F616" s="4"/>
       <c r="G616" s="4"/>
     </row>
-    <row r="617" spans="1:7" ht="15">
+    <row r="617" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A617" s="4"/>
       <c r="B617" s="4"/>
       <c r="C617" s="4"/>
@@ -8745,7 +8535,7 @@
       <c r="F617" s="4"/>
       <c r="G617" s="4"/>
     </row>
-    <row r="618" spans="1:7" ht="15">
+    <row r="618" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A618" s="4"/>
       <c r="B618" s="4"/>
       <c r="C618" s="4"/>
@@ -8753,7 +8543,7 @@
       <c r="F618" s="4"/>
       <c r="G618" s="4"/>
     </row>
-    <row r="619" spans="1:7" ht="15">
+    <row r="619" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A619" s="4"/>
       <c r="B619" s="4"/>
       <c r="C619" s="4"/>
@@ -8761,7 +8551,7 @@
       <c r="F619" s="4"/>
       <c r="G619" s="4"/>
     </row>
-    <row r="620" spans="1:7" ht="15">
+    <row r="620" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A620" s="4"/>
       <c r="B620" s="4"/>
       <c r="C620" s="4"/>
@@ -8769,7 +8559,7 @@
       <c r="F620" s="4"/>
       <c r="G620" s="4"/>
     </row>
-    <row r="621" spans="1:7" ht="15">
+    <row r="621" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A621" s="4"/>
       <c r="B621" s="4"/>
       <c r="C621" s="4"/>
@@ -8777,7 +8567,7 @@
       <c r="F621" s="4"/>
       <c r="G621" s="4"/>
     </row>
-    <row r="622" spans="1:7" ht="15">
+    <row r="622" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A622" s="4"/>
       <c r="B622" s="4"/>
       <c r="C622" s="4"/>
@@ -8785,7 +8575,7 @@
       <c r="F622" s="4"/>
       <c r="G622" s="4"/>
     </row>
-    <row r="623" spans="1:7" ht="15">
+    <row r="623" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A623" s="4"/>
       <c r="B623" s="4"/>
       <c r="C623" s="4"/>
@@ -8793,7 +8583,7 @@
       <c r="F623" s="4"/>
       <c r="G623" s="4"/>
     </row>
-    <row r="624" spans="1:7" ht="15">
+    <row r="624" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A624" s="4"/>
       <c r="B624" s="4"/>
       <c r="C624" s="4"/>
@@ -8801,7 +8591,7 @@
       <c r="F624" s="4"/>
       <c r="G624" s="4"/>
     </row>
-    <row r="625" spans="1:7" ht="15">
+    <row r="625" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A625" s="4"/>
       <c r="B625" s="4"/>
       <c r="C625" s="4"/>
@@ -8809,7 +8599,7 @@
       <c r="F625" s="4"/>
       <c r="G625" s="4"/>
     </row>
-    <row r="626" spans="1:7" ht="15">
+    <row r="626" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A626" s="4"/>
       <c r="B626" s="4"/>
       <c r="C626" s="4"/>
@@ -8817,7 +8607,7 @@
       <c r="F626" s="4"/>
       <c r="G626" s="4"/>
     </row>
-    <row r="627" spans="1:7" ht="15">
+    <row r="627" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A627" s="4"/>
       <c r="B627" s="4"/>
       <c r="C627" s="4"/>
@@ -8825,7 +8615,7 @@
       <c r="F627" s="4"/>
       <c r="G627" s="4"/>
     </row>
-    <row r="628" spans="1:7" ht="15">
+    <row r="628" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A628" s="4"/>
       <c r="B628" s="4"/>
       <c r="C628" s="4"/>
@@ -8833,7 +8623,7 @@
       <c r="F628" s="4"/>
       <c r="G628" s="4"/>
     </row>
-    <row r="629" spans="1:7" ht="15">
+    <row r="629" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A629" s="4"/>
       <c r="B629" s="4"/>
       <c r="C629" s="4"/>
@@ -8841,7 +8631,7 @@
       <c r="F629" s="4"/>
       <c r="G629" s="4"/>
     </row>
-    <row r="630" spans="1:7" ht="15">
+    <row r="630" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A630" s="4"/>
       <c r="B630" s="4"/>
       <c r="C630" s="4"/>
@@ -8849,7 +8639,7 @@
       <c r="F630" s="4"/>
       <c r="G630" s="4"/>
     </row>
-    <row r="631" spans="1:7" ht="15">
+    <row r="631" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A631" s="4"/>
       <c r="B631" s="4"/>
       <c r="C631" s="4"/>
@@ -8857,7 +8647,7 @@
       <c r="F631" s="4"/>
       <c r="G631" s="4"/>
     </row>
-    <row r="632" spans="1:7" ht="15">
+    <row r="632" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A632" s="4"/>
       <c r="B632" s="4"/>
       <c r="C632" s="4"/>
@@ -8865,7 +8655,7 @@
       <c r="F632" s="4"/>
       <c r="G632" s="4"/>
     </row>
-    <row r="633" spans="1:7" ht="15">
+    <row r="633" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A633" s="4"/>
       <c r="B633" s="4"/>
       <c r="C633" s="4"/>
@@ -8873,7 +8663,7 @@
       <c r="F633" s="4"/>
       <c r="G633" s="4"/>
     </row>
-    <row r="634" spans="1:7" ht="15">
+    <row r="634" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A634" s="4"/>
       <c r="B634" s="4"/>
       <c r="C634" s="4"/>
@@ -8881,7 +8671,7 @@
       <c r="F634" s="4"/>
       <c r="G634" s="4"/>
     </row>
-    <row r="635" spans="1:7" ht="15">
+    <row r="635" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A635" s="4"/>
       <c r="B635" s="4"/>
       <c r="C635" s="4"/>
@@ -8889,7 +8679,7 @@
       <c r="F635" s="4"/>
       <c r="G635" s="4"/>
     </row>
-    <row r="636" spans="1:7" ht="15">
+    <row r="636" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A636" s="4"/>
       <c r="B636" s="4"/>
       <c r="C636" s="4"/>
@@ -8897,7 +8687,7 @@
       <c r="F636" s="4"/>
       <c r="G636" s="4"/>
     </row>
-    <row r="637" spans="1:7" ht="15">
+    <row r="637" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A637" s="4"/>
       <c r="B637" s="4"/>
       <c r="C637" s="4"/>
@@ -8905,7 +8695,7 @@
       <c r="F637" s="4"/>
       <c r="G637" s="4"/>
     </row>
-    <row r="638" spans="1:7" ht="15">
+    <row r="638" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A638" s="4"/>
       <c r="B638" s="4"/>
       <c r="C638" s="4"/>
@@ -8913,7 +8703,7 @@
       <c r="F638" s="4"/>
       <c r="G638" s="4"/>
     </row>
-    <row r="639" spans="1:7" ht="15">
+    <row r="639" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A639" s="4"/>
       <c r="B639" s="4"/>
       <c r="C639" s="4"/>
@@ -8921,7 +8711,7 @@
       <c r="F639" s="4"/>
       <c r="G639" s="4"/>
     </row>
-    <row r="640" spans="1:7" ht="15">
+    <row r="640" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A640" s="4"/>
       <c r="B640" s="4"/>
       <c r="C640" s="4"/>
@@ -8929,7 +8719,7 @@
       <c r="F640" s="4"/>
       <c r="G640" s="4"/>
     </row>
-    <row r="641" spans="1:7" ht="15">
+    <row r="641" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A641" s="4"/>
       <c r="B641" s="4"/>
       <c r="C641" s="4"/>
@@ -8937,7 +8727,7 @@
       <c r="F641" s="4"/>
       <c r="G641" s="4"/>
     </row>
-    <row r="642" spans="1:7" ht="15">
+    <row r="642" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A642" s="4"/>
       <c r="B642" s="4"/>
       <c r="C642" s="4"/>
@@ -8945,7 +8735,7 @@
       <c r="F642" s="4"/>
       <c r="G642" s="4"/>
     </row>
-    <row r="643" spans="1:7" ht="15">
+    <row r="643" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A643" s="4"/>
       <c r="B643" s="4"/>
       <c r="C643" s="4"/>
@@ -8953,7 +8743,7 @@
       <c r="F643" s="4"/>
       <c r="G643" s="4"/>
     </row>
-    <row r="644" spans="1:7" ht="15">
+    <row r="644" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A644" s="4"/>
       <c r="B644" s="4"/>
       <c r="C644" s="4"/>
@@ -8961,7 +8751,7 @@
       <c r="F644" s="4"/>
       <c r="G644" s="4"/>
     </row>
-    <row r="645" spans="1:7" ht="15">
+    <row r="645" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A645" s="4"/>
       <c r="B645" s="4"/>
       <c r="C645" s="4"/>
@@ -8969,7 +8759,7 @@
       <c r="F645" s="4"/>
       <c r="G645" s="4"/>
     </row>
-    <row r="646" spans="1:7" ht="15">
+    <row r="646" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A646" s="4"/>
       <c r="B646" s="4"/>
       <c r="C646" s="4"/>
@@ -8977,7 +8767,7 @@
       <c r="F646" s="4"/>
       <c r="G646" s="4"/>
     </row>
-    <row r="647" spans="1:7" ht="15">
+    <row r="647" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A647" s="4"/>
       <c r="B647" s="4"/>
       <c r="C647" s="4"/>
@@ -8985,7 +8775,7 @@
       <c r="F647" s="4"/>
       <c r="G647" s="4"/>
     </row>
-    <row r="648" spans="1:7" ht="15">
+    <row r="648" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A648" s="4"/>
       <c r="B648" s="4"/>
       <c r="C648" s="4"/>
@@ -8993,7 +8783,7 @@
       <c r="F648" s="4"/>
       <c r="G648" s="4"/>
     </row>
-    <row r="649" spans="1:7" ht="15">
+    <row r="649" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A649" s="4"/>
       <c r="B649" s="4"/>
       <c r="C649" s="4"/>
@@ -9001,7 +8791,7 @@
       <c r="F649" s="4"/>
       <c r="G649" s="4"/>
     </row>
-    <row r="650" spans="1:7" ht="15">
+    <row r="650" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A650" s="4"/>
       <c r="B650" s="4"/>
       <c r="C650" s="4"/>
@@ -9009,7 +8799,7 @@
       <c r="F650" s="4"/>
       <c r="G650" s="4"/>
     </row>
-    <row r="651" spans="1:7" ht="15">
+    <row r="651" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A651" s="4"/>
       <c r="B651" s="4"/>
       <c r="C651" s="4"/>
@@ -9017,7 +8807,7 @@
       <c r="F651" s="4"/>
       <c r="G651" s="4"/>
     </row>
-    <row r="652" spans="1:7" ht="15">
+    <row r="652" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A652" s="4"/>
       <c r="B652" s="4"/>
       <c r="C652" s="4"/>
@@ -9025,7 +8815,7 @@
       <c r="F652" s="4"/>
       <c r="G652" s="4"/>
     </row>
-    <row r="653" spans="1:7" ht="15">
+    <row r="653" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A653" s="4"/>
       <c r="B653" s="4"/>
       <c r="C653" s="4"/>
@@ -9033,7 +8823,7 @@
       <c r="F653" s="4"/>
       <c r="G653" s="4"/>
     </row>
-    <row r="654" spans="1:7" ht="15">
+    <row r="654" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A654" s="4"/>
       <c r="B654" s="4"/>
       <c r="C654" s="4"/>
@@ -9041,7 +8831,7 @@
       <c r="F654" s="4"/>
       <c r="G654" s="4"/>
     </row>
-    <row r="655" spans="1:7" ht="15">
+    <row r="655" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A655" s="4"/>
       <c r="B655" s="4"/>
       <c r="C655" s="4"/>
@@ -9049,7 +8839,7 @@
       <c r="F655" s="4"/>
       <c r="G655" s="4"/>
     </row>
-    <row r="656" spans="1:7" ht="15">
+    <row r="656" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A656" s="4"/>
       <c r="B656" s="4"/>
       <c r="C656" s="4"/>
@@ -9057,7 +8847,7 @@
       <c r="F656" s="4"/>
       <c r="G656" s="4"/>
     </row>
-    <row r="657" spans="1:7" ht="15">
+    <row r="657" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A657" s="4"/>
       <c r="B657" s="4"/>
       <c r="C657" s="4"/>
@@ -9065,7 +8855,7 @@
       <c r="F657" s="4"/>
       <c r="G657" s="4"/>
     </row>
-    <row r="658" spans="1:7" ht="15">
+    <row r="658" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A658" s="4"/>
       <c r="B658" s="4"/>
       <c r="C658" s="4"/>
@@ -9073,7 +8863,7 @@
       <c r="F658" s="4"/>
       <c r="G658" s="4"/>
     </row>
-    <row r="659" spans="1:7" ht="15">
+    <row r="659" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A659" s="4"/>
       <c r="B659" s="4"/>
       <c r="C659" s="4"/>
@@ -9081,7 +8871,7 @@
       <c r="F659" s="4"/>
       <c r="G659" s="4"/>
     </row>
-    <row r="660" spans="1:7" ht="15">
+    <row r="660" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A660" s="4"/>
       <c r="B660" s="4"/>
       <c r="C660" s="4"/>
@@ -9089,7 +8879,7 @@
       <c r="F660" s="4"/>
       <c r="G660" s="4"/>
     </row>
-    <row r="661" spans="1:7" ht="15">
+    <row r="661" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A661" s="4"/>
       <c r="B661" s="4"/>
       <c r="C661" s="4"/>
@@ -9097,7 +8887,7 @@
       <c r="F661" s="4"/>
       <c r="G661" s="4"/>
     </row>
-    <row r="662" spans="1:7" ht="15">
+    <row r="662" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A662" s="4"/>
       <c r="B662" s="4"/>
       <c r="C662" s="4"/>
@@ -9105,7 +8895,7 @@
       <c r="F662" s="4"/>
       <c r="G662" s="4"/>
     </row>
-    <row r="663" spans="1:7" ht="15">
+    <row r="663" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A663" s="4"/>
       <c r="B663" s="4"/>
       <c r="C663" s="4"/>
@@ -9113,7 +8903,7 @@
       <c r="F663" s="4"/>
       <c r="G663" s="4"/>
     </row>
-    <row r="664" spans="1:7" ht="15">
+    <row r="664" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A664" s="4"/>
       <c r="B664" s="4"/>
       <c r="C664" s="4"/>
@@ -9121,7 +8911,7 @@
       <c r="F664" s="4"/>
       <c r="G664" s="4"/>
     </row>
-    <row r="665" spans="1:7" ht="15">
+    <row r="665" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A665" s="4"/>
       <c r="B665" s="4"/>
       <c r="C665" s="4"/>
@@ -9129,7 +8919,7 @@
       <c r="F665" s="4"/>
       <c r="G665" s="4"/>
     </row>
-    <row r="666" spans="1:7" ht="15">
+    <row r="666" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A666" s="4"/>
       <c r="B666" s="4"/>
       <c r="C666" s="4"/>
@@ -9137,7 +8927,7 @@
       <c r="F666" s="4"/>
       <c r="G666" s="4"/>
     </row>
-    <row r="667" spans="1:7" ht="15">
+    <row r="667" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A667" s="4"/>
       <c r="B667" s="4"/>
       <c r="C667" s="4"/>
@@ -9145,7 +8935,7 @@
       <c r="F667" s="4"/>
       <c r="G667" s="4"/>
     </row>
-    <row r="668" spans="1:7" ht="15">
+    <row r="668" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A668" s="4"/>
       <c r="B668" s="4"/>
       <c r="C668" s="4"/>
@@ -9153,7 +8943,7 @@
       <c r="F668" s="4"/>
       <c r="G668" s="4"/>
     </row>
-    <row r="669" spans="1:7" ht="15">
+    <row r="669" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A669" s="4"/>
       <c r="B669" s="4"/>
       <c r="C669" s="4"/>
@@ -9161,7 +8951,7 @@
       <c r="F669" s="4"/>
       <c r="G669" s="4"/>
     </row>
-    <row r="670" spans="1:7" ht="15">
+    <row r="670" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A670" s="4"/>
       <c r="B670" s="4"/>
       <c r="C670" s="4"/>
@@ -9169,7 +8959,7 @@
       <c r="F670" s="4"/>
       <c r="G670" s="4"/>
     </row>
-    <row r="671" spans="1:7" ht="15">
+    <row r="671" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A671" s="4"/>
       <c r="B671" s="4"/>
       <c r="C671" s="4"/>
@@ -9177,7 +8967,7 @@
       <c r="F671" s="4"/>
       <c r="G671" s="4"/>
     </row>
-    <row r="672" spans="1:7" ht="15">
+    <row r="672" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A672" s="4"/>
       <c r="B672" s="4"/>
       <c r="C672" s="4"/>
@@ -9185,7 +8975,7 @@
       <c r="F672" s="4"/>
       <c r="G672" s="4"/>
     </row>
-    <row r="673" spans="1:7" ht="15">
+    <row r="673" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A673" s="4"/>
       <c r="B673" s="4"/>
       <c r="C673" s="4"/>
@@ -9193,7 +8983,7 @@
       <c r="F673" s="4"/>
       <c r="G673" s="4"/>
     </row>
-    <row r="674" spans="1:7" ht="15">
+    <row r="674" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A674" s="4"/>
       <c r="B674" s="4"/>
       <c r="C674" s="4"/>
@@ -9201,7 +8991,7 @@
       <c r="F674" s="4"/>
       <c r="G674" s="4"/>
     </row>
-    <row r="675" spans="1:7" ht="15">
+    <row r="675" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A675" s="4"/>
       <c r="B675" s="4"/>
       <c r="C675" s="4"/>
@@ -9209,7 +8999,7 @@
       <c r="F675" s="4"/>
       <c r="G675" s="4"/>
     </row>
-    <row r="676" spans="1:7" ht="15">
+    <row r="676" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A676" s="4"/>
       <c r="B676" s="4"/>
       <c r="C676" s="4"/>
@@ -9217,7 +9007,7 @@
       <c r="F676" s="4"/>
       <c r="G676" s="4"/>
     </row>
-    <row r="677" spans="1:7" ht="15">
+    <row r="677" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A677" s="4"/>
       <c r="B677" s="4"/>
       <c r="C677" s="4"/>
@@ -9225,7 +9015,7 @@
       <c r="F677" s="4"/>
       <c r="G677" s="4"/>
     </row>
-    <row r="678" spans="1:7" ht="15">
+    <row r="678" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A678" s="4"/>
       <c r="B678" s="4"/>
       <c r="C678" s="4"/>
@@ -9233,7 +9023,7 @@
       <c r="F678" s="4"/>
       <c r="G678" s="4"/>
     </row>
-    <row r="679" spans="1:7" ht="15">
+    <row r="679" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A679" s="4"/>
       <c r="B679" s="4"/>
       <c r="C679" s="4"/>
@@ -9241,7 +9031,7 @@
       <c r="F679" s="4"/>
       <c r="G679" s="4"/>
     </row>
-    <row r="680" spans="1:7" ht="15">
+    <row r="680" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A680" s="4"/>
       <c r="B680" s="4"/>
       <c r="C680" s="4"/>
@@ -9249,7 +9039,7 @@
       <c r="F680" s="4"/>
       <c r="G680" s="4"/>
     </row>
-    <row r="681" spans="1:7" ht="15">
+    <row r="681" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A681" s="4"/>
       <c r="B681" s="4"/>
       <c r="C681" s="4"/>
@@ -9257,7 +9047,7 @@
       <c r="F681" s="4"/>
       <c r="G681" s="4"/>
     </row>
-    <row r="682" spans="1:7" ht="15">
+    <row r="682" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A682" s="4"/>
       <c r="B682" s="4"/>
       <c r="C682" s="4"/>
@@ -9265,7 +9055,7 @@
       <c r="F682" s="4"/>
       <c r="G682" s="4"/>
     </row>
-    <row r="683" spans="1:7" ht="15">
+    <row r="683" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A683" s="4"/>
       <c r="B683" s="4"/>
       <c r="C683" s="4"/>
@@ -9273,7 +9063,7 @@
       <c r="F683" s="4"/>
       <c r="G683" s="4"/>
     </row>
-    <row r="684" spans="1:7" ht="15">
+    <row r="684" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A684" s="4"/>
       <c r="B684" s="4"/>
       <c r="C684" s="4"/>
@@ -9281,7 +9071,7 @@
       <c r="F684" s="4"/>
       <c r="G684" s="4"/>
     </row>
-    <row r="685" spans="1:7" ht="15">
+    <row r="685" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A685" s="4"/>
       <c r="B685" s="4"/>
       <c r="C685" s="4"/>
@@ -9289,7 +9079,7 @@
       <c r="F685" s="4"/>
       <c r="G685" s="4"/>
     </row>
-    <row r="686" spans="1:7" ht="15">
+    <row r="686" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A686" s="4"/>
       <c r="B686" s="4"/>
       <c r="C686" s="4"/>
@@ -9297,7 +9087,7 @@
       <c r="F686" s="4"/>
       <c r="G686" s="4"/>
     </row>
-    <row r="687" spans="1:7" ht="15">
+    <row r="687" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A687" s="4"/>
       <c r="B687" s="4"/>
       <c r="C687" s="4"/>
@@ -9305,7 +9095,7 @@
       <c r="F687" s="4"/>
       <c r="G687" s="4"/>
     </row>
-    <row r="688" spans="1:7" ht="15">
+    <row r="688" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A688" s="4"/>
       <c r="B688" s="4"/>
       <c r="C688" s="4"/>
@@ -9313,7 +9103,7 @@
       <c r="F688" s="4"/>
       <c r="G688" s="4"/>
     </row>
-    <row r="689" spans="1:7" ht="15">
+    <row r="689" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A689" s="4"/>
       <c r="B689" s="4"/>
       <c r="C689" s="4"/>
@@ -9321,7 +9111,7 @@
       <c r="F689" s="4"/>
       <c r="G689" s="4"/>
     </row>
-    <row r="690" spans="1:7" ht="15">
+    <row r="690" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A690" s="4"/>
       <c r="B690" s="4"/>
       <c r="C690" s="4"/>
@@ -9329,7 +9119,7 @@
       <c r="F690" s="4"/>
       <c r="G690" s="4"/>
     </row>
-    <row r="691" spans="1:7" ht="15">
+    <row r="691" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A691" s="4"/>
       <c r="B691" s="4"/>
       <c r="C691" s="4"/>
@@ -9337,7 +9127,7 @@
       <c r="F691" s="4"/>
       <c r="G691" s="4"/>
     </row>
-    <row r="692" spans="1:7" ht="15">
+    <row r="692" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A692" s="4"/>
       <c r="B692" s="4"/>
       <c r="C692" s="4"/>
@@ -9345,7 +9135,7 @@
       <c r="F692" s="4"/>
       <c r="G692" s="4"/>
     </row>
-    <row r="693" spans="1:7" ht="15">
+    <row r="693" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A693" s="4"/>
       <c r="B693" s="4"/>
       <c r="C693" s="4"/>
@@ -9353,7 +9143,7 @@
       <c r="F693" s="4"/>
       <c r="G693" s="4"/>
     </row>
-    <row r="694" spans="1:7" ht="15">
+    <row r="694" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A694" s="4"/>
       <c r="B694" s="4"/>
       <c r="C694" s="4"/>
@@ -9361,7 +9151,7 @@
       <c r="F694" s="4"/>
       <c r="G694" s="4"/>
     </row>
-    <row r="695" spans="1:7" ht="15">
+    <row r="695" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A695" s="4"/>
       <c r="B695" s="4"/>
       <c r="C695" s="4"/>
@@ -9369,7 +9159,7 @@
       <c r="F695" s="4"/>
       <c r="G695" s="4"/>
     </row>
-    <row r="696" spans="1:7" ht="15">
+    <row r="696" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A696" s="4"/>
       <c r="B696" s="4"/>
       <c r="C696" s="4"/>
@@ -9377,7 +9167,7 @@
       <c r="F696" s="4"/>
       <c r="G696" s="4"/>
     </row>
-    <row r="697" spans="1:7" ht="15">
+    <row r="697" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A697" s="4"/>
       <c r="B697" s="4"/>
       <c r="C697" s="4"/>
@@ -9385,7 +9175,7 @@
       <c r="F697" s="4"/>
       <c r="G697" s="4"/>
     </row>
-    <row r="698" spans="1:7" ht="15">
+    <row r="698" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A698" s="4"/>
       <c r="B698" s="4"/>
       <c r="C698" s="4"/>
@@ -9393,7 +9183,7 @@
       <c r="F698" s="4"/>
       <c r="G698" s="4"/>
     </row>
-    <row r="699" spans="1:7" ht="15">
+    <row r="699" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A699" s="4"/>
       <c r="B699" s="4"/>
       <c r="C699" s="4"/>
@@ -9401,7 +9191,7 @@
       <c r="F699" s="4"/>
       <c r="G699" s="4"/>
     </row>
-    <row r="700" spans="1:7" ht="15">
+    <row r="700" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A700" s="4"/>
       <c r="B700" s="4"/>
       <c r="C700" s="4"/>
@@ -9409,7 +9199,7 @@
       <c r="F700" s="4"/>
       <c r="G700" s="4"/>
     </row>
-    <row r="701" spans="1:7" ht="15">
+    <row r="701" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A701" s="4"/>
       <c r="B701" s="4"/>
       <c r="C701" s="4"/>
@@ -9417,7 +9207,7 @@
       <c r="F701" s="4"/>
       <c r="G701" s="4"/>
     </row>
-    <row r="702" spans="1:7" ht="15">
+    <row r="702" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A702" s="4"/>
       <c r="B702" s="4"/>
       <c r="C702" s="4"/>
@@ -9425,7 +9215,7 @@
       <c r="F702" s="4"/>
       <c r="G702" s="4"/>
     </row>
-    <row r="703" spans="1:7" ht="15">
+    <row r="703" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A703" s="4"/>
       <c r="B703" s="4"/>
       <c r="C703" s="4"/>
@@ -9433,7 +9223,7 @@
       <c r="F703" s="4"/>
       <c r="G703" s="4"/>
     </row>
-    <row r="704" spans="1:7" ht="15">
+    <row r="704" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A704" s="4"/>
       <c r="B704" s="4"/>
       <c r="C704" s="4"/>
@@ -9441,7 +9231,7 @@
       <c r="F704" s="4"/>
       <c r="G704" s="4"/>
     </row>
-    <row r="705" spans="1:7" ht="15">
+    <row r="705" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A705" s="4"/>
       <c r="B705" s="4"/>
       <c r="C705" s="4"/>
@@ -9449,7 +9239,7 @@
       <c r="F705" s="4"/>
       <c r="G705" s="4"/>
     </row>
-    <row r="706" spans="1:7" ht="15">
+    <row r="706" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A706" s="4"/>
       <c r="B706" s="4"/>
       <c r="C706" s="4"/>
@@ -9457,7 +9247,7 @@
       <c r="F706" s="4"/>
       <c r="G706" s="4"/>
     </row>
-    <row r="707" spans="1:7" ht="15">
+    <row r="707" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A707" s="4"/>
       <c r="B707" s="4"/>
       <c r="C707" s="4"/>
@@ -9465,7 +9255,7 @@
       <c r="F707" s="4"/>
       <c r="G707" s="4"/>
     </row>
-    <row r="708" spans="1:7" ht="15">
+    <row r="708" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A708" s="4"/>
       <c r="B708" s="4"/>
       <c r="C708" s="4"/>
@@ -9473,7 +9263,7 @@
       <c r="F708" s="4"/>
       <c r="G708" s="4"/>
     </row>
-    <row r="709" spans="1:7" ht="15">
+    <row r="709" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A709" s="4"/>
       <c r="B709" s="4"/>
       <c r="C709" s="4"/>
@@ -9481,7 +9271,7 @@
       <c r="F709" s="4"/>
       <c r="G709" s="4"/>
     </row>
-    <row r="710" spans="1:7" ht="15">
+    <row r="710" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A710" s="4"/>
       <c r="B710" s="4"/>
       <c r="C710" s="4"/>
@@ -9489,7 +9279,7 @@
       <c r="F710" s="4"/>
       <c r="G710" s="4"/>
     </row>
-    <row r="711" spans="1:7" ht="15">
+    <row r="711" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A711" s="4"/>
       <c r="B711" s="4"/>
       <c r="C711" s="4"/>
@@ -9497,7 +9287,7 @@
       <c r="F711" s="4"/>
       <c r="G711" s="4"/>
     </row>
-    <row r="712" spans="1:7" ht="15">
+    <row r="712" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A712" s="4"/>
       <c r="B712" s="4"/>
       <c r="C712" s="4"/>
@@ -9505,7 +9295,7 @@
       <c r="F712" s="4"/>
       <c r="G712" s="4"/>
     </row>
-    <row r="713" spans="1:7" ht="15">
+    <row r="713" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A713" s="4"/>
       <c r="B713" s="4"/>
       <c r="C713" s="4"/>
@@ -9513,7 +9303,7 @@
       <c r="F713" s="4"/>
       <c r="G713" s="4"/>
     </row>
-    <row r="714" spans="1:7" ht="15">
+    <row r="714" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A714" s="4"/>
       <c r="B714" s="4"/>
       <c r="C714" s="4"/>
@@ -9521,7 +9311,7 @@
       <c r="F714" s="4"/>
       <c r="G714" s="4"/>
     </row>
-    <row r="715" spans="1:7" ht="15">
+    <row r="715" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A715" s="4"/>
       <c r="B715" s="4"/>
       <c r="C715" s="4"/>
@@ -9529,7 +9319,7 @@
       <c r="F715" s="4"/>
       <c r="G715" s="4"/>
     </row>
-    <row r="716" spans="1:7" ht="15">
+    <row r="716" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A716" s="4"/>
       <c r="B716" s="4"/>
       <c r="C716" s="4"/>
@@ -9537,7 +9327,7 @@
       <c r="F716" s="4"/>
       <c r="G716" s="4"/>
     </row>
-    <row r="717" spans="1:7" ht="15">
+    <row r="717" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A717" s="4"/>
       <c r="B717" s="4"/>
       <c r="C717" s="4"/>
@@ -9545,7 +9335,7 @@
       <c r="F717" s="4"/>
       <c r="G717" s="4"/>
     </row>
-    <row r="718" spans="1:7" ht="15">
+    <row r="718" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A718" s="4"/>
       <c r="B718" s="4"/>
       <c r="C718" s="4"/>
@@ -9553,7 +9343,7 @@
       <c r="F718" s="4"/>
       <c r="G718" s="4"/>
     </row>
-    <row r="719" spans="1:7" ht="15">
+    <row r="719" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A719" s="4"/>
       <c r="B719" s="4"/>
       <c r="C719" s="4"/>
@@ -9561,7 +9351,7 @@
       <c r="F719" s="4"/>
       <c r="G719" s="4"/>
     </row>
-    <row r="720" spans="1:7" ht="15">
+    <row r="720" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A720" s="4"/>
       <c r="B720" s="4"/>
       <c r="C720" s="4"/>
@@ -9569,7 +9359,7 @@
       <c r="F720" s="4"/>
       <c r="G720" s="4"/>
     </row>
-    <row r="721" spans="1:7" ht="15">
+    <row r="721" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A721" s="4"/>
       <c r="B721" s="4"/>
       <c r="C721" s="4"/>
@@ -9577,7 +9367,7 @@
       <c r="F721" s="4"/>
       <c r="G721" s="4"/>
     </row>
-    <row r="722" spans="1:7" ht="15">
+    <row r="722" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A722" s="4"/>
       <c r="B722" s="4"/>
       <c r="C722" s="4"/>
@@ -9585,7 +9375,7 @@
       <c r="F722" s="4"/>
       <c r="G722" s="4"/>
     </row>
-    <row r="723" spans="1:7" ht="15">
+    <row r="723" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A723" s="4"/>
       <c r="B723" s="4"/>
       <c r="C723" s="4"/>
@@ -9593,7 +9383,7 @@
       <c r="F723" s="4"/>
       <c r="G723" s="4"/>
     </row>
-    <row r="724" spans="1:7" ht="15">
+    <row r="724" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A724" s="4"/>
       <c r="B724" s="4"/>
       <c r="C724" s="4"/>
@@ -9601,7 +9391,7 @@
       <c r="F724" s="4"/>
       <c r="G724" s="4"/>
     </row>
-    <row r="725" spans="1:7" ht="15">
+    <row r="725" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A725" s="4"/>
       <c r="B725" s="4"/>
       <c r="C725" s="4"/>
@@ -9609,7 +9399,7 @@
       <c r="F725" s="4"/>
       <c r="G725" s="4"/>
     </row>
-    <row r="726" spans="1:7" ht="15">
+    <row r="726" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A726" s="4"/>
       <c r="B726" s="4"/>
       <c r="C726" s="4"/>
@@ -9617,7 +9407,7 @@
       <c r="F726" s="4"/>
       <c r="G726" s="4"/>
     </row>
-    <row r="727" spans="1:7" ht="15">
+    <row r="727" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A727" s="4"/>
       <c r="B727" s="4"/>
       <c r="C727" s="4"/>
@@ -9625,7 +9415,7 @@
       <c r="F727" s="4"/>
       <c r="G727" s="4"/>
     </row>
-    <row r="728" spans="1:7" ht="15">
+    <row r="728" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A728" s="4"/>
       <c r="B728" s="4"/>
       <c r="C728" s="4"/>
@@ -9633,7 +9423,7 @@
       <c r="F728" s="4"/>
       <c r="G728" s="4"/>
     </row>
-    <row r="729" spans="1:7" ht="15">
+    <row r="729" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A729" s="4"/>
       <c r="B729" s="4"/>
       <c r="C729" s="4"/>
@@ -9641,7 +9431,7 @@
       <c r="F729" s="4"/>
       <c r="G729" s="4"/>
     </row>
-    <row r="730" spans="1:7" ht="15">
+    <row r="730" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A730" s="4"/>
       <c r="B730" s="4"/>
       <c r="C730" s="4"/>
@@ -9649,7 +9439,7 @@
       <c r="F730" s="4"/>
       <c r="G730" s="4"/>
     </row>
-    <row r="731" spans="1:7" ht="15">
+    <row r="731" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A731" s="4"/>
       <c r="B731" s="4"/>
       <c r="C731" s="4"/>
@@ -9657,7 +9447,7 @@
       <c r="F731" s="4"/>
       <c r="G731" s="4"/>
     </row>
-    <row r="732" spans="1:7" ht="15">
+    <row r="732" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A732" s="4"/>
       <c r="B732" s="4"/>
       <c r="C732" s="4"/>
@@ -9665,7 +9455,7 @@
       <c r="F732" s="4"/>
       <c r="G732" s="4"/>
     </row>
-    <row r="733" spans="1:7" ht="15">
+    <row r="733" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A733" s="4"/>
       <c r="B733" s="4"/>
       <c r="C733" s="4"/>
@@ -9673,7 +9463,7 @@
       <c r="F733" s="4"/>
       <c r="G733" s="4"/>
     </row>
-    <row r="734" spans="1:7" ht="15">
+    <row r="734" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A734" s="4"/>
       <c r="B734" s="4"/>
       <c r="C734" s="4"/>
@@ -9681,7 +9471,7 @@
       <c r="F734" s="4"/>
       <c r="G734" s="4"/>
     </row>
-    <row r="735" spans="1:7" ht="15">
+    <row r="735" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A735" s="4"/>
       <c r="B735" s="4"/>
       <c r="C735" s="4"/>
@@ -9689,7 +9479,7 @@
       <c r="F735" s="4"/>
       <c r="G735" s="4"/>
     </row>
-    <row r="736" spans="1:7" ht="15">
+    <row r="736" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A736" s="4"/>
       <c r="B736" s="4"/>
       <c r="C736" s="4"/>
@@ -9697,7 +9487,7 @@
       <c r="F736" s="4"/>
       <c r="G736" s="4"/>
     </row>
-    <row r="737" spans="1:7" ht="15">
+    <row r="737" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A737" s="4"/>
       <c r="B737" s="4"/>
       <c r="C737" s="4"/>
@@ -9705,7 +9495,7 @@
       <c r="F737" s="4"/>
       <c r="G737" s="4"/>
     </row>
-    <row r="738" spans="1:7" ht="15">
+    <row r="738" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A738" s="4"/>
       <c r="B738" s="4"/>
       <c r="C738" s="4"/>
@@ -9713,7 +9503,7 @@
       <c r="F738" s="4"/>
       <c r="G738" s="4"/>
     </row>
-    <row r="739" spans="1:7" ht="15">
+    <row r="739" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A739" s="4"/>
       <c r="B739" s="4"/>
       <c r="C739" s="4"/>
@@ -9721,7 +9511,7 @@
       <c r="F739" s="4"/>
       <c r="G739" s="4"/>
     </row>
-    <row r="740" spans="1:7" ht="15">
+    <row r="740" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A740" s="4"/>
       <c r="B740" s="4"/>
       <c r="C740" s="4"/>
@@ -9729,7 +9519,7 @@
       <c r="F740" s="4"/>
       <c r="G740" s="4"/>
     </row>
-    <row r="741" spans="1:7" ht="15">
+    <row r="741" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A741" s="4"/>
       <c r="B741" s="4"/>
       <c r="C741" s="4"/>
@@ -9737,7 +9527,7 @@
       <c r="F741" s="4"/>
       <c r="G741" s="4"/>
     </row>
-    <row r="742" spans="1:7" ht="15">
+    <row r="742" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A742" s="4"/>
       <c r="B742" s="4"/>
       <c r="C742" s="4"/>
@@ -9745,7 +9535,7 @@
       <c r="F742" s="4"/>
       <c r="G742" s="4"/>
     </row>
-    <row r="743" spans="1:7" ht="15">
+    <row r="743" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A743" s="4"/>
       <c r="B743" s="4"/>
       <c r="C743" s="4"/>
@@ -9753,7 +9543,7 @@
       <c r="F743" s="4"/>
       <c r="G743" s="4"/>
     </row>
-    <row r="744" spans="1:7" ht="15">
+    <row r="744" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A744" s="4"/>
       <c r="B744" s="4"/>
       <c r="C744" s="4"/>
@@ -9761,7 +9551,7 @@
       <c r="F744" s="4"/>
       <c r="G744" s="4"/>
     </row>
-    <row r="745" spans="1:7" ht="15">
+    <row r="745" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A745" s="4"/>
       <c r="B745" s="4"/>
       <c r="C745" s="4"/>
@@ -9769,7 +9559,7 @@
       <c r="F745" s="4"/>
       <c r="G745" s="4"/>
     </row>
-    <row r="746" spans="1:7" ht="15">
+    <row r="746" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A746" s="4"/>
       <c r="B746" s="4"/>
       <c r="C746" s="4"/>
@@ -9777,7 +9567,7 @@
       <c r="F746" s="4"/>
       <c r="G746" s="4"/>
     </row>
-    <row r="747" spans="1:7" ht="15">
+    <row r="747" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A747" s="4"/>
       <c r="B747" s="4"/>
       <c r="C747" s="4"/>
@@ -9785,7 +9575,7 @@
       <c r="F747" s="4"/>
       <c r="G747" s="4"/>
     </row>
-    <row r="748" spans="1:7" ht="15">
+    <row r="748" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A748" s="4"/>
       <c r="B748" s="4"/>
       <c r="C748" s="4"/>
@@ -9793,7 +9583,7 @@
       <c r="F748" s="4"/>
       <c r="G748" s="4"/>
     </row>
-    <row r="749" spans="1:7" ht="15">
+    <row r="749" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A749" s="4"/>
       <c r="B749" s="4"/>
       <c r="C749" s="4"/>
@@ -9801,7 +9591,7 @@
       <c r="F749" s="4"/>
       <c r="G749" s="4"/>
     </row>
-    <row r="750" spans="1:7" ht="15">
+    <row r="750" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A750" s="4"/>
       <c r="B750" s="4"/>
       <c r="C750" s="4"/>
@@ -9809,7 +9599,7 @@
       <c r="F750" s="4"/>
       <c r="G750" s="4"/>
     </row>
-    <row r="751" spans="1:7" ht="15">
+    <row r="751" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A751" s="4"/>
       <c r="B751" s="4"/>
       <c r="C751" s="4"/>
